--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -6906,29 +6906,25 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>addresses.isDefault</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>Mark the standard address per type (unified-address model; at most one default per customer &amp; type) — v3 partner addresses carry no isDefault flag.</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read · Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Correcting a customer number after the fact. v3 accepts a number on POST but not on PATCH, so a typo in a migrated number can only be fixed in the UI.</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -6938,29 +6934,25 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>addresses.label</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>Free label/name per address location (e.g. 'Lager München') — v3 knows only billing/shipping roles, no named locations.</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read · Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Customer vs. lead (Interessent). v2 has isLead, but no v3 customers payload carries it — not in the record, not behind any allowed include — so the core cannot set it without leaving v3. Roughly half a typical CRM migration is leads, so they all land as customers today.</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -6970,29 +6962,25 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>addresses.type</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>read, update</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Set the address role incl. the 'both' value (one address serving billing AND shipping) — v3 splits billing (primaryAddress/deviating) vs shipping (deliveryAddresses) by store, so the role is not a freely settable field.</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Active/archived state is not exposed via v3 customers — needed for honest archiving (plan §6.1).</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -7002,22 +6990,22 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>contacts.address</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>read, update</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Bind a contact person to a specific address (person-at-location) — v3 stores only a free-text contactPerson on delivery addresses, not a reference.</t>
+          <t>B2B hierarchy (branch → HQ) is not exposed via the public API (plan §6.1 parent).</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr"/>
@@ -7030,22 +7018,22 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>contacts.isPrimary</t>
+          <t>billTo</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>read, update</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Mark the main contact person — v3 contactPersons carry no primary flag.</t>
+          <t>Central billing (Zentralregulierung — invoice to association/HQ) is not exposed (plan §6.1 billTo).</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr"/>
@@ -7058,12 +7046,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>defaults.paymentTerms.dueDays</t>
+          <t>channels</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -7073,7 +7061,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Default payment term for the customer — drives every order/invoice; must be settable.</t>
+          <t>Per-channel external ids (channel links) are not exposed via the public API.</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr"/>
@@ -7086,7 +7074,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>defaults.taxation</t>
+          <t>addresses.type</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -7094,17 +7082,21 @@
           <t>create, update</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Default taxation scheme (domestic/euB2B/euOss/export) per customer.</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr"/>
+          <t>Set the address role incl. the 'both' value (one address serving billing AND shipping) — v3 splits billing (primaryAddress/deviating) vs shipping (deliveryAddresses) by store, so the role is not a freely settable field.</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create, update</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -7114,25 +7106,29 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>defaults.paymentMethod</t>
+          <t>addresses.label</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Default payment method per customer.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr"/>
+          <t>Free label/name per address location (e.g. 'Lager München') — v3 knows only billing/shipping roles, no named locations.</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read · Schema deklariert: create, update</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -7142,25 +7138,29 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>finance.creditLimit</t>
+          <t>addresses.isDefault</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>The customer credit limit — a core AR control; UI-only today, not writable via API (docs/05 #14).</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr"/>
+          <t>Mark the standard address per type (unified-address model; at most one default per customer &amp; type) — v3 partner addresses carry no isDefault flag.</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read · Schema deklariert: create, update</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>finance.onHold</t>
+          <t>defaults.paymentMethod</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Put a customer on delivery/credit hold — UI-only today (docs/05 #14).</t>
+          <t>Default payment method per customer.</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr"/>
@@ -7198,12 +7198,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>finance.dunningBlocked</t>
+          <t>defaults.paymentTerms.dueDays</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Block dunning for a customer — UI-only today.</t>
+          <t>Default payment term for the customer — drives every order/invoice; must be settable.</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr"/>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>finance.openAmount</t>
+          <t>defaults.taxation</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Aggregated open amount per customer is computed nowhere in the API (docs/05 #14) — must be derived/served.</t>
+          <t>Default taxation scheme (domestic/euB2B/euOss/export) per customer.</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr"/>
@@ -7254,12 +7254,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>defaults.shippingMethod</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, update</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the customer — today only readable, not writable via API.</t>
+          <t>The default shipping method is not surfaced by the v3 partner read.</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr"/>
@@ -7282,7 +7282,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>defaults.priceList</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Active/archived state is not exposed via v3 customers — needed for honest archiving (plan §6.1).</t>
+          <t>The assigned price list is not surfaced by the v3 partner read.</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr"/>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>defaults.partialShipping</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>B2B hierarchy (branch → HQ) is not exposed via the public API (plan §6.1 parent).</t>
+          <t>The partial-shipping preference is not surfaced by the v3 partner read.</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr"/>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>billTo</t>
+          <t>finance.openAmount</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Central billing (Zentralregulierung — invoice to association/HQ) is not exposed (plan §6.1 billTo).</t>
+          <t>Aggregated open amount per customer is computed nowhere in the API (docs/05 #14) — must be derived/served.</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr"/>
@@ -7366,12 +7366,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>channels</t>
+          <t>finance.creditLimit</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Per-channel external ids (channel links) are not exposed via the public API.</t>
+          <t>The customer credit limit — a core AR control; UI-only today, not writable via API (docs/05 #14).</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr"/>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>defaults.shippingMethod</t>
+          <t>finance.onHold</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>The default shipping method is not surfaced by the v3 partner read.</t>
+          <t>Put a customer on delivery/credit hold — UI-only today (docs/05 #14).</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr"/>
@@ -7422,12 +7422,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>defaults.priceList</t>
+          <t>finance.dunningBlocked</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>The assigned price list is not surfaced by the v3 partner read.</t>
+          <t>Block dunning for a customer — UI-only today.</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr"/>
@@ -7450,12 +7450,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>defaults.partialShipping</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>The partial-shipping preference is not surfaced by the v3 partner read.</t>
+          <t>Custom field values on the customer — today only readable, not writable via API.</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr"/>
@@ -7478,22 +7478,22 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>contacts.address</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Customer vs. lead (Interessent). v2 has isLead, but no v3 customers payload carries it — not in the record, not behind any allowed include — so the core cannot set it without leaving v3. Roughly half a typical CRM migration is leads, so they all land as customers today.</t>
+          <t>Bind a contact person to a specific address (person-at-location) — v3 stores only a free-text contactPerson on delivery addresses, not a reference.</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr"/>
@@ -7506,22 +7506,22 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contacts.isPrimary</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Correcting a customer number after the fact. v3 accepts a number on POST but not on PATCH, so a typo in a migrated number can only be fixed in the UI.</t>
+          <t>Mark the main contact person — v3 contactPersons carry no primary flag.</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr"/>
@@ -7534,12 +7534,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>references.customerInquiryNumber</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>The customer's inquiry / RFQ number — B2B standard; read-only upstream today.</t>
+          <t>Carrying a quote number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr"/>
@@ -7562,12 +7562,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>dates.validUntil</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Offer validity date — drives auto-expiry and follow-up; must be settable per quote.</t>
+          <t>Reassign the quote's partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>dates.expectedOrderDate</t>
+          <t>references.customerInquiryNumber</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Expected order date feeds the sales forecast — settable per quote.</t>
+          <t>The customer's inquiry / RFQ number — B2B standard; read-only upstream today.</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr"/>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>dates.requestedDelivery</t>
+          <t>dates.validUntil</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Desired delivery date on the quote — not writable upstream today.</t>
+          <t>Offer validity date — drives auto-expiry and follow-up; must be settable per quote.</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr"/>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>payment.method</t>
+          <t>dates.expectedOrderDate</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Payment method proposed on the quote — frequently set per offer.</t>
+          <t>Expected order date feeds the sales forecast — settable per quote.</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>payment.terms.dueDays</t>
+          <t>dates.requestedDelivery</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Payment term proposed on the quote.</t>
+          <t>Desired delivery date on the quote — not writable upstream today.</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr"/>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>shipping.method</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -7710,21 +7710,17 @@
           <t>create, update</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Shipping method proposed on the quote.</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -7762,7 +7758,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>payment.method</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -7777,7 +7773,7 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the quote — today only readable via include, not writable via API.</t>
+          <t>Payment method proposed on the quote — frequently set per offer.</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr"/>
@@ -7790,12 +7786,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>payment.terms.dueDays</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -7805,7 +7801,7 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Reassign the quote's partner after creation — v3 accepts it only on create.</t>
+          <t>Payment term proposed on the quote.</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr"/>
@@ -7818,25 +7814,29 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>shipping.method</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr"/>
+          <t>Shipping method proposed on the quote.</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create, update</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Carrying a quote number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+          <t>Custom field values on the quote — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr"/>
@@ -7874,22 +7874,22 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr"/>
@@ -7902,29 +7902,25 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>The customer's own order / PO number (B2B standard field). Read-only upstream today; a clerk must be able to set and correct it.</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Correcting a sales order number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -7934,12 +7930,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
@@ -7949,7 +7945,7 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>On the phone the customer quotes their PO number, not the ERP number — the full-text search must reach it.</t>
+          <t>Reassign the order to the correct customer after creation — v3 accepts the partner only on create today.</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr"/>
@@ -7962,25 +7958,29 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>references.externalNumber</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>search</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Support finds shop orders by the SHOP number the customer has.</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr"/>
+          <t>The customer's own order / PO number (B2B standard field). Read-only upstream today; a clerk must be able to set and correct it.</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>references.externalId</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Automated reconciliation matches by the external id.</t>
+          <t>On the phone the customer quotes their PO number, not the ERP number — the full-text search must reach it.</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr"/>
@@ -8018,29 +8018,25 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>dates.requestedDelivery</t>
+          <t>references.externalId</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>search</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Desired delivery date — core fulfilment field; one of the first things entered on an order. Not writable upstream today.</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: update</t>
-        </is>
-      </c>
+          <t>Automated reconciliation matches by the external id.</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -8050,29 +8046,25 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>shipping.method</t>
+          <t>references.externalNumber</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>search</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Carrier / shipping method — core to fulfilment; must be selectable per order.</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Support finds shop orders by the SHOP number the customer has.</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -8082,25 +8074,29 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>dates.requestedDelivery</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Custom field values carry company-specific data — today only readable via include, not writable via API (all documents).</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr"/>
+          <t>Desired delivery date — core fulfilment field; one of the first things entered on an order. Not writable upstream today.</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: update</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -8110,12 +8106,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>billingAddress.zip</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
@@ -8125,7 +8121,7 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Companies segment and find orders by their own custom-field values.</t>
+          <t>Postal-code search is a standard phone use-case (shop orders).</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr"/>
@@ -8138,12 +8134,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>billingAddress.email</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -8153,7 +8149,7 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Reassign the order to the correct customer after creation — v3 accepts the partner only on create today.</t>
+          <t>Email search is a standard use-case for shop orders — often the only identifier support has.</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr"/>
@@ -8166,7 +8162,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>fulfillmentPolicy.partialShipping</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -8181,7 +8177,7 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Partial-shipping policy has no upstream slot — the read reports a hardcoded "allowed". Needs a real v3 field before it can be written or trusted.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr"/>
@@ -8194,25 +8190,29 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>billingAddress.zip</t>
+          <t>shipping.method</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>search</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Postal-code search is a standard phone use-case (shop orders).</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="inlineStr"/>
+          <t>Carrier / shipping method — core to fulfilment; must be selectable per order.</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create, update</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>billingAddress.email</t>
+          <t>fulfillmentPolicy.partialShipping</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Email search is a standard use-case for shop orders — often the only identifier support has.</t>
+          <t>Partial-shipping policy has no upstream slot — the read reports a hardcoded "allowed". Needs a real v3 field before it can be written or trusted.</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr"/>
@@ -8278,22 +8278,22 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+          <t>Custom field values carry company-specific data — today only readable via include, not writable via API (all documents).</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr"/>
@@ -8306,12 +8306,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Correcting a sales order number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
+          <t>Companies segment and find orders by their own custom-field values.</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr"/>
@@ -8334,22 +8334,22 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr"/>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -8370,21 +8370,17 @@
           <t>create</t>
         </is>
       </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>The customer's PO number on the delivery note (B2B) — read-only upstream today; must be settable.</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Carrying a delivery note number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -8394,12 +8390,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
@@ -8409,7 +8405,7 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Warehouse/support find a delivery note by the customer's PO number.</t>
+          <t>Reassign the delivery note's partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr"/>
@@ -8422,25 +8418,29 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>The picking/shipping warehouse — must be selectable per delivery note, not fixed to the default.</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="inlineStr"/>
+          <t>The customer's PO number on the delivery note (B2B) — read-only upstream today; must be settable.</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>customs.incoterm</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Incoterm for export shipments — a customs-declaration essential, not settable via API today.</t>
+          <t>Warehouse/support find a delivery note by the customer's PO number.</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr"/>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>customs.totalWeight</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Total shipment weight for the customs declaration / carrier — needs to be settable.</t>
+          <t>The picking/shipping warehouse — must be selectable per delivery note, not fixed to the default.</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr"/>
@@ -8506,12 +8506,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>customs.note</t>
+          <t>billingAddress.zip</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Customs note for export paperwork.</t>
+          <t>Postal-code search — standard phone use-case for delivery lookups.</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr"/>
@@ -8534,12 +8534,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the delivery note — today only readable via include, not writable via API.</t>
+          <t>Adjust delivered positions/quantities after creation — the v3 update DTO carries no line-item write path.</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr"/>
@@ -8562,12 +8562,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>shipments</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>Reassign the delivery note's partner after creation — v3 accepts it only on create.</t>
+          <t>Tracking numbers need a nachlade GET /v1/deliveryNotes/{id}/shipments — not yet composed into the read payload.</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr"/>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>customs.totalWeight</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Adjust delivered positions/quantities after creation — the v3 update DTO carries no line-item write path.</t>
+          <t>Total shipment weight for the customs declaration / carrier — needs to be settable.</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr"/>
@@ -8618,12 +8618,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>shipments</t>
+          <t>customs.incoterm</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Tracking numbers need a nachlade GET /v1/deliveryNotes/{id}/shipments — not yet composed into the read payload.</t>
+          <t>Incoterm for export shipments — a customs-declaration essential, not settable via API today.</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr"/>
@@ -8646,12 +8646,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>billingAddress.zip</t>
+          <t>customs.note</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Postal-code search — standard phone use-case for delivery lookups.</t>
+          <t>Customs note for export paperwork.</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr"/>
@@ -8674,12 +8674,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Carrying a delivery note number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+          <t>Custom field values on the delivery note — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr"/>
@@ -8730,12 +8730,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>tracking.number</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Support looks up a shipment by tracking number — needs a filterable/searchable upstream list parameter.</t>
+          <t>The shipment lifecycle status is not exposed by v1 shipments — only sentAt exists.</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr"/>
@@ -8758,7 +8758,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>The shipment lifecycle status is not exposed by v1 shipments — only sentAt exists.</t>
+          <t>Package weight is not exposed by v1 shipments.</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr"/>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>events</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Package weight is not exposed by v1 shipments.</t>
+          <t>Carrier tracking events are not exposed — needs a carrier-events feed.</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr"/>
@@ -8814,12 +8814,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>events</t>
+          <t>tracking.number</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Carrier tracking events are not exposed — needs a carrier-events feed.</t>
+          <t>Support looks up a shipment by tracking number — needs a filterable/searchable upstream list parameter.</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr"/>
@@ -8842,29 +8842,25 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>The customer's PO number on the invoice (B2B) — read-only upstream today; must be settable and correctable.</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Correcting a invoice number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -8874,12 +8870,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
@@ -8889,7 +8885,7 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Support and accounting find invoices by the customer's PO number.</t>
+          <t>Reassign the invoice's partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr"/>
@@ -8902,25 +8898,29 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>references.debtorAccountNumber</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Deviating debtor account for the FiBu/DATEV export — settable when it differs from the customer default.</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="inlineStr"/>
+          <t>The customer's PO number on the invoice (B2B) — read-only upstream today; must be settable and correctable.</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>payment.method</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Payment method on the invoice — central to order-to-cash; frequently overridden.</t>
+          <t>Support and accounting find invoices by the customer's PO number.</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr"/>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>payment.terms.dueDays</t>
+          <t>references.debtorAccountNumber</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Net payment term in days — drives the due date and dunning.</t>
+          <t>Deviating debtor account for the FiBu/DATEV export — settable when it differs from the customer default.</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr"/>
@@ -8986,12 +8986,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>payment.terms.discountPercent</t>
+          <t>billingAddress.email</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Cash-discount percentage — standard DACH B2B.</t>
+          <t>Email search — standard use-case for finding a customer's invoices.</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr"/>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>payment.terms.discountDays</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Cash-discount period in days — pairs with the discount.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr"/>
@@ -9042,12 +9042,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>dunning.blocked</t>
+          <t>totals.outstanding</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
@@ -9057,12 +9057,12 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Block/unblock dunning per invoice — a core AR control not writable upstream today.</t>
+          <t>Exact open amount needs readable payment↔invoice allocations (docs/05 #2); today only derived from paymentStatus.</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>Schema deklariert: update</t>
+          <t>live bewiesen für: read</t>
         </is>
       </c>
     </row>
@@ -9074,29 +9074,25 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>dunning.note</t>
+          <t>payment.method</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>A dunning note for the AR clerk — must be writable.</t>
-        </is>
-      </c>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: update</t>
-        </is>
-      </c>
+          <t>Payment method on the invoice — central to order-to-cash; frequently overridden.</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -9106,7 +9102,7 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>payment.terms.dueDays</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -9121,7 +9117,7 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the invoice — today only readable via include, not writable via API.</t>
+          <t>Net payment term in days — drives the due date and dunning.</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr"/>
@@ -9134,12 +9130,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>payment.terms.discountPercent</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -9149,7 +9145,7 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Reassign the invoice's partner after creation — v3 accepts it only on create.</t>
+          <t>Cash-discount percentage — standard DACH B2B.</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr"/>
@@ -9162,29 +9158,25 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>eInvoice</t>
+          <t>payment.terms.discountDays</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D81" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>The finished ZUGFeRD/XRechnung artefact + delivery status is a missing upstream API (docs/05 #7) — only XML raw data exists today.</t>
-        </is>
-      </c>
-      <c r="F81" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>Cash-discount period in days — pairs with the discount.</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -9194,12 +9186,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>totals.outstanding</t>
+          <t>dunning.blocked</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
@@ -9209,12 +9201,12 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Exact open amount needs readable payment↔invoice allocations (docs/05 #2); today only derived from paymentStatus.</t>
+          <t>Block/unblock dunning per invoice — a core AR control not writable upstream today.</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>live bewiesen für: read</t>
+          <t>Schema deklariert: update</t>
         </is>
       </c>
     </row>
@@ -9226,25 +9218,29 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>billingAddress.email</t>
+          <t>dunning.note</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>search</t>
-        </is>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Email search — standard use-case for finding a customer's invoices.</t>
-        </is>
-      </c>
-      <c r="F83" s="8" t="inlineStr"/>
+          <t>A dunning note for the AR clerk — must be writable.</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: update</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -9254,7 +9250,7 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>eInvoice</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
@@ -9262,17 +9258,21 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D84" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="inlineStr"/>
+          <t>The finished ZUGFeRD/XRechnung artefact + delivery status is a missing upstream API (docs/05 #7) — only XML raw data exists today.</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -9282,12 +9282,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Correcting a invoice number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
+          <t>Custom field values on the invoice — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr"/>
@@ -9310,22 +9310,22 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr"/>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>allocations</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Payment↔invoice allocations (n:m) are neither readable nor writable — without them exact outstanding amounts are impossible (docs/05 #2).</t>
+          <t>Payout/settlement aggregation (fees, chargebacks) per provider needs docs/05 #8.</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr"/>
@@ -9394,12 +9394,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>allocations</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>read, update</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Payout/settlement aggregation (fees, chargebacks) per provider needs docs/05 #8.</t>
+          <t>Payment↔invoice allocations (n:m) are neither readable nor writable — without them exact outstanding amounts are impossible (docs/05 #2).</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr"/>
@@ -9422,12 +9422,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>references.rmaNumber</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>The RMA number the customer quotes — no upstream field today; core to returns handling.</t>
+          <t>Carrying a return number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr"/>
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>references.rmaNumber</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Support finds a return by the RMA number the customer has.</t>
+          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr"/>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>references.rmaNumber</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>The customer's PO number on the return — read-only upstream today.</t>
+          <t>The RMA number the customer quotes — no upstream field today; core to returns handling.</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr"/>
@@ -9506,29 +9506,25 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>items.reason</t>
+          <t>references.rmaNumber</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D93" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>search</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>The return reason per line — essential for returns analytics; not settable via API today.</t>
-        </is>
-      </c>
-      <c r="F93" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Support finds a return by the RMA number the customer has.</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -9538,7 +9534,7 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>items.condition</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
@@ -9553,7 +9549,7 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Item condition (resellable/damaged/disposal) drives restocking — not in the v3 payload yet.</t>
+          <t>The customer's PO number on the return — read-only upstream today.</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr"/>
@@ -9566,7 +9562,7 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>items.action</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -9581,7 +9577,7 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Resolution per line (credit/replace/repair) — not in the v3 payload yet.</t>
+          <t>The returns warehouse must be selectable per return.</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr"/>
@@ -9594,12 +9590,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
@@ -9609,7 +9605,7 @@
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>The returns warehouse must be selectable per return.</t>
+          <t>Edit return positions after creation — the v3 update DTO carries no line-item write path.</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr"/>
@@ -9622,7 +9618,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>items.reason</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -9630,17 +9626,21 @@
           <t>create, update</t>
         </is>
       </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the return — today only readable via include, not writable via API.</t>
-        </is>
-      </c>
-      <c r="F97" s="8" t="inlineStr"/>
+          <t>The return reason per line — essential for returns analytics; not settable via API today.</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>items.condition</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
+          <t>Item condition (resellable/damaged/disposal) drives restocking — not in the v3 payload yet.</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr"/>
@@ -9678,12 +9678,12 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>items.condition</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Edit return positions after creation — the v3 update DTO carries no line-item write path.</t>
+          <t>Item condition is not surfaced by the v3 return payload yet (docs/05 #4 batch/trace family).</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr"/>
@@ -9706,12 +9706,12 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>items.condition</t>
+          <t>items.action</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Item condition is not surfaced by the v3 return payload yet (docs/05 #4 batch/trace family).</t>
+          <t>Resolution per line (credit/replace/repair) — not in the v3 payload yet.</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr"/>
@@ -9734,12 +9734,12 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Carrying a return number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+          <t>Custom field values on the return — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr"/>
@@ -9762,29 +9762,25 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="D102" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>The customer's PO number on the credit note (B2B) — read-only upstream today.</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Correcting a credit note number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
@@ -9794,12 +9790,12 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>references.debtorAccountNumber</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
@@ -9809,7 +9805,7 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Deviating debtor account for the FiBu/DATEV export of the credit note.</t>
+          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr"/>
@@ -9822,25 +9818,29 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>dates.serviceDate</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D104" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Leistungsdatum — a §14 UStG mandatory field on the credit note; must be settable.</t>
-        </is>
-      </c>
-      <c r="F104" s="8" t="inlineStr"/>
+          <t>The customer's PO number on the credit note (B2B) — read-only upstream today.</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>settlement.mode</t>
+          <t>references.debtorAccountNumber</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Refund vs offset-against-invoice is a per-credit-note decision — not settable upstream today.</t>
+          <t>Deviating debtor account for the FiBu/DATEV export of the credit note.</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr"/>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>dates.serviceDate</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the credit note — today only readable via include, not writable via API.</t>
+          <t>Leistungsdatum — a §14 UStG mandatory field on the credit note; must be settable.</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr"/>
@@ -9906,12 +9906,12 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr"/>
@@ -9966,22 +9966,22 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>settlement.mode</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D109" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+          <t>Refund vs offset-against-invoice is a per-credit-note decision — not settable upstream today.</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr"/>
@@ -9994,12 +9994,12 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Correcting a credit note number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
+          <t>Custom field values on the credit note — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F110" s="8" t="inlineStr"/>
@@ -10022,22 +10022,22 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr"/>
@@ -10050,29 +10050,25 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>addresses.isDefault</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D112" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>read, update</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Mark the standard address per type (unified-address model; at most one default per customer &amp; type) — v3 partner addresses carry no isDefault flag.</t>
-        </is>
-      </c>
-      <c r="F112" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read · Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Active/archived state is not exposed via v3 suppliers — needed for honest archiving (plan §6.1).</t>
+        </is>
+      </c>
+      <c r="F112" s="8" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
@@ -10082,29 +10078,25 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>addresses.label</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D113" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>read, update</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Free label/name per address location (e.g. 'Lager München') — v3 knows only billing/shipping roles, no named locations.</t>
-        </is>
-      </c>
-      <c r="F113" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read · Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>B2B hierarchy (branch → HQ) is not exposed via the public API (plan §6.1 parent).</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
@@ -10114,29 +10106,25 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>addresses.type</t>
+          <t>billTo</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D114" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>read, update</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Set the address role incl. the 'both' value (one address serving billing AND shipping) — v3 splits billing (primaryAddress/deviating) vs shipping (deliveryAddresses) by store, so the role is not a freely settable field.</t>
-        </is>
-      </c>
-      <c r="F114" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Central billing (Zentralregulierung — invoice to association/HQ) is not exposed (plan §6.1 billTo).</t>
+        </is>
+      </c>
+      <c r="F114" s="8" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
@@ -10146,22 +10134,22 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>contacts.address</t>
+          <t>channels</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D115" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Bind a contact person to a specific address (person-at-location) — v3 stores only a free-text contactPerson on delivery addresses, not a reference.</t>
+          <t>Per-channel external ids (channel links) are not exposed via the public API.</t>
         </is>
       </c>
       <c r="F115" s="8" t="inlineStr"/>
@@ -10174,22 +10162,22 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>contacts.isPrimary</t>
+          <t>purchasing.confirmationRequired</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D116" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Mark the main contact person — v3 contactPersons carry no primary flag.</t>
+          <t>Whether an order confirmation (AB) is required from this supplier — drives purchasing workflow; not settable via API today.</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr"/>
@@ -10202,7 +10190,7 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>purchasing.confirmationRequired</t>
+          <t>purchasing.sendOrdersVia</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -10217,7 +10205,7 @@
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Whether an order confirmation (AB) is required from this supplier — drives purchasing workflow; not settable via API today.</t>
+          <t>How POs are sent to the supplier (email/portal/EDI) — a supplier default that must be settable.</t>
         </is>
       </c>
       <c r="F117" s="8" t="inlineStr"/>
@@ -10230,7 +10218,7 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>purchasing.sendOrdersVia</t>
+          <t>purchasing.deliveryDays</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
@@ -10245,7 +10233,7 @@
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>How POs are sent to the supplier (email/portal/EDI) — a supplier default that must be settable.</t>
+          <t>Standard supplier lead time in days — feeds replenishment planning.</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr"/>
@@ -10258,7 +10246,7 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>purchasing.deliveryDays</t>
+          <t>addresses.type</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
@@ -10266,17 +10254,21 @@
           <t>create, update</t>
         </is>
       </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Standard supplier lead time in days — feeds replenishment planning.</t>
-        </is>
-      </c>
-      <c r="F119" s="8" t="inlineStr"/>
+          <t>Set the address role incl. the 'both' value (one address serving billing AND shipping) — v3 splits billing (primaryAddress/deviating) vs shipping (deliveryAddresses) by store, so the role is not a freely settable field.</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create, update</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -10286,25 +10278,29 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>defaults.paymentTerms.dueDays</t>
+          <t>addresses.label</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D120" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Default supplier payment term — drives liability due dates.</t>
-        </is>
-      </c>
-      <c r="F120" s="8" t="inlineStr"/>
+          <t>Free label/name per address location (e.g. 'Lager München') — v3 knows only billing/shipping roles, no named locations.</t>
+        </is>
+      </c>
+      <c r="F120" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read · Schema deklariert: create, update</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
@@ -10314,25 +10310,29 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>finance.creditorAccountNumber</t>
+          <t>addresses.isDefault</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>The creditor account for the FiBu/DATEV export — settable per supplier.</t>
-        </is>
-      </c>
-      <c r="F121" s="8" t="inlineStr"/>
+          <t>Mark the standard address per type (unified-address model; at most one default per customer &amp; type) — v3 partner addresses carry no isDefault flag.</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read · Schema deklariert: create, update</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>finance.openAmount</t>
+          <t>defaults.shippingMethod</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>read, update</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Aggregated open liabilities per supplier are computed nowhere in the API — must be derived/served.</t>
+          <t>The default shipping method is not surfaced by the v3 partner read.</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr"/>
@@ -10370,12 +10370,12 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>defaults.priceList</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, update</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the supplier — today only readable, not writable via API.</t>
+          <t>The assigned price list is not surfaced by the v3 partner read.</t>
         </is>
       </c>
       <c r="F123" s="8" t="inlineStr"/>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>defaults.partialShipping</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Active/archived state is not exposed via v3 suppliers — needed for honest archiving (plan §6.1).</t>
+          <t>The partial-shipping preference is not surfaced by the v3 partner read.</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr"/>
@@ -10426,12 +10426,12 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>defaults.paymentTerms.dueDays</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>B2B hierarchy (branch → HQ) is not exposed via the public API (plan §6.1 parent).</t>
+          <t>Default supplier payment term — drives liability due dates.</t>
         </is>
       </c>
       <c r="F125" s="8" t="inlineStr"/>
@@ -10454,12 +10454,12 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>billTo</t>
+          <t>finance.openAmount</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Central billing (Zentralregulierung — invoice to association/HQ) is not exposed (plan §6.1 billTo).</t>
+          <t>Aggregated open liabilities per supplier are computed nowhere in the API — must be derived/served.</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr"/>
@@ -10482,12 +10482,12 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>channels</t>
+          <t>finance.creditorAccountNumber</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Per-channel external ids (channel links) are not exposed via the public API.</t>
+          <t>The creditor account for the FiBu/DATEV export — settable per supplier.</t>
         </is>
       </c>
       <c r="F127" s="8" t="inlineStr"/>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>defaults.shippingMethod</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>The default shipping method is not surfaced by the v3 partner read.</t>
+          <t>Custom field values on the supplier — today only readable, not writable via API.</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr"/>
@@ -10538,22 +10538,22 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>defaults.priceList</t>
+          <t>contacts.address</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
-        </is>
-      </c>
-      <c r="D129" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>The assigned price list is not surfaced by the v3 partner read.</t>
+          <t>Bind a contact person to a specific address (person-at-location) — v3 stores only a free-text contactPerson on delivery addresses, not a reference.</t>
         </is>
       </c>
       <c r="F129" s="8" t="inlineStr"/>
@@ -10566,22 +10566,22 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>defaults.partialShipping</t>
+          <t>contacts.isPrimary</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
-        </is>
-      </c>
-      <c r="D130" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>The partial-shipping preference is not surfaced by the v3 partner read.</t>
+          <t>Mark the main contact person — v3 contactPersons carry no primary flag.</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr"/>
@@ -10594,12 +10594,12 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>references.supplierOfferNumber</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>The supplier's quote number we ordered against — read-only upstream today.</t>
+          <t>Carrying a purchase order number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
         </is>
       </c>
       <c r="F131" s="8" t="inlineStr"/>
@@ -10622,12 +10622,12 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>references.ourCustomerNumber</t>
+          <t>supplier</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Our customer number at the supplier — belongs on the PO, not settable via API today.</t>
+          <t>Reassign the PO's supplier after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr"/>
@@ -10650,12 +10650,12 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>confirmation.supplierOrderNumber</t>
+          <t>references.ourCustomerNumber</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>The AB (order-confirmation) number from the supplier — the whole confirmation block is read-only upstream (docs/05: AB handling).</t>
+          <t>Our customer number at the supplier — belongs on the PO, not settable via API today.</t>
         </is>
       </c>
       <c r="F133" s="8" t="inlineStr"/>
@@ -10678,12 +10678,12 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>confirmation.status</t>
+          <t>references.supplierOfferNumber</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
@@ -10693,7 +10693,7 @@
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Recording the confirmation status (pending/confirmed/deviating) is core purchasing — not writable via API today.</t>
+          <t>The supplier's quote number we ordered against — read-only upstream today.</t>
         </is>
       </c>
       <c r="F134" s="8" t="inlineStr"/>
@@ -10706,12 +10706,12 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>dates.requestedDelivery</t>
+          <t>confirmation.status</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Requested delivery date at the supplier — not writable upstream today.</t>
+          <t>Recording the confirmation status (pending/confirmed/deviating) is core purchasing — not writable via API today.</t>
         </is>
       </c>
       <c r="F135" s="8" t="inlineStr"/>
@@ -10734,12 +10734,12 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>confirmation.supplierOrderNumber</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>The receiving warehouse for the PO must be selectable.</t>
+          <t>The AB (order-confirmation) number from the supplier — the whole confirmation block is read-only upstream (docs/05: AB handling).</t>
         </is>
       </c>
       <c r="F136" s="8" t="inlineStr"/>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>dates.requestedDelivery</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the PO — today only readable via include, not writable via API.</t>
+          <t>Requested delivery date at the supplier — not writable upstream today.</t>
         </is>
       </c>
       <c r="F137" s="8" t="inlineStr"/>
@@ -10790,12 +10790,12 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>supplier</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>Reassign the PO's supplier after creation — v3 accepts it only on create.</t>
+          <t>The receiving warehouse for the PO must be selectable.</t>
         </is>
       </c>
       <c r="F138" s="8" t="inlineStr"/>
@@ -10846,12 +10846,12 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>dropship</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>read, create</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Dropshipping (Strecke: salesOrder link + customer delivery address) is not exposed via v3 purchaseOrders.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F140" s="8" t="inlineStr"/>
@@ -10874,12 +10874,12 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>dropship</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read, create</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Carrying a purchase order number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+          <t>Dropshipping (Strecke: salesOrder link + customer delivery address) is not exposed via v3 purchaseOrders.</t>
         </is>
       </c>
       <c r="F141" s="8" t="inlineStr"/>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Custom field values on the PO — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr"/>
@@ -10930,12 +10930,12 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>references.supplierDeliveryNoteNumber</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update, read</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Cancel/storno of a posted goods receipt — the remaining upstream gap after the BF entity list covered browsing (docs/05 #9 revised).</t>
+          <t>The supplier's delivery-note number on the goods receipt — needed for the three-way match; not in the BF record yet.</t>
         </is>
       </c>
       <c r="F143" s="8" t="inlineStr"/>
@@ -10958,12 +10958,12 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>references.supplierDeliveryNoteNumber</t>
+          <t>dates.received</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>create, update, read</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>The supplier's delivery-note number on the goods receipt — needed for the three-way match; not in the BF record yet.</t>
+          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
         </is>
       </c>
       <c r="F144" s="8" t="inlineStr"/>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>dates.posted</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Line items (product × quantity × storage location, quality check per line) are not exposed on the BF goodsReceipt record — creation still goes through the PO action only.</t>
+          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
         </is>
       </c>
       <c r="F145" s="8" t="inlineStr"/>
@@ -11014,12 +11014,12 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>dates.received</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
+          <t>Cancel/storno of a posted goods receipt — the remaining upstream gap after the BF entity list covered browsing (docs/05 #9 revised).</t>
         </is>
       </c>
       <c r="F146" s="8" t="inlineStr"/>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>dates.posted</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>read, create, update</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
+          <t>Line items (product × quantity × storage location, quality check per line) are not exposed on the BF goodsReceipt record — creation still goes through the PO action only.</t>
         </is>
       </c>
       <c r="F147" s="8" t="inlineStr"/>
@@ -11098,12 +11098,12 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>match.status</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D149" s="9" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Re-running/overriding the match verdict via API (rematch) — the check statuses are readable now; a command to re-evaluate is still missing upstream.</t>
+          <t>Filtering incoming invoices by workflow status is the AP daily view — the BF supplierInvoice API does not allow filtering documentStatus today.</t>
         </is>
       </c>
       <c r="F149" s="8" t="inlineStr"/>
@@ -11126,12 +11126,12 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>approval.status</t>
+          <t>dates.invoiceDate</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>sort</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Approve/reject via API: BF process steps (GoodsCheck/InvoiceCheck/Payment) are reported to exist — wiring + live verification of those steps is pending (steps were empty on the test instance's metadata).</t>
+          <t>Sorting incoming invoices by invoice date — dateOfSupplierInvoice is not sortable on the BF API today.</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr"/>
@@ -11154,12 +11154,12 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>match.status</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D151" s="9" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Filtering incoming invoices by workflow status is the AP daily view — the BF supplierInvoice API does not allow filtering documentStatus today.</t>
+          <t>Re-running/overriding the match verdict via API (rematch) — the check statuses are readable now; a command to re-evaluate is still missing upstream.</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr"/>
@@ -11210,12 +11210,12 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>dates.invoiceDate</t>
+          <t>approval.status</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>sort</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D153" s="9" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Sorting incoming invoices by invoice date — dateOfSupplierInvoice is not sortable on the BF API today.</t>
+          <t>Approve/reject via API: BF process steps (GoodsCheck/InvoiceCheck/Payment) are reported to exist — wiring + live verification of those steps is pending (steps were empty on the test instance's metadata).</t>
         </is>
       </c>
       <c r="F153" s="8" t="inlineStr"/>
@@ -11322,29 +11322,25 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>prices.sale</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D157" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>WRITE works — the sale price is composed as a separate salesPrices write on create/update. READ is still blue: the v3 read model does not carry the sale price (needs the salesPrices include parsed), so a written price is not read back.</t>
-        </is>
-      </c>
-      <c r="F157" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>Tagging products (assortment curation, campaigns) — product writes now go through v2, but the v2 tags shape ({id,key,name,color}) is not yet mapped/verified, so tag writes stay blue.</t>
+        </is>
+      </c>
+      <c r="F157" s="8" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
@@ -11354,25 +11350,29 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>tax.profile</t>
+          <t>prices.sale</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D158" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>The 16-account tax matrix consolidated into a referenceable taxProfile (ADR-011) — today only the raw taxAccounts embed exists, not a clean reference.</t>
-        </is>
-      </c>
-      <c r="F158" s="8" t="inlineStr"/>
+          <t>WRITE works — the sale price is composed as a separate salesPrices write on create/update. READ is still blue: the v3 read model does not carry the sale price (needs the salesPrices include parsed), so a written price is not read back.</t>
+        </is>
+      </c>
+      <c r="F158" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
@@ -11382,12 +11382,12 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>logistics.packagingUnits</t>
+          <t>tax.profile</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>create, read, update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D159" s="9" t="inlineStr">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Packaging units (VPE) need the packagingUnits include parsed — not yet mapped.</t>
+          <t>The 16-account tax matrix consolidated into a referenceable taxProfile (ADR-011) — today only the raw taxAccounts embed exists, not a clean reference.</t>
         </is>
       </c>
       <c r="F159" s="8" t="inlineStr"/>
@@ -11410,12 +11410,12 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>stock.incoming</t>
+          <t>logistics.packagingUnits</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, read, update</t>
         </is>
       </c>
       <c r="D160" s="9" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Inbound quantity (ordered but not yet received) is the one stock figure Xentral does not compute: /products/{id}/stocks returns physical, sellable, reserved, correction, pseudo, openSalesOrders, calculated and producible — all mapped — but nothing inbound. The per-warehouse split the same call carries is answered by StockLevel (filter[product], narrowed by warehouse), so it is not duplicated onto the product.</t>
+          <t>Packaging units (VPE) need the packagingUnits include parsed — not yet mapped.</t>
         </is>
       </c>
       <c r="F160" s="8" t="inlineStr"/>
@@ -11438,12 +11438,12 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>suppliers</t>
+          <t>stock.incoming</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D161" s="9" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>The default supplier IS writable (mapped to v2 standardSupplier); multi-supplier sourcing (several suppliers with per-supplier price/number) needs a suppliers include/relation not yet mapped, plus a write path.</t>
+          <t>Inbound quantity (ordered but not yet received) is the one stock figure Xentral does not compute: /products/{id}/stocks returns physical, sellable, reserved, correction, pseudo, openSalesOrders, calculated and producible — all mapped — but nothing inbound. The per-warehouse split the same call carries is answered by StockLevel (filter[product], narrowed by warehouse), so it is not duplicated onto the product.</t>
         </is>
       </c>
       <c r="F161" s="8" t="inlineStr"/>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>suppliers</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Tagging products (assortment curation, campaigns) — product writes now go through v2, but the v2 tags shape ({id,key,name,color}) is not yet mapped/verified, so tag writes stay blue.</t>
+          <t>The default supplier IS writable (mapped to v2 standardSupplier); multi-supplier sourcing (several suppliers with per-supplier price/number) needs a suppliers include/relation not yet mapped, plus a write path.</t>
         </is>
       </c>
       <c r="F162" s="8" t="inlineStr"/>
@@ -11522,12 +11522,12 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>contents.reserved</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D164" s="9" t="inlineStr">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>Location contents are composed from the StockLevel projection now; the reserved portion per location stays unavailable — upstream reports reservations only as a product total.</t>
+          <t>Upstream returns the bin description but rejects it on create and update ("The attribute description is not allowed.") — the field is read-only for every API generation we have. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F164" s="8" t="inlineStr"/>
@@ -11550,12 +11550,12 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>contents.reserved</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D165" s="9" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Upstream returns the bin description but rejects it on create and update ("The attribute description is not allowed.") — the field is read-only for every API generation we have. Measured on mvp 2026-08-02.</t>
+          <t>Location contents are composed from the StockLevel projection now; the reserved portion per location stays unavailable — upstream reports reservations only as a product total.</t>
         </is>
       </c>
       <c r="F165" s="8" t="inlineStr"/>
@@ -11606,12 +11606,12 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>batch</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>read, list</t>
         </is>
       </c>
       <c r="D167" s="9" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>No per-location reservation is exposed upstream; /v1/products/{id}/stocks reports reserved only as a product TOTAL. The projection reports quantity and leaves reserved/available blank rather than spreading a total over locations.</t>
+          <t>The batch split exists on the v2 items path (qualityControlAttributes) but not on /v1/products/{id}/storageLocations. Emitting batch rows on one anchor only would make the grain depend on the filter, so the projection stays product × storage location. A unified GET /v3/stockLevels is the clean ask (docs/05 #18).</t>
         </is>
       </c>
       <c r="F167" s="8" t="inlineStr"/>
@@ -11634,12 +11634,12 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D168" s="9" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>Same gap as reserved: available = quantity - reserved is only derivable per product, not per storage location.</t>
+          <t>The list needs an anchor filter (product or storageLocation): upstream has no global stock collection, so an unanchored query would mean fanning out over every product of the tenant.</t>
         </is>
       </c>
       <c r="F168" s="8" t="inlineStr"/>
@@ -11662,12 +11662,12 @@
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>batch</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>read, list</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D169" s="9" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>The batch split exists on the v2 items path (qualityControlAttributes) but not on /v1/products/{id}/storageLocations. Emitting batch rows on one anchor only would make the grain depend on the filter, so the projection stays product × storage location. A unified GET /v3/stockLevels is the clean ask (docs/05 #18).</t>
+          <t>No per-location reservation is exposed upstream; /v1/products/{id}/stocks reports reserved only as a product TOTAL. The projection reports quantity and leaves reserved/available blank rather than spreading a total over locations.</t>
         </is>
       </c>
       <c r="F169" s="8" t="inlineStr"/>
@@ -11690,12 +11690,12 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D170" s="9" t="inlineStr">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>The list needs an anchor filter (product or storageLocation): upstream has no global stock collection, so an unanchored query would mean fanning out over every product of the tenant.</t>
+          <t>Same gap as reserved: available = quantity - reserved is only derivable per product, not per storage location.</t>
         </is>
       </c>
       <c r="F170" s="8" t="inlineStr"/>
@@ -11746,12 +11746,12 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>unitCost</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D172" s="9" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
+          <t>A booking returns no identity: the v1 storage-item endpoints answer 201 with an empty body and — contrary to their own spec — send no Location header (verified on mvp 2026-07-31). Without an id a repeated booking cannot be recognised afterwards, which is why correction+setQuantityTo is the only retry-safe write. The ask: return the specced Location header, or the created movement.</t>
         </is>
       </c>
       <c r="F172" s="8" t="inlineStr"/>
@@ -11774,12 +11774,12 @@
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>unitCost</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D173" s="9" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>A booking returns no identity: the v1 storage-item endpoints answer 201 with an empty body and — contrary to their own spec — send no Location header (verified on mvp 2026-07-31). Without an id a repeated booking cannot be recognised afterwards, which is why correction+setQuantityTo is the only retry-safe write. The ask: return the specced Location header, or the created movement.</t>
+          <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
         </is>
       </c>
       <c r="F173" s="8" t="inlineStr"/>
@@ -11802,12 +11802,12 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>positions</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D174" s="9" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Counting positions (expected/counted/difference with values) live in the counting-list reports — not composed into the API payload yet; needed for the GoBD difference review.</t>
+          <t>Starting a stock take via API (scope: warehouse/locations/products, key date) — the v1 inventory endpoints exist but the write orchestration is not built yet.</t>
         </is>
       </c>
       <c r="F174" s="8" t="inlineStr"/>
@@ -11830,12 +11830,12 @@
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>dates.keyDate</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D175" s="9" t="inlineStr">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Starting a stock take via API (scope: warehouse/locations/products, key date) — the v1 inventory endpoints exist but the write orchestration is not built yet.</t>
+          <t>The inventory key date (Stichtag) is not exposed by v1 inventoryRuns.</t>
         </is>
       </c>
       <c r="F175" s="8" t="inlineStr"/>
@@ -11858,12 +11858,12 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>positions.counted</t>
+          <t>dates.posted</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D176" s="9" t="inlineStr">
@@ -11873,7 +11873,7 @@
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Submitting counted quantities via API (mobile counting) — needed for headless inventory.</t>
+          <t>The posted timestamp is not exposed by v1 inventoryRuns.</t>
         </is>
       </c>
       <c r="F176" s="8" t="inlineStr"/>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>documents.stockMovements</t>
+          <t>totals</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
@@ -11894,17 +11894,21 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D177" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D177" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Posted correction movements per stock take need the stockMovements API (docs/05 #1) to be traceable.</t>
-        </is>
-      </c>
-      <c r="F177" s="8" t="inlineStr"/>
+          <t>Position/difference totals are not exposed by v1 inventoryRuns.</t>
+        </is>
+      </c>
+      <c r="F177" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
@@ -11914,7 +11918,7 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>dates.keyDate</t>
+          <t>positions</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
@@ -11929,7 +11933,7 @@
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>The inventory key date (Stichtag) is not exposed by v1 inventoryRuns.</t>
+          <t>Counting positions (expected/counted/difference with values) live in the counting-list reports — not composed into the API payload yet; needed for the GoBD difference review.</t>
         </is>
       </c>
       <c r="F178" s="8" t="inlineStr"/>
@@ -11942,12 +11946,12 @@
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>dates.posted</t>
+          <t>positions.counted</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D179" s="9" t="inlineStr">
@@ -11957,7 +11961,7 @@
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>The posted timestamp is not exposed by v1 inventoryRuns.</t>
+          <t>Submitting counted quantities via API (mobile counting) — needed for headless inventory.</t>
         </is>
       </c>
       <c r="F179" s="8" t="inlineStr"/>
@@ -11970,7 +11974,7 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>totals</t>
+          <t>documents.stockMovements</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
@@ -11978,21 +11982,17 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D180" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+      <c r="D180" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Position/difference totals are not exposed by v1 inventoryRuns.</t>
-        </is>
-      </c>
-      <c r="F180" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>Posted correction movements per stock take need the stockMovements API (docs/05 #1) to be traceable.</t>
+        </is>
+      </c>
+      <c r="F180" s="8" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>tasks</t>
+          <t>criteria</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Task-level detail (location, product, quantity, status per pick) is not exposed on the pickLists API — needed for progress boards and pick-path optimisation.</t>
+          <t>Pick-run criteria (channel, shipping method) are not exposed by v1 pickLists.</t>
         </is>
       </c>
       <c r="F182" s="8" t="inlineStr"/>
@@ -12058,12 +12058,12 @@
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>tasks.status</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D183" s="9" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Granular task-level pick confirmation with quantity + scans (docs/05 #3) — today only whole-list start/complete exists.</t>
+          <t>The picked sales orders are not exposed by v1 pickLists (only counts).</t>
         </is>
       </c>
       <c r="F183" s="8" t="inlineStr"/>
@@ -12086,12 +12086,12 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>strategy</t>
+          <t>containers</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D184" s="9" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>Choosing the picking strategy (single/multiOrder/wave/zone) at creation — no create endpoint today.</t>
+          <t>Totes/containers are not exposed by v1 pickLists.</t>
         </is>
       </c>
       <c r="F184" s="8" t="inlineStr"/>
@@ -12114,12 +12114,12 @@
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>criteria</t>
+          <t>strategy</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D185" s="9" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Pick-run criteria (channel, shipping method) are not exposed by v1 pickLists.</t>
+          <t>Choosing the picking strategy (single/multiOrder/wave/zone) at creation — no create endpoint today.</t>
         </is>
       </c>
       <c r="F185" s="8" t="inlineStr"/>
@@ -12142,7 +12142,7 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>tasks</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>The picked sales orders are not exposed by v1 pickLists (only counts).</t>
+          <t>Task-level detail (location, product, quantity, status per pick) is not exposed on the pickLists API — needed for progress boards and pick-path optimisation.</t>
         </is>
       </c>
       <c r="F186" s="8" t="inlineStr"/>
@@ -12170,12 +12170,12 @@
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>containers</t>
+          <t>tasks.status</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D187" s="9" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Totes/containers are not exposed by v1 pickLists.</t>
+          <t>Granular task-level pick confirmation with quantity + scans (docs/05 #3) — today only whole-list start/complete exists.</t>
         </is>
       </c>
       <c r="F187" s="8" t="inlineStr"/>
@@ -12226,12 +12226,12 @@
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>trace</t>
+          <t>bestBefore</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D189" s="9" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Batch trace (which goods receipts brought it in, which delivery notes shipped it — recall scenario) has no API at all (docs/05 #4).</t>
+          <t>Correcting a best-before date via API — internal web routes only today.</t>
         </is>
       </c>
       <c r="F189" s="8" t="inlineStr"/>
@@ -12282,12 +12282,12 @@
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>bestBefore</t>
+          <t>trace</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D191" s="9" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Correcting a best-before date via API — internal web routes only today.</t>
+          <t>Batch trace (which goods receipts brought it in, which delivery notes shipped it — recall scenario) has no API at all (docs/05 #4).</t>
         </is>
       </c>
       <c r="F191" s="8" t="inlineStr"/>
@@ -12310,7 +12310,7 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>sync</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>Channel sync-run status (last run, success/failure) is not exposed — needed to monitor shop imports (docs/05 #17, still open after the BF salesChannel entity covered the list).</t>
+          <t>The platform kind (shopify/amazon/…) is not exposed — the BF salesChannel entity carries only a name (05 #17).</t>
         </is>
       </c>
       <c r="F192" s="8" t="inlineStr">
@@ -12342,25 +12342,29 @@
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>defaults</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D193" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D193" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>The channel type (shop/marketplace/direct/pos) is not on the BF salesChannel record — needed for channel-specific routing.</t>
-        </is>
-      </c>
-      <c r="F193" s="8" t="inlineStr"/>
+          <t>Channel defaults (price list, warehouse) are not exposed (05 #17).</t>
+        </is>
+      </c>
+      <c r="F193" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
@@ -12370,29 +12374,25 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D194" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
         <is>
-          <t>Enable/disable state is not on the BF salesChannel record.</t>
-        </is>
-      </c>
-      <c r="F194" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>REVISED (docs/05 #17): BF salesChannel has CRUD — our facade write-mapping + live verification is pending.</t>
+        </is>
+      </c>
+      <c r="F194" s="8" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, create, update</t>
         </is>
       </c>
       <c r="D195" s="9" t="inlineStr">
@@ -12417,7 +12417,7 @@
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>REVISED (docs/05 #17): BF salesChannel has CRUD — our facade write-mapping + live verification is pending.</t>
+          <t>The channel type (shop/marketplace/direct/pos) is not on the BF salesChannel record — needed for channel-specific routing.</t>
         </is>
       </c>
       <c r="F195" s="8" t="inlineStr"/>
@@ -12430,12 +12430,12 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>read, create, update</t>
         </is>
       </c>
       <c r="D196" s="10" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>The platform kind (shopify/amazon/…) is not exposed — the BF salesChannel entity carries only a name (05 #17).</t>
+          <t>Enable/disable state is not on the BF salesChannel record.</t>
         </is>
       </c>
       <c r="F196" s="8" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>defaults</t>
+          <t>sync</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Channel defaults (price list, warehouse) are not exposed (05 #17).</t>
+          <t>Channel sync-run status (last run, success/failure) is not exposed — needed to monitor shop imports (docs/05 #17, still open after the BF salesChannel entity covered the list).</t>
         </is>
       </c>
       <c r="F197" s="8" t="inlineStr">
@@ -12522,22 +12522,22 @@
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>timeline</t>
+          <t>dates.completed</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D199" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D199" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>The task's comment thread. Declared `readWrite` with a full sub-node and returned by NO read — not the list, not the single read, and no include/expand parameter produces it. Not modelled until it reads back.</t>
+          <t>Completing a task through the API does not stamp its completion date: `status: completed` persists, `completionDate` stays null.</t>
         </is>
       </c>
       <c r="F199" s="8" t="inlineStr"/>
@@ -12550,22 +12550,22 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>dates.completed</t>
+          <t>timeline</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D200" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D200" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E200" s="8" t="inlineStr">
         <is>
-          <t>Completing a task through the API does not stamp its completion date: `status: completed` persists, `completionDate` stays null.</t>
+          <t>The task's comment thread. Declared `readWrite` with a full sub-node and returned by NO read — not the list, not the single read, and no include/expand parameter produces it. Not modelled until it reads back.</t>
         </is>
       </c>
       <c r="F200" s="8" t="inlineStr"/>

--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Messlauf: 2026-08-05T08:07:28+00:00</t>
+          <t>Messlauf: 2026-08-08T15:46:22+00:00</t>
         </is>
       </c>
     </row>
@@ -7998,9 +7998,9 @@
           <t>search</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -8008,7 +8008,11 @@
           <t>On the phone the customer quotes their PO number, not the ERP number — the full-text search must reach it.</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr"/>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: search</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -8054,9 +8058,9 @@
           <t>search</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -8064,7 +8068,11 @@
           <t>Support finds shop orders by the SHOP number the customer has.</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr"/>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: search</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -8114,9 +8122,9 @@
           <t>search</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -8124,7 +8132,11 @@
           <t>Postal-code search is a standard phone use-case (shop orders).</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: search</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -8142,9 +8154,9 @@
           <t>search</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -8152,7 +8164,11 @@
           <t>Email search is a standard use-case for shop orders — often the only identifier support has.</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr"/>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: search</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -8514,9 +8530,9 @@
           <t>search</t>
         </is>
       </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
@@ -8524,7 +8540,11 @@
           <t>Postal-code search — standard phone use-case for delivery lookups.</t>
         </is>
       </c>
-      <c r="F58" s="8" t="inlineStr"/>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: search</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -8994,9 +9014,9 @@
           <t>search</t>
         </is>
       </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -9004,7 +9024,11 @@
           <t>Email search — standard use-case for finding a customer's invoices.</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr"/>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: search</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -9206,7 +9230,7 @@
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>Schema deklariert: update</t>
+          <t>live bewiesen für: update · Schema deklariert: update</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9262,7 @@
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>Schema deklariert: update</t>
+          <t>live bewiesen für: update · Schema deklariert: update</t>
         </is>
       </c>
     </row>
@@ -11358,9 +11382,9 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D158" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+      <c r="D158" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
@@ -11368,11 +11392,7 @@
           <t>WRITE works — the sale price is composed as a separate salesPrices write on create/update. READ is still blue: the v3 read model does not carry the sale price (needs the salesPrices include parsed), so a written price is not read back.</t>
         </is>
       </c>
-      <c r="F158" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+      <c r="F158" s="8" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">

--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Übersicht'!$A$6:$H$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fähigkeiten'!$A$1:$F$181</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Felder'!$A$1:$F$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Felder'!$A$1:$F$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -650,7 +650,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F200"/>
+  <dimension ref="A1:F192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>references.externalId</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -7998,21 +7998,17 @@
           <t>search</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>On the phone the customer quotes their PO number, not the ERP number — the full-text search must reach it.</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: search</t>
-        </is>
-      </c>
+          <t>Automated reconciliation matches by the external id.</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -8022,25 +8018,29 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>references.externalId</t>
+          <t>dates.requestedDelivery</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>search</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Automated reconciliation matches by the external id.</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr"/>
+          <t>Desired delivery date — core fulfilment field; one of the first things entered on an order. Not writable upstream today.</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: update</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -8050,29 +8050,25 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>references.externalNumber</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>search</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Support finds shop orders by the SHOP number the customer has.</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: search</t>
-        </is>
-      </c>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -8082,12 +8078,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>dates.requestedDelivery</t>
+          <t>shipping.method</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
@@ -8097,12 +8093,12 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Desired delivery date — core fulfilment field; one of the first things entered on an order. Not writable upstream today.</t>
+          <t>Carrier / shipping method — core to fulfilment; must be selectable per order.</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Schema deklariert: update</t>
+          <t>Schema deklariert: create, update</t>
         </is>
       </c>
     </row>
@@ -8114,29 +8110,25 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>billingAddress.zip</t>
+          <t>fulfillmentPolicy.partialShipping</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>search</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Postal-code search is a standard phone use-case (shop orders).</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: search</t>
-        </is>
-      </c>
+          <t>Partial-shipping policy has no upstream slot — the read reports a hardcoded "allowed". Needs a real v3 field before it can be written or trusted.</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -8146,29 +8138,25 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>billingAddress.email</t>
+          <t>discounts</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>search</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Email search is a standard use-case for shop orders — often the only identifier support has.</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: search</t>
-        </is>
-      </c>
+          <t>Header discounts/vouchers (e-commerce) are not exposed by v3 salesOrders — only line-level discounts exist.</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -8178,7 +8166,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -8193,7 +8181,7 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Custom field values carry company-specific data — today only readable via include, not writable via API (all documents).</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr"/>
@@ -8206,29 +8194,25 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>shipping.method</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Carrier / shipping method — core to fulfilment; must be selectable per order.</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Companies segment and find orders by their own custom-field values.</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -8238,22 +8222,22 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>fulfillmentPolicy.partialShipping</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Partial-shipping policy has no upstream slot — the read reports a hardcoded "allowed". Needs a real v3 field before it can be written or trusted.</t>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr"/>
@@ -8261,17 +8245,17 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>SalesOrder</t>
+          <t>DeliveryNote</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>discounts</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -8281,7 +8265,7 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Header discounts/vouchers (e-commerce) are not exposed by v3 salesOrders — only line-level discounts exist.</t>
+          <t>Carrying a delivery note number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr"/>
@@ -8289,17 +8273,17 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>SalesOrder</t>
+          <t>DeliveryNote</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
@@ -8309,7 +8293,7 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>Custom field values carry company-specific data — today only readable via include, not writable via API (all documents).</t>
+          <t>Reassign the delivery note's partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr"/>
@@ -8317,55 +8301,59 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>SalesOrder</t>
+          <t>DeliveryNote</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>filter</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Companies segment and find orders by their own custom-field values.</t>
-        </is>
-      </c>
-      <c r="F51" s="8" t="inlineStr"/>
+          <t>The customer's PO number on the delivery note (B2B) — read-only upstream today; must be settable.</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>SalesOrder</t>
+          <t>DeliveryNote</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>search</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+          <t>Warehouse/support find a delivery note by the customer's PO number.</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr"/>
@@ -8378,12 +8366,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -8393,7 +8381,7 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Carrying a delivery note number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+          <t>The picking/shipping warehouse — must be selectable per delivery note, not fixed to the default.</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr"/>
@@ -8406,7 +8394,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -8421,7 +8409,7 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Reassign the delivery note's partner after creation — v3 accepts it only on create.</t>
+          <t>Adjust delivered positions/quantities after creation — the v3 update DTO carries no line-item write path.</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr"/>
@@ -8434,29 +8422,25 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>shipments</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>The customer's PO number on the delivery note (B2B) — read-only upstream today; must be settable.</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Tracking numbers need a nachlade GET /v1/deliveryNotes/{id}/shipments — not yet composed into the read payload.</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -8466,12 +8450,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>customs.totalWeight</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -8481,7 +8465,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Warehouse/support find a delivery note by the customer's PO number.</t>
+          <t>Total shipment weight for the customs declaration / carrier — needs to be settable.</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr"/>
@@ -8494,7 +8478,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>customs.incoterm</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -8509,7 +8493,7 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>The picking/shipping warehouse — must be selectable per delivery note, not fixed to the default.</t>
+          <t>Incoterm for export shipments — a customs-declaration essential, not settable via API today.</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr"/>
@@ -8522,29 +8506,25 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>billingAddress.zip</t>
+          <t>customs.note</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>search</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Postal-code search — standard phone use-case for delivery lookups.</t>
-        </is>
-      </c>
-      <c r="F58" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: search</t>
-        </is>
-      </c>
+          <t>Customs note for export paperwork.</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -8554,12 +8534,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
@@ -8569,7 +8549,7 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Adjust delivered positions/quantities after creation — the v3 update DTO carries no line-item write path.</t>
+          <t>Custom field values on the delivery note — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr"/>
@@ -8577,17 +8557,17 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>DeliveryNote</t>
+          <t>Shipment</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>shipments</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
@@ -8597,7 +8577,7 @@
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>Tracking numbers need a nachlade GET /v1/deliveryNotes/{id}/shipments — not yet composed into the read payload.</t>
+          <t>Creating a shipment + label via the facade (POST /v1/shipments + createLabel exists upstream) is not orchestrated here yet — needed for headless fulfilment.</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr"/>
@@ -8605,17 +8585,17 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>DeliveryNote</t>
+          <t>Shipment</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>customs.totalWeight</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
@@ -8625,7 +8605,7 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Total shipment weight for the customs declaration / carrier — needs to be settable.</t>
+          <t>The shipment lifecycle status is not exposed by v1 shipments — only sentAt exists.</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr"/>
@@ -8633,17 +8613,17 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>DeliveryNote</t>
+          <t>Shipment</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>customs.incoterm</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
@@ -8653,7 +8633,7 @@
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Incoterm for export shipments — a customs-declaration essential, not settable via API today.</t>
+          <t>Package weight is not exposed by v1 shipments.</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr"/>
@@ -8661,17 +8641,17 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>DeliveryNote</t>
+          <t>Shipment</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>customs.note</t>
+          <t>events</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
@@ -8681,7 +8661,7 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Customs note for export paperwork.</t>
+          <t>Carrier tracking events are not exposed — needs a carrier-events feed.</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr"/>
@@ -8689,17 +8669,17 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>DeliveryNote</t>
+          <t>Shipment</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>tracking.number</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
@@ -8709,7 +8689,7 @@
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the delivery note — today only readable via include, not writable via API.</t>
+          <t>Support looks up a shipment by tracking number — needs a filterable/searchable upstream list parameter.</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr"/>
@@ -8717,17 +8697,17 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Shipment</t>
+          <t>SalesInvoice</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
@@ -8737,7 +8717,7 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Creating a shipment + label via the facade (POST /v1/shipments + createLabel exists upstream) is not orchestrated here yet — needed for headless fulfilment.</t>
+          <t>Correcting a invoice number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr"/>
@@ -8745,17 +8725,17 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Shipment</t>
+          <t>SalesInvoice</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -8765,7 +8745,7 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>The shipment lifecycle status is not exposed by v1 shipments — only sentAt exists.</t>
+          <t>Reassign the invoice's partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr"/>
@@ -8773,45 +8753,49 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Shipment</t>
+          <t>SalesInvoice</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Package weight is not exposed by v1 shipments.</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr"/>
+          <t>The customer's PO number on the invoice (B2B) — read-only upstream today; must be settable and correctable.</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Shipment</t>
+          <t>SalesInvoice</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>events</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -8821,7 +8805,7 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Carrier tracking events are not exposed — needs a carrier-events feed.</t>
+          <t>Support and accounting find invoices by the customer's PO number.</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr"/>
@@ -8829,17 +8813,17 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>Shipment</t>
+          <t>SalesInvoice</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>tracking.number</t>
+          <t>references.debtorAccountNumber</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
@@ -8849,7 +8833,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Support looks up a shipment by tracking number — needs a filterable/searchable upstream list parameter.</t>
+          <t>Deviating debtor account for the FiBu/DATEV export — settable when it differs from the customer default.</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr"/>
@@ -8862,12 +8846,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
@@ -8877,7 +8861,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>Correcting a invoice number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr"/>
@@ -8890,25 +8874,29 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>totals.outstanding</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Reassign the invoice's partner after creation — v3 accepts it only on create.</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="inlineStr"/>
+          <t>Exact open amount needs readable payment↔invoice allocations (docs/05 #2); today only derived from paymentStatus.</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -8918,29 +8906,25 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>payment.method</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>The customer's PO number on the invoice (B2B) — read-only upstream today; must be settable and correctable.</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Payment method on the invoice — central to order-to-cash; frequently overridden.</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -8950,12 +8934,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>payment.terms.dueDays</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
@@ -8965,7 +8949,7 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Support and accounting find invoices by the customer's PO number.</t>
+          <t>Net payment term in days — drives the due date and dunning.</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr"/>
@@ -8978,7 +8962,7 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>references.debtorAccountNumber</t>
+          <t>payment.terms.discountPercent</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -8993,7 +8977,7 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Deviating debtor account for the FiBu/DATEV export — settable when it differs from the customer default.</t>
+          <t>Cash-discount percentage — standard DACH B2B.</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr"/>
@@ -9006,29 +8990,25 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>billingAddress.email</t>
+          <t>payment.terms.discountDays</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>search</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Email search — standard use-case for finding a customer's invoices.</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: search</t>
-        </is>
-      </c>
+          <t>Cash-discount period in days — pairs with the discount.</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -9038,25 +9018,29 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>eInvoice</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr"/>
+          <t>The finished ZUGFeRD/XRechnung artefact + delivery status is a missing upstream API (docs/05 #7) — only XML raw data exists today.</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -9066,29 +9050,25 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>totals.outstanding</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Exact open amount needs readable payment↔invoice allocations (docs/05 #2); today only derived from paymentStatus.</t>
-        </is>
-      </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>Custom field values on the invoice — today only readable via include, not writable via API.</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -9098,22 +9078,22 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>payment.method</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Payment method on the invoice — central to order-to-cash; frequently overridden.</t>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr"/>
@@ -9121,17 +9101,17 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>payment.terms.dueDays</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -9141,7 +9121,7 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Net payment term in days — drives the due date and dunning.</t>
+          <t>No payment LIST/filter exists upstream — only GET /paymentTransactions/{id} (docs/05 #2). GET /v3/payments with filters is the ask.</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr"/>
@@ -9149,17 +9129,17 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>payment.terms.discountPercent</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -9169,7 +9149,7 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Cash-discount percentage — standard DACH B2B.</t>
+          <t>Payout/settlement aggregation (fees, chargebacks) per provider needs docs/05 #8.</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr"/>
@@ -9177,17 +9157,17 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>payment.terms.discountDays</t>
+          <t>allocations</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, update</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
@@ -9197,7 +9177,7 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Cash-discount period in days — pairs with the discount.</t>
+          <t>Payment↔invoice allocations (n:m) are neither readable nor writable — without them exact outstanding amounts are impossible (docs/05 #2).</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr"/>
@@ -9205,44 +9185,40 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>dunning.blocked</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D82" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Block/unblock dunning per invoice — a core AR control not writable upstream today.</t>
-        </is>
-      </c>
-      <c r="F82" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: update · Schema deklariert: update</t>
-        </is>
-      </c>
+          <t>Carrying a return number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>dunning.note</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -9250,68 +9226,60 @@
           <t>update</t>
         </is>
       </c>
-      <c r="D83" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>A dunning note for the AR clerk — must be writable.</t>
-        </is>
-      </c>
-      <c r="F83" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: update · Schema deklariert: update</t>
-        </is>
-      </c>
+          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>eInvoice</t>
+          <t>references.rmaNumber</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D84" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>The finished ZUGFeRD/XRechnung artefact + delivery status is a missing upstream API (docs/05 #7) — only XML raw data exists today.</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>The RMA number the customer quotes — no upstream field today; core to returns handling.</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>references.rmaNumber</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
@@ -9321,7 +9289,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the invoice — today only readable via include, not writable via API.</t>
+          <t>Support finds a return by the RMA number the customer has.</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr"/>
@@ -9329,27 +9297,27 @@
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D86" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+          <t>The customer's PO number on the return — read-only upstream today.</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr"/>
@@ -9357,17 +9325,17 @@
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
@@ -9377,7 +9345,7 @@
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>No payment LIST/filter exists upstream — only GET /paymentTransactions/{id} (docs/05 #2). GET /v3/payments with filters is the ask.</t>
+          <t>The returns warehouse must be selectable per return.</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr"/>
@@ -9385,17 +9353,17 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
@@ -9405,7 +9373,7 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Payout/settlement aggregation (fees, chargebacks) per provider needs docs/05 #8.</t>
+          <t>Edit return positions after creation — the v3 update DTO carries no line-item write path.</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr"/>
@@ -9413,30 +9381,34 @@
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>allocations</t>
+          <t>items.reason</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Payment↔invoice allocations (n:m) are neither readable nor writable — without them exact outstanding amounts are impossible (docs/05 #2).</t>
-        </is>
-      </c>
-      <c r="F89" s="8" t="inlineStr"/>
+          <t>The return reason per line — essential for returns analytics; not settable via API today.</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -9446,12 +9418,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>items.condition</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
@@ -9461,7 +9433,7 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>Carrying a return number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+          <t>Item condition (resellable/damaged/disposal) drives restocking — not in the v3 payload yet.</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr"/>
@@ -9474,12 +9446,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>items.condition</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
@@ -9489,7 +9461,7 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
+          <t>Item condition is not surfaced by the v3 return payload yet (docs/05 #4 batch/trace family).</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr"/>
@@ -9502,7 +9474,7 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>references.rmaNumber</t>
+          <t>items.action</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
@@ -9517,7 +9489,7 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>The RMA number the customer quotes — no upstream field today; core to returns handling.</t>
+          <t>Resolution per line (credit/replace/repair) — not in the v3 payload yet.</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr"/>
@@ -9530,12 +9502,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>references.rmaNumber</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -9545,7 +9517,7 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Support finds a return by the RMA number the customer has.</t>
+          <t>Custom field values on the return — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr"/>
@@ -9553,17 +9525,17 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
@@ -9573,7 +9545,7 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>The customer's PO number on the return — read-only upstream today.</t>
+          <t>Correcting a credit note number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr"/>
@@ -9581,17 +9553,17 @@
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
@@ -9601,7 +9573,7 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>The returns warehouse must be selectable per return.</t>
+          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr"/>
@@ -9609,40 +9581,44 @@
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Edit return positions after creation — the v3 update DTO carries no line-item write path.</t>
-        </is>
-      </c>
-      <c r="F96" s="8" t="inlineStr"/>
+          <t>The customer's PO number on the credit note (B2B) — read-only upstream today.</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>items.reason</t>
+          <t>references.debtorAccountNumber</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -9650,31 +9626,27 @@
           <t>create, update</t>
         </is>
       </c>
-      <c r="D97" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>The return reason per line — essential for returns analytics; not settable via API today.</t>
-        </is>
-      </c>
-      <c r="F97" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Deviating debtor account for the FiBu/DATEV export of the credit note.</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>items.condition</t>
+          <t>dates.serviceDate</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
@@ -9689,7 +9661,7 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Item condition (resellable/damaged/disposal) drives restocking — not in the v3 payload yet.</t>
+          <t>Leistungsdatum — a §14 UStG mandatory field on the credit note; must be settable.</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr"/>
@@ -9697,17 +9669,17 @@
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>items.condition</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
@@ -9717,7 +9689,7 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Item condition is not surfaced by the v3 return payload yet (docs/05 #4 batch/trace family).</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr"/>
@@ -9725,40 +9697,44 @@
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>items.action</t>
+          <t>totals.outstanding</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Resolution per line (credit/replace/repair) — not in the v3 payload yet.</t>
-        </is>
-      </c>
-      <c r="F100" s="8" t="inlineStr"/>
+          <t>Exact open amount needs readable refund/offset allocations (docs/05 #2); today derived from paymentStatus only.</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>settlement.mode</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -9773,7 +9749,7 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the return — today only readable via include, not writable via API.</t>
+          <t>Refund vs offset-against-invoice is a per-credit-note decision — not settable upstream today.</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr"/>
@@ -9786,12 +9762,12 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
@@ -9801,7 +9777,7 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Correcting a credit note number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
+          <t>Custom field values on the credit note — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr"/>
@@ -9814,22 +9790,22 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr"/>
@@ -9837,49 +9813,45 @@
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="D104" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>read, update</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>The customer's PO number on the credit note (B2B) — read-only upstream today.</t>
-        </is>
-      </c>
-      <c r="F104" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Active/archived state is not exposed via v3 suppliers — needed for honest archiving (plan §6.1).</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>references.debtorAccountNumber</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, update</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
@@ -9889,7 +9861,7 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Deviating debtor account for the FiBu/DATEV export of the credit note.</t>
+          <t>B2B hierarchy (branch → HQ) is not exposed via the public API (plan §6.1 parent).</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr"/>
@@ -9897,17 +9869,17 @@
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>dates.serviceDate</t>
+          <t>billTo</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, update</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
@@ -9917,7 +9889,7 @@
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Leistungsdatum — a §14 UStG mandatory field on the credit note; must be settable.</t>
+          <t>Central billing (Zentralregulierung — invoice to association/HQ) is not exposed (plan §6.1 billTo).</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr"/>
@@ -9925,17 +9897,17 @@
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>channels</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
@@ -9945,7 +9917,7 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Per-channel external ids (channel links) are not exposed via the public API.</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr"/>
@@ -9953,44 +9925,40 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>totals.outstanding</t>
+          <t>purchasing.confirmationRequired</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D108" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Exact open amount needs readable refund/offset allocations (docs/05 #2); today derived from paymentStatus only.</t>
-        </is>
-      </c>
-      <c r="F108" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>Whether an order confirmation (AB) is required from this supplier — drives purchasing workflow; not settable via API today.</t>
+        </is>
+      </c>
+      <c r="F108" s="8" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>settlement.mode</t>
+          <t>purchasing.sendOrdersVia</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -10005,7 +9973,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Refund vs offset-against-invoice is a per-credit-note decision — not settable upstream today.</t>
+          <t>How POs are sent to the supplier (email/portal/EDI) — a supplier default that must be settable.</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr"/>
@@ -10013,12 +9981,12 @@
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>purchasing.deliveryDays</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
@@ -10033,7 +10001,7 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the credit note — today only readable via include, not writable via API.</t>
+          <t>Standard supplier lead time in days — feeds replenishment planning.</t>
         </is>
       </c>
       <c r="F110" s="8" t="inlineStr"/>
@@ -10041,30 +10009,34 @@
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>addresses.type</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D111" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
-        </is>
-      </c>
-      <c r="F111" s="8" t="inlineStr"/>
+          <t>Set the address role incl. the 'both' value (one address serving billing AND shipping) — v3 splits billing (primaryAddress/deviating) vs shipping (deliveryAddresses) by store, so the role is not a freely settable field.</t>
+        </is>
+      </c>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create, update</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -10074,25 +10046,29 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>addresses.label</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
-        </is>
-      </c>
-      <c r="D112" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Active/archived state is not exposed via v3 suppliers — needed for honest archiving (plan §6.1).</t>
-        </is>
-      </c>
-      <c r="F112" s="8" t="inlineStr"/>
+          <t>Free label/name per address location (e.g. 'Lager München') — v3 knows only billing/shipping roles, no named locations.</t>
+        </is>
+      </c>
+      <c r="F112" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read · Schema deklariert: create, update</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
@@ -10102,25 +10078,29 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>addresses.isDefault</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
-        </is>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>B2B hierarchy (branch → HQ) is not exposed via the public API (plan §6.1 parent).</t>
-        </is>
-      </c>
-      <c r="F113" s="8" t="inlineStr"/>
+          <t>Mark the standard address per type (unified-address model; at most one default per customer &amp; type) — v3 partner addresses carry no isDefault flag.</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read · Schema deklariert: create, update</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
@@ -10130,7 +10110,7 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>billTo</t>
+          <t>defaults.shippingMethod</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
@@ -10145,7 +10125,7 @@
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Central billing (Zentralregulierung — invoice to association/HQ) is not exposed (plan §6.1 billTo).</t>
+          <t>The default shipping method is not surfaced by the v3 partner read.</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr"/>
@@ -10158,12 +10138,12 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>channels</t>
+          <t>defaults.priceList</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>read, update</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
@@ -10173,7 +10153,7 @@
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Per-channel external ids (channel links) are not exposed via the public API.</t>
+          <t>The assigned price list is not surfaced by the v3 partner read.</t>
         </is>
       </c>
       <c r="F115" s="8" t="inlineStr"/>
@@ -10186,12 +10166,12 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>purchasing.confirmationRequired</t>
+          <t>defaults.partialShipping</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, update</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
@@ -10201,7 +10181,7 @@
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Whether an order confirmation (AB) is required from this supplier — drives purchasing workflow; not settable via API today.</t>
+          <t>The partial-shipping preference is not surfaced by the v3 partner read.</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr"/>
@@ -10214,7 +10194,7 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>purchasing.sendOrdersVia</t>
+          <t>defaults.paymentTerms.dueDays</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -10229,7 +10209,7 @@
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>How POs are sent to the supplier (email/portal/EDI) — a supplier default that must be settable.</t>
+          <t>Default supplier payment term — drives liability due dates.</t>
         </is>
       </c>
       <c r="F117" s="8" t="inlineStr"/>
@@ -10242,12 +10222,12 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>purchasing.deliveryDays</t>
+          <t>finance.openAmount</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
@@ -10257,7 +10237,7 @@
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Standard supplier lead time in days — feeds replenishment planning.</t>
+          <t>Aggregated open liabilities per supplier are computed nowhere in the API — must be derived/served.</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr"/>
@@ -10270,29 +10250,25 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>addresses.type</t>
+          <t>finance.creditorAccountNumber</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D119" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Set the address role incl. the 'both' value (one address serving billing AND shipping) — v3 splits billing (primaryAddress/deviating) vs shipping (deliveryAddresses) by store, so the role is not a freely settable field.</t>
-        </is>
-      </c>
-      <c r="F119" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>The creditor account for the FiBu/DATEV export — settable per supplier.</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -10302,29 +10278,25 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>addresses.label</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D120" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Free label/name per address location (e.g. 'Lager München') — v3 knows only billing/shipping roles, no named locations.</t>
-        </is>
-      </c>
-      <c r="F120" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read · Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Custom field values on the supplier — today only readable, not writable via API.</t>
+        </is>
+      </c>
+      <c r="F120" s="8" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
@@ -10334,7 +10306,7 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>addresses.isDefault</t>
+          <t>contacts.address</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -10342,21 +10314,17 @@
           <t>read, create, update</t>
         </is>
       </c>
-      <c r="D121" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Mark the standard address per type (unified-address model; at most one default per customer &amp; type) — v3 partner addresses carry no isDefault flag.</t>
-        </is>
-      </c>
-      <c r="F121" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read · Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Bind a contact person to a specific address (person-at-location) — v3 stores only a free-text contactPerson on delivery addresses, not a reference.</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
@@ -10366,22 +10334,22 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>defaults.shippingMethod</t>
+          <t>contacts.isPrimary</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
-        </is>
-      </c>
-      <c r="D122" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>The default shipping method is not surfaced by the v3 partner read.</t>
+          <t>Mark the main contact person — v3 contactPersons carry no primary flag.</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr"/>
@@ -10389,17 +10357,17 @@
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>defaults.priceList</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
@@ -10409,7 +10377,7 @@
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>The assigned price list is not surfaced by the v3 partner read.</t>
+          <t>Carrying a purchase order number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
         </is>
       </c>
       <c r="F123" s="8" t="inlineStr"/>
@@ -10417,17 +10385,17 @@
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>defaults.partialShipping</t>
+          <t>supplier</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
@@ -10437,7 +10405,7 @@
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>The partial-shipping preference is not surfaced by the v3 partner read.</t>
+          <t>Reassign the PO's supplier after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr"/>
@@ -10445,12 +10413,12 @@
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>defaults.paymentTerms.dueDays</t>
+          <t>references.ourCustomerNumber</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
@@ -10465,7 +10433,7 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Default supplier payment term — drives liability due dates.</t>
+          <t>Our customer number at the supplier — belongs on the PO, not settable via API today.</t>
         </is>
       </c>
       <c r="F125" s="8" t="inlineStr"/>
@@ -10473,17 +10441,17 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>finance.openAmount</t>
+          <t>references.supplierOfferNumber</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
@@ -10493,7 +10461,7 @@
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Aggregated open liabilities per supplier are computed nowhere in the API — must be derived/served.</t>
+          <t>The supplier's quote number we ordered against — read-only upstream today.</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr"/>
@@ -10501,12 +10469,12 @@
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>finance.creditorAccountNumber</t>
+          <t>confirmation.status</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -10521,7 +10489,7 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>The creditor account for the FiBu/DATEV export — settable per supplier.</t>
+          <t>Recording the confirmation status (pending/confirmed/deviating) is core purchasing — not writable via API today.</t>
         </is>
       </c>
       <c r="F127" s="8" t="inlineStr"/>
@@ -10529,17 +10497,17 @@
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>confirmation.supplierOrderNumber</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
@@ -10549,7 +10517,7 @@
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the supplier — today only readable, not writable via API.</t>
+          <t>The AB (order-confirmation) number from the supplier — the whole confirmation block is read-only upstream (docs/05: AB handling).</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr"/>
@@ -10557,27 +10525,27 @@
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>contacts.address</t>
+          <t>dates.requestedDelivery</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D129" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Bind a contact person to a specific address (person-at-location) — v3 stores only a free-text contactPerson on delivery addresses, not a reference.</t>
+          <t>Requested delivery date at the supplier — not writable upstream today.</t>
         </is>
       </c>
       <c r="F129" s="8" t="inlineStr"/>
@@ -10585,27 +10553,27 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>contacts.isPrimary</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D130" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Mark the main contact person — v3 contactPersons carry no primary flag.</t>
+          <t>The receiving warehouse for the PO must be selectable.</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr"/>
@@ -10618,12 +10586,12 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
@@ -10633,7 +10601,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Carrying a purchase order number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+          <t>Edit PO positions after creation — the v3 update DTO carries no line-item write path.</t>
         </is>
       </c>
       <c r="F131" s="8" t="inlineStr"/>
@@ -10646,12 +10614,12 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>supplier</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
@@ -10661,7 +10629,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Reassign the PO's supplier after creation — v3 accepts it only on create.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr"/>
@@ -10674,12 +10642,12 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>references.ourCustomerNumber</t>
+          <t>dropship</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, create</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
@@ -10689,7 +10657,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Our customer number at the supplier — belongs on the PO, not settable via API today.</t>
+          <t>Dropshipping (Strecke: salesOrder link + customer delivery address) is not exposed via v3 purchaseOrders.</t>
         </is>
       </c>
       <c r="F133" s="8" t="inlineStr"/>
@@ -10702,7 +10670,7 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>references.supplierOfferNumber</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -10717,7 +10685,7 @@
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>The supplier's quote number we ordered against — read-only upstream today.</t>
+          <t>Custom field values on the PO — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F134" s="8" t="inlineStr"/>
@@ -10725,17 +10693,17 @@
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>confirmation.status</t>
+          <t>references.supplierDeliveryNoteNumber</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update, read</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
@@ -10745,7 +10713,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Recording the confirmation status (pending/confirmed/deviating) is core purchasing — not writable via API today.</t>
+          <t>The supplier's delivery-note number on the goods receipt — needed for the three-way match; not in the BF record yet.</t>
         </is>
       </c>
       <c r="F135" s="8" t="inlineStr"/>
@@ -10753,17 +10721,17 @@
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>confirmation.supplierOrderNumber</t>
+          <t>dates.received</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
@@ -10773,7 +10741,7 @@
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>The AB (order-confirmation) number from the supplier — the whole confirmation block is read-only upstream (docs/05: AB handling).</t>
+          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
         </is>
       </c>
       <c r="F136" s="8" t="inlineStr"/>
@@ -10781,17 +10749,17 @@
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>dates.requestedDelivery</t>
+          <t>dates.posted</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D137" s="9" t="inlineStr">
@@ -10801,7 +10769,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Requested delivery date at the supplier — not writable upstream today.</t>
+          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
         </is>
       </c>
       <c r="F137" s="8" t="inlineStr"/>
@@ -10809,17 +10777,17 @@
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
@@ -10829,7 +10797,7 @@
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>The receiving warehouse for the PO must be selectable.</t>
+          <t>Cancel/storno of a posted goods receipt — the remaining upstream gap after the BF entity list covered browsing (docs/05 #9 revised).</t>
         </is>
       </c>
       <c r="F138" s="8" t="inlineStr"/>
@@ -10837,7 +10805,7 @@
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
@@ -10847,7 +10815,7 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read, create, update</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
@@ -10857,7 +10825,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Edit PO positions after creation — the v3 update DTO carries no line-item write path.</t>
+          <t>Line items (product × quantity × storage location, quality check per line) are not exposed on the BF goodsReceipt record — creation still goes through the PO action only.</t>
         </is>
       </c>
       <c r="F139" s="8" t="inlineStr"/>
@@ -10865,12 +10833,12 @@
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
@@ -10885,7 +10853,7 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>The document number is system-assigned: sending `documentNumber` on create answers 201 and the record comes back with an empty number (measured on mvp 2026-08-02). Same behaviour as the other documents.</t>
         </is>
       </c>
       <c r="F140" s="8" t="inlineStr"/>
@@ -10893,17 +10861,17 @@
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>dropship</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>read, create</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
@@ -10913,7 +10881,7 @@
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Dropshipping (Strecke: salesOrder link + customer delivery address) is not exposed via v3 purchaseOrders.</t>
+          <t>Filtering incoming invoices by workflow status is the AP daily view — the BF supplierInvoice API does not allow filtering documentStatus today.</t>
         </is>
       </c>
       <c r="F141" s="8" t="inlineStr"/>
@@ -10921,17 +10889,17 @@
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>dates.invoiceDate</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>sort</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
@@ -10941,7 +10909,7 @@
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the PO — today only readable via include, not writable via API.</t>
+          <t>Sorting incoming invoices by invoice date — dateOfSupplierInvoice is not sortable on the BF API today.</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr"/>
@@ -10949,17 +10917,17 @@
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>references.supplierDeliveryNoteNumber</t>
+          <t>match.status</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>create, update, read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
@@ -10969,7 +10937,7 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>The supplier's delivery-note number on the goods receipt — needed for the three-way match; not in the BF record yet.</t>
+          <t>Re-running/overriding the match verdict via API (rematch) — the check statuses are readable now; a command to re-evaluate is still missing upstream.</t>
         </is>
       </c>
       <c r="F143" s="8" t="inlineStr"/>
@@ -10977,17 +10945,17 @@
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>dates.received</t>
+          <t>payment.status</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
@@ -10997,7 +10965,7 @@
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
+          <t>Open-liabilities view needs filtering by payment status — not allowed on the BF supplierInvoice API today.</t>
         </is>
       </c>
       <c r="F144" s="8" t="inlineStr"/>
@@ -11005,17 +10973,17 @@
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>dates.posted</t>
+          <t>approval.status</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
@@ -11025,7 +10993,7 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
+          <t>Approve/reject via API: BF process steps (GoodsCheck/InvoiceCheck/Payment) are reported to exist — wiring + live verification of those steps is pending (steps were empty on the test instance's metadata).</t>
         </is>
       </c>
       <c r="F145" s="8" t="inlineStr"/>
@@ -11033,17 +11001,17 @@
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>approval.by</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
@@ -11053,7 +11021,7 @@
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Cancel/storno of a posted goods receipt — the remaining upstream gap after the BF entity list covered browsing (docs/05 #9 revised).</t>
+          <t>The approver is not exposed — BF supplierInvoice carries only the check statuses.</t>
         </is>
       </c>
       <c r="F146" s="8" t="inlineStr"/>
@@ -11061,17 +11029,17 @@
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>approval.at</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
@@ -11081,7 +11049,7 @@
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Line items (product × quantity × storage location, quality check per line) are not exposed on the BF goodsReceipt record — creation still goes through the PO action only.</t>
+          <t>The approval timestamp is not exposed by the BF supplierInvoice entity.</t>
         </is>
       </c>
       <c r="F147" s="8" t="inlineStr"/>
@@ -11089,12 +11057,12 @@
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
@@ -11109,7 +11077,7 @@
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>The document number is system-assigned: sending `documentNumber` on create answers 201 and the record comes back with an empty number (measured on mvp 2026-08-02). Same behaviour as the other documents.</t>
+          <t>The consolidated product kind (ADR-011) should be settable directly instead of juggling isServiceProduct/isFee/isShippingCostsProduct booleans — the v2 create body only exposes isShippingCostsProduct, so service/digital cannot be expressed.</t>
         </is>
       </c>
       <c r="F148" s="8" t="inlineStr"/>
@@ -11117,17 +11085,17 @@
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D149" s="9" t="inlineStr">
@@ -11137,7 +11105,7 @@
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Filtering incoming invoices by workflow status is the AP daily view — the BF supplierInvoice API does not allow filtering documentStatus today.</t>
+          <t>Tagging products (assortment curation, campaigns) — product writes now go through v2, but the v2 tags shape ({id,key,name,color}) is not yet mapped/verified, so tag writes stay blue.</t>
         </is>
       </c>
       <c r="F149" s="8" t="inlineStr"/>
@@ -11145,17 +11113,17 @@
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>dates.invoiceDate</t>
+          <t>prices.sale</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>sort</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
@@ -11165,7 +11133,7 @@
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Sorting incoming invoices by invoice date — dateOfSupplierInvoice is not sortable on the BF API today.</t>
+          <t>WRITE works — the sale price is composed as a separate salesPrices write on create/update. READ is still blue: the v3 read model does not carry the sale price (needs the salesPrices include parsed), so a written price is not read back.</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr"/>
@@ -11173,17 +11141,17 @@
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>match.status</t>
+          <t>tax.profile</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D151" s="9" t="inlineStr">
@@ -11193,7 +11161,7 @@
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Re-running/overriding the match verdict via API (rematch) — the check statuses are readable now; a command to re-evaluate is still missing upstream.</t>
+          <t>The 16-account tax matrix consolidated into a referenceable taxProfile (ADR-011) — today only the raw taxAccounts embed exists, not a clean reference.</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr"/>
@@ -11201,17 +11169,17 @@
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>payment.status</t>
+          <t>logistics.packagingUnits</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>create, read, update</t>
         </is>
       </c>
       <c r="D152" s="9" t="inlineStr">
@@ -11221,7 +11189,7 @@
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Open-liabilities view needs filtering by payment status — not allowed on the BF supplierInvoice API today.</t>
+          <t>Packaging units (VPE) need the packagingUnits include parsed — not yet mapped.</t>
         </is>
       </c>
       <c r="F152" s="8" t="inlineStr"/>
@@ -11229,17 +11197,17 @@
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>approval.status</t>
+          <t>stock.incoming</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D153" s="9" t="inlineStr">
@@ -11249,7 +11217,7 @@
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Approve/reject via API: BF process steps (GoodsCheck/InvoiceCheck/Payment) are reported to exist — wiring + live verification of those steps is pending (steps were empty on the test instance's metadata).</t>
+          <t>Inbound quantity (ordered but not yet received) is the one stock figure Xentral does not compute: /products/{id}/stocks returns physical, sellable, reserved, correction, pseudo, openSalesOrders, calculated and producible — all mapped — but nothing inbound. The per-warehouse split the same call carries is answered by StockLevel (filter[product], narrowed by warehouse), so it is not duplicated onto the product.</t>
         </is>
       </c>
       <c r="F153" s="8" t="inlineStr"/>
@@ -11257,17 +11225,17 @@
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>approval.by</t>
+          <t>suppliers</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D154" s="9" t="inlineStr">
@@ -11277,7 +11245,7 @@
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>The approver is not exposed — BF supplierInvoice carries only the check statuses.</t>
+          <t>The default supplier IS writable (mapped to v2 standardSupplier); multi-supplier sourcing (several suppliers with per-supplier price/number) needs a suppliers include/relation not yet mapped, plus a write path.</t>
         </is>
       </c>
       <c r="F154" s="8" t="inlineStr"/>
@@ -11285,12 +11253,12 @@
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>PriceList</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>approval.at</t>
+          <t>entries</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
@@ -11305,7 +11273,7 @@
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>The approval timestamp is not exposed by the BF supplierInvoice entity.</t>
+          <t>v1 salesPrices exposes flat price rows (this entity is one row); the grouped priceList with a tier array needs a composer (ADR-012). Write each tier as its own entry (create/update/delete are live via v3/v1 salesPrices).</t>
         </is>
       </c>
       <c r="F155" s="8" t="inlineStr"/>
@@ -11313,12 +11281,12 @@
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StorageLocation</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
@@ -11333,7 +11301,7 @@
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>The consolidated product kind (ADR-011) should be settable directly instead of juggling isServiceProduct/isFee/isShippingCostsProduct booleans — the v2 create body only exposes isShippingCostsProduct, so service/digital cannot be expressed.</t>
+          <t>Upstream returns the bin description but rejects it on create and update ("The attribute description is not allowed.") — the field is read-only for every API generation we have. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F156" s="8" t="inlineStr"/>
@@ -11341,17 +11309,17 @@
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StorageLocation</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>contents.reserved</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D157" s="9" t="inlineStr">
@@ -11361,7 +11329,7 @@
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Tagging products (assortment curation, campaigns) — product writes now go through v2, but the v2 tags shape ({id,key,name,color}) is not yet mapped/verified, so tag writes stay blue.</t>
+          <t>Location contents are composed from the StockLevel projection now; the reserved portion per location stays unavailable — upstream reports reservations only as a product total.</t>
         </is>
       </c>
       <c r="F157" s="8" t="inlineStr"/>
@@ -11369,12 +11337,12 @@
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StorageLocation</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>prices.sale</t>
+          <t>locationType</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
@@ -11382,14 +11350,14 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D158" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D158" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>WRITE works — the sale price is composed as a separate salesPrices write on create/update. READ is still blue: the v3 read model does not carry the sale price (needs the salesPrices include parsed), so a written price is not read back.</t>
+          <t>v1 accepts a `locationType` on write with 204 but never returns it on any read, so a value written there cannot be verified or shown. Not modelled until upstream reads it back. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F158" s="8" t="inlineStr"/>
@@ -11397,17 +11365,17 @@
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>tax.profile</t>
+          <t>batch</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, list</t>
         </is>
       </c>
       <c r="D159" s="9" t="inlineStr">
@@ -11417,7 +11385,7 @@
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>The 16-account tax matrix consolidated into a referenceable taxProfile (ADR-011) — today only the raw taxAccounts embed exists, not a clean reference.</t>
+          <t>The batch split exists on the v2 items path (qualityControlAttributes) but not on /v1/products/{id}/storageLocations. Emitting batch rows on one anchor only would make the grain depend on the filter, so the projection stays product × storage location. A unified GET /v3/stockLevels is the clean ask (docs/05 #18).</t>
         </is>
       </c>
       <c r="F159" s="8" t="inlineStr"/>
@@ -11425,17 +11393,17 @@
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>logistics.packagingUnits</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>create, read, update</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D160" s="9" t="inlineStr">
@@ -11445,7 +11413,7 @@
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Packaging units (VPE) need the packagingUnits include parsed — not yet mapped.</t>
+          <t>The list needs an anchor filter (product or storageLocation): upstream has no global stock collection, so an unanchored query would mean fanning out over every product of the tenant.</t>
         </is>
       </c>
       <c r="F160" s="8" t="inlineStr"/>
@@ -11453,12 +11421,12 @@
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>stock.incoming</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
@@ -11473,7 +11441,7 @@
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Inbound quantity (ordered but not yet received) is the one stock figure Xentral does not compute: /products/{id}/stocks returns physical, sellable, reserved, correction, pseudo, openSalesOrders, calculated and producible — all mapped — but nothing inbound. The per-warehouse split the same call carries is answered by StockLevel (filter[product], narrowed by warehouse), so it is not duplicated onto the product.</t>
+          <t>No per-location reservation is exposed upstream; /v1/products/{id}/stocks reports reserved only as a product TOTAL. The projection reports quantity and leaves reserved/available blank rather than spreading a total over locations.</t>
         </is>
       </c>
       <c r="F161" s="8" t="inlineStr"/>
@@ -11481,17 +11449,17 @@
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>suppliers</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D162" s="9" t="inlineStr">
@@ -11501,7 +11469,7 @@
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>The default supplier IS writable (mapped to v2 standardSupplier); multi-supplier sourcing (several suppliers with per-supplier price/number) needs a suppliers include/relation not yet mapped, plus a write path.</t>
+          <t>Same gap as reserved: available = quantity - reserved is only derivable per product, not per storage location.</t>
         </is>
       </c>
       <c r="F162" s="8" t="inlineStr"/>
@@ -11509,17 +11477,17 @@
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>PriceList</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>entries</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>list, read</t>
         </is>
       </c>
       <c r="D163" s="9" t="inlineStr">
@@ -11529,7 +11497,7 @@
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>v1 salesPrices exposes flat price rows (this entity is one row); the grouped priceList with a tier array needs a composer (ADR-012). Write each tier as its own entry (create/update/delete are live via v3/v1 salesPrices).</t>
+          <t>The stock ledger (Lagerprotokoll) has NO read API at all — the single biggest gap (docs/05 #1). GET /v3/stockMovements is the ask. Until it ships the entity does not declare list/read at all, so a caller learns this from the contract instead of a 404.</t>
         </is>
       </c>
       <c r="F163" s="8" t="inlineStr"/>
@@ -11537,17 +11505,17 @@
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>StorageLocation</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D164" s="9" t="inlineStr">
@@ -11557,7 +11525,7 @@
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>Upstream returns the bin description but rejects it on create and update ("The attribute description is not allowed.") — the field is read-only for every API generation we have. Measured on mvp 2026-08-02.</t>
+          <t>A booking returns no identity: the v1 storage-item endpoints answer 201 with an empty body and — contrary to their own spec — send no Location header (verified on mvp 2026-07-31). Without an id a repeated booking cannot be recognised afterwards, which is why correction+setQuantityTo is the only retry-safe write. The ask: return the specced Location header, or the created movement.</t>
         </is>
       </c>
       <c r="F164" s="8" t="inlineStr"/>
@@ -11565,12 +11533,12 @@
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>StorageLocation</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>contents.reserved</t>
+          <t>unitCost</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
@@ -11585,7 +11553,7 @@
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Location contents are composed from the StockLevel projection now; the reserved portion per location stays unavailable — upstream reports reservations only as a product total.</t>
+          <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
         </is>
       </c>
       <c r="F165" s="8" t="inlineStr"/>
@@ -11593,27 +11561,27 @@
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>StorageLocation</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>locationType</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D166" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>v1 accepts a `locationType` on write with 204 but never returns it on any read, so a value written there cannot be verified or shown. Not modelled until upstream reads it back. Measured on mvp 2026-08-02.</t>
+          <t>Starting a stock take via API (scope: warehouse/locations/products, key date) — the v1 inventory endpoints exist but the write orchestration is not built yet.</t>
         </is>
       </c>
       <c r="F166" s="8" t="inlineStr"/>
@@ -11621,17 +11589,17 @@
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>batch</t>
+          <t>dates.keyDate</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>read, list</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D167" s="9" t="inlineStr">
@@ -11641,7 +11609,7 @@
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>The batch split exists on the v2 items path (qualityControlAttributes) but not on /v1/products/{id}/storageLocations. Emitting batch rows on one anchor only would make the grain depend on the filter, so the projection stays product × storage location. A unified GET /v3/stockLevels is the clean ask (docs/05 #18).</t>
+          <t>The inventory key date (Stichtag) is not exposed by v1 inventoryRuns.</t>
         </is>
       </c>
       <c r="F167" s="8" t="inlineStr"/>
@@ -11649,17 +11617,17 @@
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>dates.posted</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D168" s="9" t="inlineStr">
@@ -11669,7 +11637,7 @@
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>The list needs an anchor filter (product or storageLocation): upstream has no global stock collection, so an unanchored query would mean fanning out over every product of the tenant.</t>
+          <t>The posted timestamp is not exposed by v1 inventoryRuns.</t>
         </is>
       </c>
       <c r="F168" s="8" t="inlineStr"/>
@@ -11677,12 +11645,12 @@
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>totals</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
@@ -11690,27 +11658,31 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D169" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D169" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>No per-location reservation is exposed upstream; /v1/products/{id}/stocks reports reserved only as a product TOTAL. The projection reports quantity and leaves reserved/available blank rather than spreading a total over locations.</t>
-        </is>
-      </c>
-      <c r="F169" s="8" t="inlineStr"/>
+          <t>Position/difference totals are not exposed by v1 inventoryRuns.</t>
+        </is>
+      </c>
+      <c r="F169" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>positions</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
@@ -11725,7 +11697,7 @@
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>Same gap as reserved: available = quantity - reserved is only derivable per product, not per storage location.</t>
+          <t>Counting positions (expected/counted/difference with values) live in the counting-list reports — not composed into the API payload yet; needed for the GoBD difference review.</t>
         </is>
       </c>
       <c r="F170" s="8" t="inlineStr"/>
@@ -11733,17 +11705,17 @@
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>StockMovement</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>positions.counted</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>list, read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D171" s="9" t="inlineStr">
@@ -11753,7 +11725,7 @@
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>The stock ledger (Lagerprotokoll) has NO read API at all — the single biggest gap (docs/05 #1). GET /v3/stockMovements is the ask. Until it ships the entity does not declare list/read at all, so a caller learns this from the contract instead of a 404.</t>
+          <t>Submitting counted quantities via API (mobile counting) — needed for headless inventory.</t>
         </is>
       </c>
       <c r="F171" s="8" t="inlineStr"/>
@@ -11761,17 +11733,17 @@
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>StockMovement</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>documents.stockMovements</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D172" s="9" t="inlineStr">
@@ -11781,7 +11753,7 @@
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>A booking returns no identity: the v1 storage-item endpoints answer 201 with an empty body and — contrary to their own spec — send no Location header (verified on mvp 2026-07-31). Without an id a repeated booking cannot be recognised afterwards, which is why correction+setQuantityTo is the only retry-safe write. The ask: return the specced Location header, or the created movement.</t>
+          <t>Posted correction movements per stock take need the stockMovements API (docs/05 #1) to be traceable.</t>
         </is>
       </c>
       <c r="F172" s="8" t="inlineStr"/>
@@ -11789,17 +11761,17 @@
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>StockMovement</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>unitCost</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D173" s="9" t="inlineStr">
@@ -11809,7 +11781,7 @@
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
+          <t>Creating a picking run by criteria (wave: channel, shipping method, cutoff, maxOrders) has NO upstream endpoint — the main gap (docs/05 #3); execution (start/complete, totes) already exists.</t>
         </is>
       </c>
       <c r="F173" s="8" t="inlineStr"/>
@@ -11817,17 +11789,17 @@
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>criteria</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D174" s="9" t="inlineStr">
@@ -11837,7 +11809,7 @@
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Starting a stock take via API (scope: warehouse/locations/products, key date) — the v1 inventory endpoints exist but the write orchestration is not built yet.</t>
+          <t>Pick-run criteria (channel, shipping method) are not exposed by v1 pickLists.</t>
         </is>
       </c>
       <c r="F174" s="8" t="inlineStr"/>
@@ -11845,12 +11817,12 @@
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>dates.keyDate</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
@@ -11865,7 +11837,7 @@
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>The inventory key date (Stichtag) is not exposed by v1 inventoryRuns.</t>
+          <t>The picked sales orders are not exposed by v1 pickLists (only counts).</t>
         </is>
       </c>
       <c r="F175" s="8" t="inlineStr"/>
@@ -11873,12 +11845,12 @@
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>dates.posted</t>
+          <t>containers</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
@@ -11893,7 +11865,7 @@
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>The posted timestamp is not exposed by v1 inventoryRuns.</t>
+          <t>Totes/containers are not exposed by v1 pickLists.</t>
         </is>
       </c>
       <c r="F176" s="8" t="inlineStr"/>
@@ -11901,44 +11873,40 @@
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>totals</t>
+          <t>strategy</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D177" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Position/difference totals are not exposed by v1 inventoryRuns.</t>
-        </is>
-      </c>
-      <c r="F177" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>Choosing the picking strategy (single/multiOrder/wave/zone) at creation — no create endpoint today.</t>
+        </is>
+      </c>
+      <c r="F177" s="8" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>positions</t>
+          <t>tasks</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
@@ -11953,7 +11921,7 @@
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Counting positions (expected/counted/difference with values) live in the counting-list reports — not composed into the API payload yet; needed for the GoBD difference review.</t>
+          <t>Task-level detail (location, product, quantity, status per pick) is not exposed on the pickLists API — needed for progress boards and pick-path optimisation.</t>
         </is>
       </c>
       <c r="F178" s="8" t="inlineStr"/>
@@ -11961,12 +11929,12 @@
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>positions.counted</t>
+          <t>tasks.status</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
@@ -11981,7 +11949,7 @@
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Submitting counted quantities via API (mobile counting) — needed for headless inventory.</t>
+          <t>Granular task-level pick confirmation with quantity + scans (docs/05 #3) — today only whole-list start/complete exists.</t>
         </is>
       </c>
       <c r="F179" s="8" t="inlineStr"/>
@@ -11989,17 +11957,17 @@
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>documents.stockMovements</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>list, read</t>
         </is>
       </c>
       <c r="D180" s="9" t="inlineStr">
@@ -12009,7 +11977,7 @@
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Posted correction movements per stock take need the stockMovements API (docs/05 #1) to be traceable.</t>
+          <t>Batches exist only as read-only v3 Product includes — no batch resource, no list, no detail (docs/05 #4). GET /v3/batches is the ask.</t>
         </is>
       </c>
       <c r="F180" s="8" t="inlineStr"/>
@@ -12017,17 +11985,17 @@
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>bestBefore</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D181" s="9" t="inlineStr">
@@ -12037,7 +12005,7 @@
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Creating a picking run by criteria (wave: channel, shipping method, cutoff, maxOrders) has NO upstream endpoint — the main gap (docs/05 #3); execution (start/complete, totes) already exists.</t>
+          <t>Correcting a best-before date via API — internal web routes only today.</t>
         </is>
       </c>
       <c r="F181" s="8" t="inlineStr"/>
@@ -12045,17 +12013,17 @@
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>criteria</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D182" s="9" t="inlineStr">
@@ -12065,7 +12033,7 @@
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Pick-run criteria (channel, shipping method) are not exposed by v1 pickLists.</t>
+          <t>Blocking/releasing a batch (quality hold) via API — maintenance happens only through internal web routes today.</t>
         </is>
       </c>
       <c r="F182" s="8" t="inlineStr"/>
@@ -12073,12 +12041,12 @@
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>trace</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
@@ -12093,7 +12061,7 @@
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>The picked sales orders are not exposed by v1 pickLists (only counts).</t>
+          <t>Batch trace (which goods receipts brought it in, which delivery notes shipped it — recall scenario) has no API at all (docs/05 #4).</t>
         </is>
       </c>
       <c r="F183" s="8" t="inlineStr"/>
@@ -12101,12 +12069,12 @@
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>containers</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
@@ -12114,60 +12082,68 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D184" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D184" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>Totes/containers are not exposed by v1 pickLists.</t>
-        </is>
-      </c>
-      <c r="F184" s="8" t="inlineStr"/>
+          <t>The platform kind (shopify/amazon/…) is not exposed — the BF salesChannel entity carries only a name (05 #17).</t>
+        </is>
+      </c>
+      <c r="F184" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>strategy</t>
+          <t>defaults</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="D185" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D185" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Choosing the picking strategy (single/multiOrder/wave/zone) at creation — no create endpoint today.</t>
-        </is>
-      </c>
-      <c r="F185" s="8" t="inlineStr"/>
+          <t>Channel defaults (price list, warehouse) are not exposed (05 #17).</t>
+        </is>
+      </c>
+      <c r="F185" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="6" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>tasks</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D186" s="9" t="inlineStr">
@@ -12177,7 +12153,7 @@
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>Task-level detail (location, product, quantity, status per pick) is not exposed on the pickLists API — needed for progress boards and pick-path optimisation.</t>
+          <t>REVISED (docs/05 #17): BF salesChannel has CRUD — our facade write-mapping + live verification is pending.</t>
         </is>
       </c>
       <c r="F186" s="8" t="inlineStr"/>
@@ -12185,17 +12161,17 @@
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>tasks.status</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read, create, update</t>
         </is>
       </c>
       <c r="D187" s="9" t="inlineStr">
@@ -12205,7 +12181,7 @@
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Granular task-level pick confirmation with quantity + scans (docs/05 #3) — today only whole-list start/complete exists.</t>
+          <t>The channel type (shop/marketplace/direct/pos) is not on the BF salesChannel record — needed for channel-specific routing.</t>
         </is>
       </c>
       <c r="F187" s="8" t="inlineStr"/>
@@ -12213,73 +12189,81 @@
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>list, read</t>
-        </is>
-      </c>
-      <c r="D188" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D188" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>Batches exist only as read-only v3 Product includes — no batch resource, no list, no detail (docs/05 #4). GET /v3/batches is the ask.</t>
-        </is>
-      </c>
-      <c r="F188" s="8" t="inlineStr"/>
+          <t>Enable/disable state is not on the BF salesChannel record.</t>
+        </is>
+      </c>
+      <c r="F188" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>bestBefore</t>
+          <t>sync</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D189" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D189" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Correcting a best-before date via API — internal web routes only today.</t>
-        </is>
-      </c>
-      <c r="F189" s="8" t="inlineStr"/>
+          <t>Channel sync-run status (last run, success/failure) is not exposed — needed to monitor shop imports (docs/05 #17, still open after the BF salesChannel entity covered the list).</t>
+        </is>
+      </c>
+      <c r="F189" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>assignee</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D190" s="9" t="inlineStr">
@@ -12289,7 +12273,7 @@
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>Blocking/releasing a batch (quality hold) via API — maintenance happens only through internal web routes today.</t>
+          <t>The one thing that would make a task a work item. `assignee` is readOnly upstream: a create or update carrying it answers 2xx and leaves the field null. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F190" s="8" t="inlineStr"/>
@@ -12297,17 +12281,17 @@
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>trace</t>
+          <t>dates.completed</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D191" s="9" t="inlineStr">
@@ -12317,7 +12301,7 @@
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Batch trace (which goods receipts brought it in, which delivery notes shipped it — recall scenario) has no API at all (docs/05 #4).</t>
+          <t>Completing a task through the API does not stamp its completion date: `status: completed` persists, `completionDate` stays null.</t>
         </is>
       </c>
       <c r="F191" s="8" t="inlineStr"/>
@@ -12325,12 +12309,12 @@
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>timeline</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
@@ -12338,260 +12322,20 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D192" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+      <c r="D192" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>The platform kind (shopify/amazon/…) is not exposed — the BF salesChannel entity carries only a name (05 #17).</t>
-        </is>
-      </c>
-      <c r="F192" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="6" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B193" s="6" t="inlineStr">
-        <is>
-          <t>defaults</t>
-        </is>
-      </c>
-      <c r="C193" s="6" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D193" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
-        </is>
-      </c>
-      <c r="E193" s="8" t="inlineStr">
-        <is>
-          <t>Channel defaults (price list, warehouse) are not exposed (05 #17).</t>
-        </is>
-      </c>
-      <c r="F193" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="6" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B194" s="6" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C194" s="6" t="inlineStr">
-        <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D194" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E194" s="8" t="inlineStr">
-        <is>
-          <t>REVISED (docs/05 #17): BF salesChannel has CRUD — our facade write-mapping + live verification is pending.</t>
-        </is>
-      </c>
-      <c r="F194" s="8" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="6" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B195" s="6" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C195" s="6" t="inlineStr">
-        <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D195" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E195" s="8" t="inlineStr">
-        <is>
-          <t>The channel type (shop/marketplace/direct/pos) is not on the BF salesChannel record — needed for channel-specific routing.</t>
-        </is>
-      </c>
-      <c r="F195" s="8" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="6" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B196" s="6" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C196" s="6" t="inlineStr">
-        <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D196" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
-        </is>
-      </c>
-      <c r="E196" s="8" t="inlineStr">
-        <is>
-          <t>Enable/disable state is not on the BF salesChannel record.</t>
-        </is>
-      </c>
-      <c r="F196" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="6" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B197" s="6" t="inlineStr">
-        <is>
-          <t>sync</t>
-        </is>
-      </c>
-      <c r="C197" s="6" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D197" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
-        </is>
-      </c>
-      <c r="E197" s="8" t="inlineStr">
-        <is>
-          <t>Channel sync-run status (last run, success/failure) is not exposed — needed to monitor shop imports (docs/05 #17, still open after the BF salesChannel entity covered the list).</t>
-        </is>
-      </c>
-      <c r="F197" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="6" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B198" s="6" t="inlineStr">
-        <is>
-          <t>assignee</t>
-        </is>
-      </c>
-      <c r="C198" s="6" t="inlineStr">
-        <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D198" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E198" s="8" t="inlineStr">
-        <is>
-          <t>The one thing that would make a task a work item. `assignee` is readOnly upstream: a create or update carrying it answers 2xx and leaves the field null. Measured on mvp 2026-08-02.</t>
-        </is>
-      </c>
-      <c r="F198" s="8" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="6" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B199" s="6" t="inlineStr">
-        <is>
-          <t>dates.completed</t>
-        </is>
-      </c>
-      <c r="C199" s="6" t="inlineStr">
-        <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D199" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E199" s="8" t="inlineStr">
-        <is>
-          <t>Completing a task through the API does not stamp its completion date: `status: completed` persists, `completionDate` stays null.</t>
-        </is>
-      </c>
-      <c r="F199" s="8" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="6" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B200" s="6" t="inlineStr">
-        <is>
-          <t>timeline</t>
-        </is>
-      </c>
-      <c r="C200" s="6" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D200" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
-        </is>
-      </c>
-      <c r="E200" s="8" t="inlineStr">
-        <is>
           <t>The task's comment thread. Declared `readWrite` with a full sub-node and returned by NO read — not the list, not the single read, and no include/expand parameter produces it. Not modelled until it reads back.</t>
         </is>
       </c>
-      <c r="F200" s="8" t="inlineStr"/>
+      <c r="F192" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F200"/>
+  <autoFilter ref="A1:F192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Übersicht'!$A$6:$H$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fähigkeiten'!$A$1:$F$181</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Felder'!$A$1:$F$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Felder'!$A$1:$F$184</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,7 +590,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F192"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7106,29 +7106,25 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>addresses.label</t>
+          <t>defaults.paymentMethod</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Free label/name per address location (e.g. 'Lager München') — v3 knows only billing/shipping roles, no named locations.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read · Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Default payment method per customer.</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -7138,29 +7134,25 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>addresses.isDefault</t>
+          <t>defaults.paymentTerms.dueDays</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Mark the standard address per type (unified-address model; at most one default per customer &amp; type) — v3 partner addresses carry no isDefault flag.</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read · Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Default payment term for the customer — drives every order/invoice; must be settable.</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -7170,7 +7162,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>defaults.paymentMethod</t>
+          <t>defaults.taxation</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -7185,7 +7177,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Default payment method per customer.</t>
+          <t>Default taxation scheme (domestic/euB2B/euOss/export) per customer.</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr"/>
@@ -7198,12 +7190,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>defaults.paymentTerms.dueDays</t>
+          <t>defaults.shippingMethod</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, update</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -7213,7 +7205,7 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Default payment term for the customer — drives every order/invoice; must be settable.</t>
+          <t>The default shipping method is not surfaced by the v3 partner read.</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr"/>
@@ -7226,12 +7218,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>defaults.taxation</t>
+          <t>defaults.priceList</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, update</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -7241,7 +7233,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Default taxation scheme (domestic/euB2B/euOss/export) per customer.</t>
+          <t>The assigned price list is not surfaced by the v3 partner read.</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr"/>
@@ -7254,7 +7246,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>defaults.shippingMethod</t>
+          <t>defaults.partialShipping</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -7269,7 +7261,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>The default shipping method is not surfaced by the v3 partner read.</t>
+          <t>The partial-shipping preference is not surfaced by the v3 partner read.</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr"/>
@@ -7282,12 +7274,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>defaults.priceList</t>
+          <t>finance.openAmount</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -7297,7 +7289,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>The assigned price list is not surfaced by the v3 partner read.</t>
+          <t>Aggregated open amount per customer is computed nowhere in the API (docs/05 #14) — must be derived/served.</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr"/>
@@ -7310,12 +7302,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>defaults.partialShipping</t>
+          <t>finance.creditLimit</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -7325,7 +7317,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>The partial-shipping preference is not surfaced by the v3 partner read.</t>
+          <t>The customer credit limit — a core AR control; UI-only today, not writable via API (docs/05 #14).</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr"/>
@@ -7338,12 +7330,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>finance.openAmount</t>
+          <t>finance.onHold</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -7353,7 +7345,7 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Aggregated open amount per customer is computed nowhere in the API (docs/05 #14) — must be derived/served.</t>
+          <t>Put a customer on delivery/credit hold — UI-only today (docs/05 #14).</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr"/>
@@ -7366,7 +7358,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>finance.creditLimit</t>
+          <t>finance.dunningBlocked</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -7381,7 +7373,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>The customer credit limit — a core AR control; UI-only today, not writable via API (docs/05 #14).</t>
+          <t>Block dunning for a customer — UI-only today.</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr"/>
@@ -7394,12 +7386,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>finance.onHold</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -7409,7 +7401,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Put a customer on delivery/credit hold — UI-only today (docs/05 #14).</t>
+          <t>Custom field values on the customer — today only readable, not writable via API.</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr"/>
@@ -7422,22 +7414,22 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>finance.dunningBlocked</t>
+          <t>contacts.address</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Block dunning for a customer — UI-only today.</t>
+          <t>Bind a contact person to a specific address (person-at-location) — v3 stores only a free-text contactPerson on delivery addresses, not a reference.</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr"/>
@@ -7450,22 +7442,22 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>contacts.isPrimary</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the customer — today only readable, not writable via API.</t>
+          <t>Mark the main contact person — v3 contactPersons carry no primary flag.</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr"/>
@@ -7473,27 +7465,27 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>contacts.address</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Bind a contact person to a specific address (person-at-location) — v3 stores only a free-text contactPerson on delivery addresses, not a reference.</t>
+          <t>Carrying a quote number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr"/>
@@ -7501,27 +7493,27 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>contacts.isPrimary</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Mark the main contact person — v3 contactPersons carry no primary flag.</t>
+          <t>Reassign the quote's partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr"/>
@@ -7534,12 +7526,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>references.customerInquiryNumber</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
@@ -7549,7 +7541,7 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Carrying a quote number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+          <t>The customer's inquiry / RFQ number — B2B standard; read-only upstream today.</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr"/>
@@ -7562,12 +7554,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>dates.validUntil</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
@@ -7577,7 +7569,7 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Reassign the quote's partner after creation — v3 accepts it only on create.</t>
+          <t>Offer validity date — drives auto-expiry and follow-up; must be settable per quote.</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr"/>
@@ -7590,7 +7582,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>references.customerInquiryNumber</t>
+          <t>dates.expectedOrderDate</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -7605,7 +7597,7 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>The customer's inquiry / RFQ number — B2B standard; read-only upstream today.</t>
+          <t>Expected order date feeds the sales forecast — settable per quote.</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr"/>
@@ -7618,7 +7610,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>dates.validUntil</t>
+          <t>dates.requestedDelivery</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -7633,7 +7625,7 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Offer validity date — drives auto-expiry and follow-up; must be settable per quote.</t>
+          <t>Desired delivery date on the quote — not writable upstream today.</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr"/>
@@ -7646,7 +7638,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>dates.expectedOrderDate</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -7661,7 +7653,7 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Expected order date feeds the sales forecast — settable per quote.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
@@ -7674,7 +7666,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>dates.requestedDelivery</t>
+          <t>items.isOptional</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -7689,7 +7681,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Desired delivery date on the quote — not writable upstream today.</t>
+          <t>Optional line items (not counted in totals) are a core quoting feature — not settable upstream today.</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr"/>
@@ -7702,7 +7694,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>payment.method</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -7717,7 +7709,7 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Payment method proposed on the quote — frequently set per offer.</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr"/>
@@ -7730,7 +7722,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>items.isOptional</t>
+          <t>payment.terms.dueDays</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -7745,7 +7737,7 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Optional line items (not counted in totals) are a core quoting feature — not settable upstream today.</t>
+          <t>Payment term proposed on the quote.</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr"/>
@@ -7758,7 +7750,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>payment.method</t>
+          <t>shipping.method</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -7766,17 +7758,21 @@
           <t>create, update</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Payment method proposed on the quote — frequently set per offer.</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr"/>
+          <t>Shipping method proposed on the quote.</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create, update</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -7786,7 +7782,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>payment.terms.dueDays</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -7801,7 +7797,7 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Payment term proposed on the quote.</t>
+          <t>Custom field values on the quote — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr"/>
@@ -7814,44 +7810,40 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>shipping.method</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Shipping method proposed on the quote.</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>SalesOrder</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
@@ -7861,7 +7853,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the quote — today only readable via include, not writable via API.</t>
+          <t>Correcting a sales order number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr"/>
@@ -7869,27 +7861,27 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>SalesOrder</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+          <t>Reassign the order to the correct customer after creation — v3 accepts the partner only on create today.</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr"/>
@@ -7902,25 +7894,29 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Correcting a sales order number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr"/>
+          <t>The customer's own order / PO number (B2B standard field). Read-only upstream today; a clerk must be able to set and correct it.</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -7930,12 +7926,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>references.externalId</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
@@ -7945,7 +7941,7 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Reassign the order to the correct customer after creation — v3 accepts the partner only on create today.</t>
+          <t>Automated reconciliation matches by the external id.</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr"/>
@@ -7958,12 +7954,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>dates.requestedDelivery</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -7973,12 +7969,12 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>The customer's own order / PO number (B2B standard field). Read-only upstream today; a clerk must be able to set and correct it.</t>
+          <t>Desired delivery date — core fulfilment field; one of the first things entered on an order. Not writable upstream today.</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Schema deklariert: create</t>
+          <t>Schema deklariert: update</t>
         </is>
       </c>
     </row>
@@ -7990,12 +7986,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>references.externalId</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
@@ -8005,7 +8001,7 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Automated reconciliation matches by the external id.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr"/>
@@ -8018,12 +8014,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>dates.requestedDelivery</t>
+          <t>shipping.method</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
@@ -8033,12 +8029,12 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Desired delivery date — core fulfilment field; one of the first things entered on an order. Not writable upstream today.</t>
+          <t>Carrier / shipping method — core to fulfilment; must be selectable per order.</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Schema deklariert: update</t>
+          <t>Schema deklariert: create, update</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8046,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>fulfillmentPolicy.partialShipping</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -8065,7 +8061,7 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Partial-shipping policy has no upstream slot — the read reports a hardcoded "allowed". Needs a real v3 field before it can be written or trusted.</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr"/>
@@ -8078,29 +8074,25 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>shipping.method</t>
+          <t>discounts</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Carrier / shipping method — core to fulfilment; must be selectable per order.</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Header discounts/vouchers (e-commerce) are not exposed by v3 salesOrders — only line-level discounts exist.</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -8110,7 +8102,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>fulfillmentPolicy.partialShipping</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -8125,7 +8117,7 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Partial-shipping policy has no upstream slot — the read reports a hardcoded "allowed". Needs a real v3 field before it can be written or trusted.</t>
+          <t>Custom field values carry company-specific data — today only readable via include, not writable via API (all documents).</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr"/>
@@ -8138,12 +8130,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>discounts</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -8153,7 +8145,7 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Header discounts/vouchers (e-commerce) are not exposed by v3 salesOrders — only line-level discounts exist.</t>
+          <t>Companies segment and find orders by their own custom-field values.</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr"/>
@@ -8166,22 +8158,22 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Custom field values carry company-specific data — today only readable via include, not writable via API (all documents).</t>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr"/>
@@ -8189,17 +8181,17 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>SalesOrder</t>
+          <t>DeliveryNote</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -8209,7 +8201,7 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Companies segment and find orders by their own custom-field values.</t>
+          <t>Carrying a delivery note number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr"/>
@@ -8217,27 +8209,27 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>SalesOrder</t>
+          <t>DeliveryNote</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+          <t>Reassign the delivery note's partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr"/>
@@ -8250,7 +8242,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -8258,17 +8250,21 @@
           <t>create</t>
         </is>
       </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Carrying a delivery note number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="inlineStr"/>
+          <t>The customer's PO number on the delivery note (B2B) — read-only upstream today; must be settable.</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -8278,12 +8274,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
@@ -8293,7 +8289,7 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>Reassign the delivery note's partner after creation — v3 accepts it only on create.</t>
+          <t>Warehouse/support find a delivery note by the customer's PO number.</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr"/>
@@ -8306,29 +8302,25 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>The customer's PO number on the delivery note (B2B) — read-only upstream today; must be settable.</t>
-        </is>
-      </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>The picking/shipping warehouse — must be selectable per delivery note, not fixed to the default.</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -8338,12 +8330,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
@@ -8353,7 +8345,7 @@
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>Warehouse/support find a delivery note by the customer's PO number.</t>
+          <t>Adjust delivered positions/quantities after creation — the v3 update DTO carries no line-item write path.</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr"/>
@@ -8366,12 +8358,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>shipments</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -8381,7 +8373,7 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>The picking/shipping warehouse — must be selectable per delivery note, not fixed to the default.</t>
+          <t>Tracking numbers need a nachlade GET /v1/deliveryNotes/{id}/shipments — not yet composed into the read payload.</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr"/>
@@ -8394,12 +8386,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>customs.totalWeight</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
@@ -8409,7 +8401,7 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Adjust delivered positions/quantities after creation — the v3 update DTO carries no line-item write path.</t>
+          <t>Total shipment weight for the customs declaration / carrier — needs to be settable.</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr"/>
@@ -8422,12 +8414,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>shipments</t>
+          <t>customs.incoterm</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -8437,7 +8429,7 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Tracking numbers need a nachlade GET /v1/deliveryNotes/{id}/shipments — not yet composed into the read payload.</t>
+          <t>Incoterm for export shipments — a customs-declaration essential, not settable via API today.</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr"/>
@@ -8450,7 +8442,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>customs.totalWeight</t>
+          <t>customs.note</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -8465,7 +8457,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Total shipment weight for the customs declaration / carrier — needs to be settable.</t>
+          <t>Customs note for export paperwork.</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr"/>
@@ -8478,7 +8470,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>customs.incoterm</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -8493,7 +8485,7 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Incoterm for export shipments — a customs-declaration essential, not settable via API today.</t>
+          <t>Custom field values on the delivery note — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr"/>
@@ -8501,17 +8493,17 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>DeliveryNote</t>
+          <t>Shipment</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>customs.note</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
@@ -8521,7 +8513,7 @@
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Customs note for export paperwork.</t>
+          <t>Creating a shipment + label via the facade (POST /v1/shipments + createLabel exists upstream) is not orchestrated here yet — needed for headless fulfilment.</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr"/>
@@ -8529,17 +8521,17 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>DeliveryNote</t>
+          <t>Shipment</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
@@ -8549,7 +8541,7 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the delivery note — today only readable via include, not writable via API.</t>
+          <t>The shipment lifecycle status is not exposed by v1 shipments — only sentAt exists.</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr"/>
@@ -8562,12 +8554,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
@@ -8577,7 +8569,7 @@
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>Creating a shipment + label via the facade (POST /v1/shipments + createLabel exists upstream) is not orchestrated here yet — needed for headless fulfilment.</t>
+          <t>Package weight is not exposed by v1 shipments.</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr"/>
@@ -8590,7 +8582,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>events</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -8605,7 +8597,7 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>The shipment lifecycle status is not exposed by v1 shipments — only sentAt exists.</t>
+          <t>Carrier tracking events are not exposed — needs a carrier-events feed.</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr"/>
@@ -8618,12 +8610,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>tracking.number</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
@@ -8633,7 +8625,7 @@
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Package weight is not exposed by v1 shipments.</t>
+          <t>Support looks up a shipment by tracking number — needs a filterable/searchable upstream list parameter.</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr"/>
@@ -8641,17 +8633,17 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Shipment</t>
+          <t>SalesInvoice</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>events</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
@@ -8661,7 +8653,7 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Carrier tracking events are not exposed — needs a carrier-events feed.</t>
+          <t>Correcting a invoice number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr"/>
@@ -8669,17 +8661,17 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>Shipment</t>
+          <t>SalesInvoice</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>tracking.number</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
@@ -8689,7 +8681,7 @@
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Support looks up a shipment by tracking number — needs a filterable/searchable upstream list parameter.</t>
+          <t>Reassign the invoice's partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr"/>
@@ -8702,25 +8694,29 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Correcting a invoice number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="inlineStr"/>
+          <t>The customer's PO number on the invoice (B2B) — read-only upstream today; must be settable and correctable.</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -8730,12 +8726,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -8745,7 +8741,7 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Reassign the invoice's partner after creation — v3 accepts it only on create.</t>
+          <t>Support and accounting find invoices by the customer's PO number.</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr"/>
@@ -8758,29 +8754,25 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>references.debtorAccountNumber</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="D67" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>The customer's PO number on the invoice (B2B) — read-only upstream today; must be settable and correctable.</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Deviating debtor account for the FiBu/DATEV export — settable when it differs from the customer default.</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -8790,12 +8782,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -8805,7 +8797,7 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Support and accounting find invoices by the customer's PO number.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr"/>
@@ -8818,25 +8810,29 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>references.debtorAccountNumber</t>
+          <t>totals.outstanding</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Deviating debtor account for the FiBu/DATEV export — settable when it differs from the customer default.</t>
-        </is>
-      </c>
-      <c r="F69" s="8" t="inlineStr"/>
+          <t>Exact open amount needs readable payment↔invoice allocations (docs/05 #2); today only derived from paymentStatus.</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -8846,7 +8842,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>payment.method</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -8861,7 +8857,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Payment method on the invoice — central to order-to-cash; frequently overridden.</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr"/>
@@ -8874,29 +8870,25 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>totals.outstanding</t>
+          <t>payment.terms.dueDays</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D71" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Exact open amount needs readable payment↔invoice allocations (docs/05 #2); today only derived from paymentStatus.</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>Net payment term in days — drives the due date and dunning.</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -8906,7 +8898,7 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>payment.method</t>
+          <t>payment.terms.discountPercent</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
@@ -8921,7 +8913,7 @@
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Payment method on the invoice — central to order-to-cash; frequently overridden.</t>
+          <t>Cash-discount percentage — standard DACH B2B.</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr"/>
@@ -8934,7 +8926,7 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>payment.terms.dueDays</t>
+          <t>payment.terms.discountDays</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -8949,7 +8941,7 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Net payment term in days — drives the due date and dunning.</t>
+          <t>Cash-discount period in days — pairs with the discount.</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr"/>
@@ -8962,25 +8954,29 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>payment.terms.discountPercent</t>
+          <t>eInvoice</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Cash-discount percentage — standard DACH B2B.</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr"/>
+          <t>The finished ZUGFeRD/XRechnung artefact + delivery status is a missing upstream API (docs/05 #7) — only XML raw data exists today.</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -8990,7 +8986,7 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>payment.terms.discountDays</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -9005,7 +9001,7 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Cash-discount period in days — pairs with the discount.</t>
+          <t>Custom field values on the invoice — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr"/>
@@ -9018,7 +9014,7 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>eInvoice</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
@@ -9026,36 +9022,32 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D76" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>The finished ZUGFeRD/XRechnung artefact + delivery status is a missing upstream API (docs/05 #7) — only XML raw data exists today.</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
@@ -9065,7 +9057,7 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the invoice — today only readable via include, not writable via API.</t>
+          <t>No payment LIST/filter exists upstream — only GET /paymentTransactions/{id} (docs/05 #2). GET /v3/payments with filters is the ask.</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr"/>
@@ -9073,12 +9065,12 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
@@ -9086,14 +9078,14 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D78" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+          <t>Payout/settlement aggregation (fees, chargebacks) per provider needs docs/05 #8.</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr"/>
@@ -9106,12 +9098,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>allocations</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>read, update</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -9121,7 +9113,7 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>No payment LIST/filter exists upstream — only GET /paymentTransactions/{id} (docs/05 #2). GET /v3/payments with filters is the ask.</t>
+          <t>Payment↔invoice allocations (n:m) are neither readable nor writable — without them exact outstanding amounts are impossible (docs/05 #2).</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr"/>
@@ -9129,17 +9121,17 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -9149,7 +9141,7 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Payout/settlement aggregation (fees, chargebacks) per provider needs docs/05 #8.</t>
+          <t>Carrying a return number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr"/>
@@ -9157,17 +9149,17 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>allocations</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
@@ -9177,7 +9169,7 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Payment↔invoice allocations (n:m) are neither readable nor writable — without them exact outstanding amounts are impossible (docs/05 #2).</t>
+          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr"/>
@@ -9190,12 +9182,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>references.rmaNumber</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
@@ -9205,7 +9197,7 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Carrying a return number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+          <t>The RMA number the customer quotes — no upstream field today; core to returns handling.</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr"/>
@@ -9218,12 +9210,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>references.rmaNumber</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
@@ -9233,7 +9225,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
+          <t>Support finds a return by the RMA number the customer has.</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr"/>
@@ -9246,7 +9238,7 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>references.rmaNumber</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
@@ -9261,7 +9253,7 @@
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>The RMA number the customer quotes — no upstream field today; core to returns handling.</t>
+          <t>The customer's PO number on the return — read-only upstream today.</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr"/>
@@ -9274,12 +9266,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>references.rmaNumber</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
@@ -9289,7 +9281,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Support finds a return by the RMA number the customer has.</t>
+          <t>The returns warehouse must be selectable per return.</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr"/>
@@ -9302,12 +9294,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
@@ -9317,7 +9309,7 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>The customer's PO number on the return — read-only upstream today.</t>
+          <t>Edit return positions after creation — the v3 update DTO carries no line-item write path.</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr"/>
@@ -9330,7 +9322,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>items.reason</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -9338,17 +9330,21 @@
           <t>create, update</t>
         </is>
       </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>The returns warehouse must be selectable per return.</t>
-        </is>
-      </c>
-      <c r="F87" s="8" t="inlineStr"/>
+          <t>The return reason per line — essential for returns analytics; not settable via API today.</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
@@ -9358,12 +9354,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>items.condition</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
@@ -9373,7 +9369,7 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Edit return positions after creation — the v3 update DTO carries no line-item write path.</t>
+          <t>Item condition (resellable/damaged/disposal) drives restocking — not in the v3 payload yet.</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr"/>
@@ -9386,29 +9382,25 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>items.reason</t>
+          <t>items.condition</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D89" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>The return reason per line — essential for returns analytics; not settable via API today.</t>
-        </is>
-      </c>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Item condition is not surfaced by the v3 return payload yet (docs/05 #4 batch/trace family).</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -9418,7 +9410,7 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>items.condition</t>
+          <t>items.action</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
@@ -9433,7 +9425,7 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>Item condition (resellable/damaged/disposal) drives restocking — not in the v3 payload yet.</t>
+          <t>Resolution per line (credit/replace/repair) — not in the v3 payload yet.</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr"/>
@@ -9446,12 +9438,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>items.condition</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
@@ -9461,7 +9453,7 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Item condition is not surfaced by the v3 return payload yet (docs/05 #4 batch/trace family).</t>
+          <t>Custom field values on the return — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr"/>
@@ -9469,17 +9461,17 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>items.action</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
@@ -9489,7 +9481,7 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Resolution per line (credit/replace/repair) — not in the v3 payload yet.</t>
+          <t>Correcting a credit note number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr"/>
@@ -9497,17 +9489,17 @@
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -9517,7 +9509,7 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the return — today only readable via include, not writable via API.</t>
+          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr"/>
@@ -9530,25 +9522,29 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Correcting a credit note number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
-        </is>
-      </c>
-      <c r="F94" s="8" t="inlineStr"/>
+          <t>The customer's PO number on the credit note (B2B) — read-only upstream today.</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
@@ -9558,12 +9554,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>references.debtorAccountNumber</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
@@ -9573,7 +9569,7 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
+          <t>Deviating debtor account for the FiBu/DATEV export of the credit note.</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr"/>
@@ -9586,29 +9582,25 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>dates.serviceDate</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="D96" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>The customer's PO number on the credit note (B2B) — read-only upstream today.</t>
-        </is>
-      </c>
-      <c r="F96" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Leistungsdatum — a §14 UStG mandatory field on the credit note; must be settable.</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
@@ -9618,7 +9610,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>references.debtorAccountNumber</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -9633,7 +9625,7 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Deviating debtor account for the FiBu/DATEV export of the credit note.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr"/>
@@ -9646,25 +9638,29 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>dates.serviceDate</t>
+          <t>totals.outstanding</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Leistungsdatum — a §14 UStG mandatory field on the credit note; must be settable.</t>
-        </is>
-      </c>
-      <c r="F98" s="8" t="inlineStr"/>
+          <t>Exact open amount needs readable refund/offset allocations (docs/05 #2); today derived from paymentStatus only.</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
@@ -9674,7 +9670,7 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>settlement.mode</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -9689,7 +9685,7 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Refund vs offset-against-invoice is a per-credit-note decision — not settable upstream today.</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr"/>
@@ -9702,29 +9698,25 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>totals.outstanding</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D100" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Exact open amount needs readable refund/offset allocations (docs/05 #2); today derived from paymentStatus only.</t>
-        </is>
-      </c>
-      <c r="F100" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>Custom field values on the credit note — today only readable via include, not writable via API.</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
@@ -9734,22 +9726,22 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>settlement.mode</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D101" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Refund vs offset-against-invoice is a per-credit-note decision — not settable upstream today.</t>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr"/>
@@ -9757,17 +9749,17 @@
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, update</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
@@ -9777,7 +9769,7 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the credit note — today only readable via include, not writable via API.</t>
+          <t>Active/archived state is not exposed via v3 suppliers — needed for honest archiving (plan §6.1).</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr"/>
@@ -9785,27 +9777,27 @@
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D103" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>read, update</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+          <t>B2B hierarchy (branch → HQ) is not exposed via the public API (plan §6.1 parent).</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr"/>
@@ -9818,7 +9810,7 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>billTo</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -9833,7 +9825,7 @@
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Active/archived state is not exposed via v3 suppliers — needed for honest archiving (plan §6.1).</t>
+          <t>Central billing (Zentralregulierung — invoice to association/HQ) is not exposed (plan §6.1 billTo).</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr"/>
@@ -9846,12 +9838,12 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>channels</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
@@ -9861,7 +9853,7 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>B2B hierarchy (branch → HQ) is not exposed via the public API (plan §6.1 parent).</t>
+          <t>Per-channel external ids (channel links) are not exposed via the public API.</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr"/>
@@ -9874,12 +9866,12 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>billTo</t>
+          <t>purchasing.confirmationRequired</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
@@ -9889,7 +9881,7 @@
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Central billing (Zentralregulierung — invoice to association/HQ) is not exposed (plan §6.1 billTo).</t>
+          <t>Whether an order confirmation (AB) is required from this supplier — drives purchasing workflow; not settable via API today.</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr"/>
@@ -9902,12 +9894,12 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>channels</t>
+          <t>purchasing.sendOrdersVia</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
@@ -9917,7 +9909,7 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Per-channel external ids (channel links) are not exposed via the public API.</t>
+          <t>How POs are sent to the supplier (email/portal/EDI) — a supplier default that must be settable.</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr"/>
@@ -9930,7 +9922,7 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>purchasing.confirmationRequired</t>
+          <t>purchasing.deliveryDays</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
@@ -9945,7 +9937,7 @@
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Whether an order confirmation (AB) is required from this supplier — drives purchasing workflow; not settable via API today.</t>
+          <t>Standard supplier lead time in days — feeds replenishment planning.</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr"/>
@@ -9958,7 +9950,7 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>purchasing.sendOrdersVia</t>
+          <t>addresses.type</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -9966,17 +9958,21 @@
           <t>create, update</t>
         </is>
       </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>How POs are sent to the supplier (email/portal/EDI) — a supplier default that must be settable.</t>
-        </is>
-      </c>
-      <c r="F109" s="8" t="inlineStr"/>
+          <t>Set the address role incl. the 'both' value (one address serving billing AND shipping) — v3 splits billing (primaryAddress/deviating) vs shipping (deliveryAddresses) by store, so the role is not a freely settable field.</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create, update</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
@@ -9986,12 +9982,12 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>purchasing.deliveryDays</t>
+          <t>defaults.shippingMethod</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, update</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
@@ -10001,7 +9997,7 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Standard supplier lead time in days — feeds replenishment planning.</t>
+          <t>The default shipping method is not surfaced by the v3 partner read.</t>
         </is>
       </c>
       <c r="F110" s="8" t="inlineStr"/>
@@ -10014,29 +10010,25 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>addresses.type</t>
+          <t>defaults.priceList</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D111" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>read, update</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Set the address role incl. the 'both' value (one address serving billing AND shipping) — v3 splits billing (primaryAddress/deviating) vs shipping (deliveryAddresses) by store, so the role is not a freely settable field.</t>
-        </is>
-      </c>
-      <c r="F111" s="8" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>The assigned price list is not surfaced by the v3 partner read.</t>
+        </is>
+      </c>
+      <c r="F111" s="8" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -10046,29 +10038,25 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>addresses.label</t>
+          <t>defaults.partialShipping</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D112" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>read, update</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Free label/name per address location (e.g. 'Lager München') — v3 knows only billing/shipping roles, no named locations.</t>
-        </is>
-      </c>
-      <c r="F112" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read · Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>The partial-shipping preference is not surfaced by the v3 partner read.</t>
+        </is>
+      </c>
+      <c r="F112" s="8" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
@@ -10078,29 +10066,25 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>addresses.isDefault</t>
+          <t>defaults.paymentTerms.dueDays</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D113" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Mark the standard address per type (unified-address model; at most one default per customer &amp; type) — v3 partner addresses carry no isDefault flag.</t>
-        </is>
-      </c>
-      <c r="F113" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read · Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Default supplier payment term — drives liability due dates.</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
@@ -10110,12 +10094,12 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>defaults.shippingMethod</t>
+          <t>finance.openAmount</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
@@ -10125,7 +10109,7 @@
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>The default shipping method is not surfaced by the v3 partner read.</t>
+          <t>Aggregated open liabilities per supplier are computed nowhere in the API — must be derived/served.</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr"/>
@@ -10138,12 +10122,12 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>defaults.priceList</t>
+          <t>finance.creditorAccountNumber</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
@@ -10153,7 +10137,7 @@
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>The assigned price list is not surfaced by the v3 partner read.</t>
+          <t>The creditor account for the FiBu/DATEV export — settable per supplier.</t>
         </is>
       </c>
       <c r="F115" s="8" t="inlineStr"/>
@@ -10166,12 +10150,12 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>defaults.partialShipping</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
@@ -10181,7 +10165,7 @@
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>The partial-shipping preference is not surfaced by the v3 partner read.</t>
+          <t>Custom field values on the supplier — today only readable, not writable via API.</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr"/>
@@ -10194,22 +10178,22 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>defaults.paymentTerms.dueDays</t>
+          <t>contacts.address</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Default supplier payment term — drives liability due dates.</t>
+          <t>Bind a contact person to a specific address (person-at-location) — v3 stores only a free-text contactPerson on delivery addresses, not a reference.</t>
         </is>
       </c>
       <c r="F117" s="8" t="inlineStr"/>
@@ -10222,22 +10206,22 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>finance.openAmount</t>
+          <t>contacts.isPrimary</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Aggregated open liabilities per supplier are computed nowhere in the API — must be derived/served.</t>
+          <t>Mark the main contact person — v3 contactPersons carry no primary flag.</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr"/>
@@ -10245,17 +10229,17 @@
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>finance.creditorAccountNumber</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
@@ -10265,7 +10249,7 @@
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>The creditor account for the FiBu/DATEV export — settable per supplier.</t>
+          <t>Carrying a purchase order number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
         </is>
       </c>
       <c r="F119" s="8" t="inlineStr"/>
@@ -10273,17 +10257,17 @@
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>supplier</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
@@ -10293,7 +10277,7 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the supplier — today only readable, not writable via API.</t>
+          <t>Reassign the PO's supplier after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F120" s="8" t="inlineStr"/>
@@ -10301,27 +10285,27 @@
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>contacts.address</t>
+          <t>references.ourCustomerNumber</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D121" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Bind a contact person to a specific address (person-at-location) — v3 stores only a free-text contactPerson on delivery addresses, not a reference.</t>
+          <t>Our customer number at the supplier — belongs on the PO, not settable via API today.</t>
         </is>
       </c>
       <c r="F121" s="8" t="inlineStr"/>
@@ -10329,27 +10313,27 @@
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>contacts.isPrimary</t>
+          <t>references.supplierOfferNumber</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D122" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Mark the main contact person — v3 contactPersons carry no primary flag.</t>
+          <t>The supplier's quote number we ordered against — read-only upstream today.</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr"/>
@@ -10362,12 +10346,12 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>confirmation.status</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
@@ -10377,7 +10361,7 @@
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Carrying a purchase order number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+          <t>Recording the confirmation status (pending/confirmed/deviating) is core purchasing — not writable via API today.</t>
         </is>
       </c>
       <c r="F123" s="8" t="inlineStr"/>
@@ -10390,7 +10374,7 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>supplier</t>
+          <t>confirmation.supplierOrderNumber</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
@@ -10405,7 +10389,7 @@
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Reassign the PO's supplier after creation — v3 accepts it only on create.</t>
+          <t>The AB (order-confirmation) number from the supplier — the whole confirmation block is read-only upstream (docs/05: AB handling).</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr"/>
@@ -10418,7 +10402,7 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>references.ourCustomerNumber</t>
+          <t>dates.requestedDelivery</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
@@ -10433,7 +10417,7 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Our customer number at the supplier — belongs on the PO, not settable via API today.</t>
+          <t>Requested delivery date at the supplier — not writable upstream today.</t>
         </is>
       </c>
       <c r="F125" s="8" t="inlineStr"/>
@@ -10446,7 +10430,7 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>references.supplierOfferNumber</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
@@ -10461,7 +10445,7 @@
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>The supplier's quote number we ordered against — read-only upstream today.</t>
+          <t>The receiving warehouse for the PO must be selectable.</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr"/>
@@ -10474,7 +10458,7 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>confirmation.status</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -10489,7 +10473,7 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Recording the confirmation status (pending/confirmed/deviating) is core purchasing — not writable via API today.</t>
+          <t>Edit PO positions after creation — the v3 update DTO carries no line-item write path.</t>
         </is>
       </c>
       <c r="F127" s="8" t="inlineStr"/>
@@ -10502,12 +10486,12 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>confirmation.supplierOrderNumber</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
@@ -10517,7 +10501,7 @@
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>The AB (order-confirmation) number from the supplier — the whole confirmation block is read-only upstream (docs/05: AB handling).</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr"/>
@@ -10530,12 +10514,12 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>dates.requestedDelivery</t>
+          <t>dropship</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, create</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
@@ -10545,7 +10529,7 @@
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Requested delivery date at the supplier — not writable upstream today.</t>
+          <t>Dropshipping (Strecke: salesOrder link + customer delivery address) is not exposed via v3 purchaseOrders.</t>
         </is>
       </c>
       <c r="F129" s="8" t="inlineStr"/>
@@ -10558,7 +10542,7 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
@@ -10573,7 +10557,7 @@
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>The receiving warehouse for the PO must be selectable.</t>
+          <t>Custom field values on the PO — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr"/>
@@ -10581,17 +10565,17 @@
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>references.supplierDeliveryNoteNumber</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update, read</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
@@ -10601,7 +10585,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Edit PO positions after creation — the v3 update DTO carries no line-item write path.</t>
+          <t>The supplier's delivery-note number on the goods receipt — needed for the three-way match; not in the BF record yet.</t>
         </is>
       </c>
       <c r="F131" s="8" t="inlineStr"/>
@@ -10609,17 +10593,17 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>dates.received</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
@@ -10629,7 +10613,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr"/>
@@ -10637,17 +10621,17 @@
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>dropship</t>
+          <t>dates.posted</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>read, create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
@@ -10657,7 +10641,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Dropshipping (Strecke: salesOrder link + customer delivery address) is not exposed via v3 purchaseOrders.</t>
+          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
         </is>
       </c>
       <c r="F133" s="8" t="inlineStr"/>
@@ -10665,17 +10649,17 @@
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
@@ -10685,7 +10669,7 @@
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Custom field values on the PO — today only readable via include, not writable via API.</t>
+          <t>Cancel/storno of a posted goods receipt — the remaining upstream gap after the BF entity list covered browsing (docs/05 #9 revised).</t>
         </is>
       </c>
       <c r="F134" s="8" t="inlineStr"/>
@@ -10698,12 +10682,12 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>references.supplierDeliveryNoteNumber</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>create, update, read</t>
+          <t>read, create, update</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
@@ -10713,7 +10697,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>The supplier's delivery-note number on the goods receipt — needed for the three-way match; not in the BF record yet.</t>
+          <t>Line items (product × quantity × storage location, quality check per line) are not exposed on the BF goodsReceipt record — creation still goes through the PO action only.</t>
         </is>
       </c>
       <c r="F135" s="8" t="inlineStr"/>
@@ -10721,17 +10705,17 @@
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>dates.received</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
@@ -10741,7 +10725,7 @@
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
+          <t>The document number is system-assigned: sending `documentNumber` on create answers 201 and the record comes back with an empty number (measured on mvp 2026-08-02). Same behaviour as the other documents.</t>
         </is>
       </c>
       <c r="F136" s="8" t="inlineStr"/>
@@ -10749,17 +10733,17 @@
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>dates.posted</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D137" s="9" t="inlineStr">
@@ -10769,7 +10753,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
+          <t>Filtering incoming invoices by workflow status is the AP daily view — the BF supplierInvoice API does not allow filtering documentStatus today.</t>
         </is>
       </c>
       <c r="F137" s="8" t="inlineStr"/>
@@ -10777,17 +10761,17 @@
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>dates.invoiceDate</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>sort</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
@@ -10797,7 +10781,7 @@
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>Cancel/storno of a posted goods receipt — the remaining upstream gap after the BF entity list covered browsing (docs/05 #9 revised).</t>
+          <t>Sorting incoming invoices by invoice date — dateOfSupplierInvoice is not sortable on the BF API today.</t>
         </is>
       </c>
       <c r="F138" s="8" t="inlineStr"/>
@@ -10805,17 +10789,17 @@
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>match.status</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>read, create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
@@ -10825,7 +10809,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Line items (product × quantity × storage location, quality check per line) are not exposed on the BF goodsReceipt record — creation still goes through the PO action only.</t>
+          <t>Re-running/overriding the match verdict via API (rematch) — the check statuses are readable now; a command to re-evaluate is still missing upstream.</t>
         </is>
       </c>
       <c r="F139" s="8" t="inlineStr"/>
@@ -10838,12 +10822,12 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>payment.status</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
@@ -10853,7 +10837,7 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>The document number is system-assigned: sending `documentNumber` on create answers 201 and the record comes back with an empty number (measured on mvp 2026-08-02). Same behaviour as the other documents.</t>
+          <t>Open-liabilities view needs filtering by payment status — not allowed on the BF supplierInvoice API today.</t>
         </is>
       </c>
       <c r="F140" s="8" t="inlineStr"/>
@@ -10866,12 +10850,12 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>approval.status</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
@@ -10881,7 +10865,7 @@
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Filtering incoming invoices by workflow status is the AP daily view — the BF supplierInvoice API does not allow filtering documentStatus today.</t>
+          <t>Approve/reject via API: BF process steps (GoodsCheck/InvoiceCheck/Payment) are reported to exist — wiring + live verification of those steps is pending (steps were empty on the test instance's metadata).</t>
         </is>
       </c>
       <c r="F141" s="8" t="inlineStr"/>
@@ -10894,12 +10878,12 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>dates.invoiceDate</t>
+          <t>approval.by</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>sort</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
@@ -10909,7 +10893,7 @@
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Sorting incoming invoices by invoice date — dateOfSupplierInvoice is not sortable on the BF API today.</t>
+          <t>The approver is not exposed — BF supplierInvoice carries only the check statuses.</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr"/>
@@ -10922,12 +10906,12 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>match.status</t>
+          <t>approval.at</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
@@ -10937,7 +10921,7 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Re-running/overriding the match verdict via API (rematch) — the check statuses are readable now; a command to re-evaluate is still missing upstream.</t>
+          <t>The approval timestamp is not exposed by the BF supplierInvoice entity.</t>
         </is>
       </c>
       <c r="F143" s="8" t="inlineStr"/>
@@ -10945,17 +10929,17 @@
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>payment.status</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
@@ -10965,7 +10949,7 @@
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Open-liabilities view needs filtering by payment status — not allowed on the BF supplierInvoice API today.</t>
+          <t>The consolidated product kind (ADR-011) should be settable directly instead of juggling isServiceProduct/isFee/isShippingCostsProduct booleans — the v2 create body only exposes isShippingCostsProduct, so service/digital cannot be expressed.</t>
         </is>
       </c>
       <c r="F144" s="8" t="inlineStr"/>
@@ -10973,17 +10957,17 @@
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>approval.status</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
@@ -10993,7 +10977,7 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Approve/reject via API: BF process steps (GoodsCheck/InvoiceCheck/Payment) are reported to exist — wiring + live verification of those steps is pending (steps were empty on the test instance's metadata).</t>
+          <t>Tagging products (assortment curation, campaigns) — product writes now go through v2, but the v2 tags shape ({id,key,name,color}) is not yet mapped/verified, so tag writes stay blue.</t>
         </is>
       </c>
       <c r="F145" s="8" t="inlineStr"/>
@@ -11001,12 +10985,12 @@
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>approval.by</t>
+          <t>prices.sale</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
@@ -11021,7 +11005,7 @@
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>The approver is not exposed — BF supplierInvoice carries only the check statuses.</t>
+          <t>WRITE works — the sale price is composed as a separate salesPrices write on create/update. READ is still blue: the v3 read model does not carry the sale price (needs the salesPrices include parsed), so a written price is not read back.</t>
         </is>
       </c>
       <c r="F146" s="8" t="inlineStr"/>
@@ -11029,17 +11013,17 @@
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>approval.at</t>
+          <t>tax.profile</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
@@ -11049,7 +11033,7 @@
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>The approval timestamp is not exposed by the BF supplierInvoice entity.</t>
+          <t>The 16-account tax matrix consolidated into a referenceable taxProfile (ADR-011) — today only the raw taxAccounts embed exists, not a clean reference.</t>
         </is>
       </c>
       <c r="F147" s="8" t="inlineStr"/>
@@ -11062,12 +11046,12 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>logistics.packagingUnits</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>create, read, update</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
@@ -11077,7 +11061,7 @@
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>The consolidated product kind (ADR-011) should be settable directly instead of juggling isServiceProduct/isFee/isShippingCostsProduct booleans — the v2 create body only exposes isShippingCostsProduct, so service/digital cannot be expressed.</t>
+          <t>Packaging units (VPE) need the packagingUnits include parsed — not yet mapped.</t>
         </is>
       </c>
       <c r="F148" s="8" t="inlineStr"/>
@@ -11090,12 +11074,12 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>stock.incoming</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D149" s="9" t="inlineStr">
@@ -11105,7 +11089,7 @@
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Tagging products (assortment curation, campaigns) — product writes now go through v2, but the v2 tags shape ({id,key,name,color}) is not yet mapped/verified, so tag writes stay blue.</t>
+          <t>Inbound quantity (ordered but not yet received) is the one stock figure Xentral does not compute: /products/{id}/stocks returns physical, sellable, reserved, correction, pseudo, openSalesOrders, calculated and producible — all mapped — but nothing inbound. The per-warehouse split the same call carries is answered by StockLevel (filter[product], narrowed by warehouse), so it is not duplicated onto the product.</t>
         </is>
       </c>
       <c r="F149" s="8" t="inlineStr"/>
@@ -11118,12 +11102,12 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>prices.sale</t>
+          <t>suppliers</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
@@ -11133,7 +11117,7 @@
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>WRITE works — the sale price is composed as a separate salesPrices write on create/update. READ is still blue: the v3 read model does not carry the sale price (needs the salesPrices include parsed), so a written price is not read back.</t>
+          <t>The default supplier IS writable (mapped to v2 standardSupplier); multi-supplier sourcing (several suppliers with per-supplier price/number) needs a suppliers include/relation not yet mapped, plus a write path.</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr"/>
@@ -11141,17 +11125,17 @@
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>PriceList</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>tax.profile</t>
+          <t>entries</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D151" s="9" t="inlineStr">
@@ -11161,7 +11145,7 @@
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>The 16-account tax matrix consolidated into a referenceable taxProfile (ADR-011) — today only the raw taxAccounts embed exists, not a clean reference.</t>
+          <t>v1 salesPrices exposes flat price rows (this entity is one row); the grouped priceList with a tier array needs a composer (ADR-012). Write each tier as its own entry (create/update/delete are live via v3/v1 salesPrices).</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr"/>
@@ -11169,17 +11153,17 @@
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StorageLocation</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>logistics.packagingUnits</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>create, read, update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D152" s="9" t="inlineStr">
@@ -11189,7 +11173,7 @@
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Packaging units (VPE) need the packagingUnits include parsed — not yet mapped.</t>
+          <t>Upstream returns the bin description but rejects it on create and update ("The attribute description is not allowed.") — the field is read-only for every API generation we have. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F152" s="8" t="inlineStr"/>
@@ -11197,12 +11181,12 @@
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StorageLocation</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>stock.incoming</t>
+          <t>contents.reserved</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
@@ -11217,7 +11201,7 @@
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Inbound quantity (ordered but not yet received) is the one stock figure Xentral does not compute: /products/{id}/stocks returns physical, sellable, reserved, correction, pseudo, openSalesOrders, calculated and producible — all mapped — but nothing inbound. The per-warehouse split the same call carries is answered by StockLevel (filter[product], narrowed by warehouse), so it is not duplicated onto the product.</t>
+          <t>Location contents are composed from the StockLevel projection now; the reserved portion per location stays unavailable — upstream reports reservations only as a product total.</t>
         </is>
       </c>
       <c r="F153" s="8" t="inlineStr"/>
@@ -11225,27 +11209,27 @@
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StorageLocation</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>suppliers</t>
+          <t>locationType</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D154" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D154" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>The default supplier IS writable (mapped to v2 standardSupplier); multi-supplier sourcing (several suppliers with per-supplier price/number) needs a suppliers include/relation not yet mapped, plus a write path.</t>
+          <t>v1 accepts a `locationType` on write with 204 but never returns it on any read, so a value written there cannot be verified or shown. Not modelled until upstream reads it back. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F154" s="8" t="inlineStr"/>
@@ -11253,17 +11237,17 @@
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>PriceList</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>entries</t>
+          <t>batch</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>read, list</t>
         </is>
       </c>
       <c r="D155" s="9" t="inlineStr">
@@ -11273,7 +11257,7 @@
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>v1 salesPrices exposes flat price rows (this entity is one row); the grouped priceList with a tier array needs a composer (ADR-012). Write each tier as its own entry (create/update/delete are live via v3/v1 salesPrices).</t>
+          <t>The batch split exists on the v2 items path (qualityControlAttributes) but not on /v1/products/{id}/storageLocations. Emitting batch rows on one anchor only would make the grain depend on the filter, so the projection stays product × storage location. A unified GET /v3/stockLevels is the clean ask (docs/05 #18).</t>
         </is>
       </c>
       <c r="F155" s="8" t="inlineStr"/>
@@ -11281,17 +11265,17 @@
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>StorageLocation</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D156" s="9" t="inlineStr">
@@ -11301,7 +11285,7 @@
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Upstream returns the bin description but rejects it on create and update ("The attribute description is not allowed.") — the field is read-only for every API generation we have. Measured on mvp 2026-08-02.</t>
+          <t>The list needs an anchor filter (product or storageLocation): upstream has no global stock collection, so an unanchored query would mean fanning out over every product of the tenant.</t>
         </is>
       </c>
       <c r="F156" s="8" t="inlineStr"/>
@@ -11309,12 +11293,12 @@
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>StorageLocation</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>contents.reserved</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -11329,7 +11313,7 @@
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Location contents are composed from the StockLevel projection now; the reserved portion per location stays unavailable — upstream reports reservations only as a product total.</t>
+          <t>No per-location reservation is exposed upstream; /v1/products/{id}/stocks reports reserved only as a product TOTAL. The projection reports quantity and leaves reserved/available blank rather than spreading a total over locations.</t>
         </is>
       </c>
       <c r="F157" s="8" t="inlineStr"/>
@@ -11337,12 +11321,12 @@
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>StorageLocation</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>locationType</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
@@ -11350,14 +11334,14 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D158" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+      <c r="D158" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>v1 accepts a `locationType` on write with 204 but never returns it on any read, so a value written there cannot be verified or shown. Not modelled until upstream reads it back. Measured on mvp 2026-08-02.</t>
+          <t>Same gap as reserved: available = quantity - reserved is only derivable per product, not per storage location.</t>
         </is>
       </c>
       <c r="F158" s="8" t="inlineStr"/>
@@ -11365,17 +11349,17 @@
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>batch</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>read, list</t>
+          <t>list, read</t>
         </is>
       </c>
       <c r="D159" s="9" t="inlineStr">
@@ -11385,7 +11369,7 @@
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>The batch split exists on the v2 items path (qualityControlAttributes) but not on /v1/products/{id}/storageLocations. Emitting batch rows on one anchor only would make the grain depend on the filter, so the projection stays product × storage location. A unified GET /v3/stockLevels is the clean ask (docs/05 #18).</t>
+          <t>The stock ledger (Lagerprotokoll) has NO read API at all — the single biggest gap (docs/05 #1). GET /v3/stockMovements is the ask. Until it ships the entity does not declare list/read at all, so a caller learns this from the contract instead of a 404.</t>
         </is>
       </c>
       <c r="F159" s="8" t="inlineStr"/>
@@ -11393,17 +11377,17 @@
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D160" s="9" t="inlineStr">
@@ -11413,7 +11397,7 @@
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>The list needs an anchor filter (product or storageLocation): upstream has no global stock collection, so an unanchored query would mean fanning out over every product of the tenant.</t>
+          <t>A booking returns no identity: the v1 storage-item endpoints answer 201 with an empty body and — contrary to their own spec — send no Location header (verified on mvp 2026-07-31). Without an id a repeated booking cannot be recognised afterwards, which is why correction+setQuantityTo is the only retry-safe write. The ask: return the specced Location header, or the created movement.</t>
         </is>
       </c>
       <c r="F160" s="8" t="inlineStr"/>
@@ -11421,12 +11405,12 @@
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>unitCost</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
@@ -11441,7 +11425,7 @@
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>No per-location reservation is exposed upstream; /v1/products/{id}/stocks reports reserved only as a product TOTAL. The projection reports quantity and leaves reserved/available blank rather than spreading a total over locations.</t>
+          <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
         </is>
       </c>
       <c r="F161" s="8" t="inlineStr"/>
@@ -11449,17 +11433,17 @@
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D162" s="9" t="inlineStr">
@@ -11469,7 +11453,7 @@
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Same gap as reserved: available = quantity - reserved is only derivable per product, not per storage location.</t>
+          <t>Starting a stock take via API (scope: warehouse/locations/products, key date) — the v1 inventory endpoints exist but the write orchestration is not built yet.</t>
         </is>
       </c>
       <c r="F162" s="8" t="inlineStr"/>
@@ -11477,17 +11461,17 @@
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>StockMovement</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>dates.keyDate</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>list, read</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D163" s="9" t="inlineStr">
@@ -11497,7 +11481,7 @@
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>The stock ledger (Lagerprotokoll) has NO read API at all — the single biggest gap (docs/05 #1). GET /v3/stockMovements is the ask. Until it ships the entity does not declare list/read at all, so a caller learns this from the contract instead of a 404.</t>
+          <t>The inventory key date (Stichtag) is not exposed by v1 inventoryRuns.</t>
         </is>
       </c>
       <c r="F163" s="8" t="inlineStr"/>
@@ -11505,17 +11489,17 @@
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>StockMovement</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>dates.posted</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D164" s="9" t="inlineStr">
@@ -11525,7 +11509,7 @@
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>A booking returns no identity: the v1 storage-item endpoints answer 201 with an empty body and — contrary to their own spec — send no Location header (verified on mvp 2026-07-31). Without an id a repeated booking cannot be recognised afterwards, which is why correction+setQuantityTo is the only retry-safe write. The ask: return the specced Location header, or the created movement.</t>
+          <t>The posted timestamp is not exposed by v1 inventoryRuns.</t>
         </is>
       </c>
       <c r="F164" s="8" t="inlineStr"/>
@@ -11533,12 +11517,12 @@
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>StockMovement</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>unitCost</t>
+          <t>positions</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
@@ -11553,7 +11537,7 @@
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
+          <t>Counting positions (expected/counted/difference with values) live in the counting-list reports — not composed into the API payload yet; needed for the GoBD difference review.</t>
         </is>
       </c>
       <c r="F165" s="8" t="inlineStr"/>
@@ -11566,12 +11550,12 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>positions.counted</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D166" s="9" t="inlineStr">
@@ -11581,7 +11565,7 @@
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Starting a stock take via API (scope: warehouse/locations/products, key date) — the v1 inventory endpoints exist but the write orchestration is not built yet.</t>
+          <t>Submitting counted quantities via API (mobile counting) — needed for headless inventory.</t>
         </is>
       </c>
       <c r="F166" s="8" t="inlineStr"/>
@@ -11594,7 +11578,7 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>dates.keyDate</t>
+          <t>documents.stockMovements</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
@@ -11609,7 +11593,7 @@
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>The inventory key date (Stichtag) is not exposed by v1 inventoryRuns.</t>
+          <t>Posted correction movements per stock take need the stockMovements API (docs/05 #1) to be traceable.</t>
         </is>
       </c>
       <c r="F167" s="8" t="inlineStr"/>
@@ -11617,17 +11601,17 @@
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>dates.posted</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D168" s="9" t="inlineStr">
@@ -11637,7 +11621,7 @@
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>The posted timestamp is not exposed by v1 inventoryRuns.</t>
+          <t>Creating a picking run by criteria (wave: channel, shipping method, cutoff, maxOrders) has NO upstream endpoint — the main gap (docs/05 #3); execution (start/complete, totes) already exists.</t>
         </is>
       </c>
       <c r="F168" s="8" t="inlineStr"/>
@@ -11645,12 +11629,12 @@
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>totals</t>
+          <t>criteria</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
@@ -11658,31 +11642,27 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D169" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>Position/difference totals are not exposed by v1 inventoryRuns.</t>
-        </is>
-      </c>
-      <c r="F169" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>Pick-run criteria (channel, shipping method) are not exposed by v1 pickLists.</t>
+        </is>
+      </c>
+      <c r="F169" s="8" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>positions</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
@@ -11697,7 +11677,7 @@
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>Counting positions (expected/counted/difference with values) live in the counting-list reports — not composed into the API payload yet; needed for the GoBD difference review.</t>
+          <t>The picked sales orders are not exposed by v1 pickLists (only counts).</t>
         </is>
       </c>
       <c r="F170" s="8" t="inlineStr"/>
@@ -11705,17 +11685,17 @@
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>positions.counted</t>
+          <t>containers</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D171" s="9" t="inlineStr">
@@ -11725,7 +11705,7 @@
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Submitting counted quantities via API (mobile counting) — needed for headless inventory.</t>
+          <t>Totes/containers are not exposed by v1 pickLists.</t>
         </is>
       </c>
       <c r="F171" s="8" t="inlineStr"/>
@@ -11733,17 +11713,17 @@
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>documents.stockMovements</t>
+          <t>strategy</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D172" s="9" t="inlineStr">
@@ -11753,7 +11733,7 @@
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Posted correction movements per stock take need the stockMovements API (docs/05 #1) to be traceable.</t>
+          <t>Choosing the picking strategy (single/multiOrder/wave/zone) at creation — no create endpoint today.</t>
         </is>
       </c>
       <c r="F172" s="8" t="inlineStr"/>
@@ -11766,12 +11746,12 @@
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>tasks</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D173" s="9" t="inlineStr">
@@ -11781,7 +11761,7 @@
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Creating a picking run by criteria (wave: channel, shipping method, cutoff, maxOrders) has NO upstream endpoint — the main gap (docs/05 #3); execution (start/complete, totes) already exists.</t>
+          <t>Task-level detail (location, product, quantity, status per pick) is not exposed on the pickLists API — needed for progress boards and pick-path optimisation.</t>
         </is>
       </c>
       <c r="F173" s="8" t="inlineStr"/>
@@ -11794,12 +11774,12 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>criteria</t>
+          <t>tasks.status</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D174" s="9" t="inlineStr">
@@ -11809,7 +11789,7 @@
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Pick-run criteria (channel, shipping method) are not exposed by v1 pickLists.</t>
+          <t>Granular task-level pick confirmation with quantity + scans (docs/05 #3) — today only whole-list start/complete exists.</t>
         </is>
       </c>
       <c r="F174" s="8" t="inlineStr"/>
@@ -11817,17 +11797,17 @@
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>list, read</t>
         </is>
       </c>
       <c r="D175" s="9" t="inlineStr">
@@ -11837,7 +11817,7 @@
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>The picked sales orders are not exposed by v1 pickLists (only counts).</t>
+          <t>Batches exist only as read-only v3 Product includes — no batch resource, no list, no detail (docs/05 #4). GET /v3/batches is the ask.</t>
         </is>
       </c>
       <c r="F175" s="8" t="inlineStr"/>
@@ -11845,17 +11825,17 @@
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>containers</t>
+          <t>bestBefore</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D176" s="9" t="inlineStr">
@@ -11865,7 +11845,7 @@
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Totes/containers are not exposed by v1 pickLists.</t>
+          <t>Correcting a best-before date via API — internal web routes only today.</t>
         </is>
       </c>
       <c r="F176" s="8" t="inlineStr"/>
@@ -11873,17 +11853,17 @@
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>strategy</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D177" s="9" t="inlineStr">
@@ -11893,7 +11873,7 @@
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Choosing the picking strategy (single/multiOrder/wave/zone) at creation — no create endpoint today.</t>
+          <t>Blocking/releasing a batch (quality hold) via API — maintenance happens only through internal web routes today.</t>
         </is>
       </c>
       <c r="F177" s="8" t="inlineStr"/>
@@ -11901,12 +11881,12 @@
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>tasks</t>
+          <t>trace</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
@@ -11921,7 +11901,7 @@
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Task-level detail (location, product, quantity, status per pick) is not exposed on the pickLists API — needed for progress boards and pick-path optimisation.</t>
+          <t>Batch trace (which goods receipts brought it in, which delivery notes shipped it — recall scenario) has no API at all (docs/05 #4).</t>
         </is>
       </c>
       <c r="F178" s="8" t="inlineStr"/>
@@ -11929,45 +11909,49 @@
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>tasks.status</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D179" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D179" s="10" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Granular task-level pick confirmation with quantity + scans (docs/05 #3) — today only whole-list start/complete exists.</t>
-        </is>
-      </c>
-      <c r="F179" s="8" t="inlineStr"/>
+          <t>The platform kind (shopify/amazon/…) is not exposed — the BF salesChannel entity carries only a name (05 #17).</t>
+        </is>
+      </c>
+      <c r="F179" s="8" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>list, read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D180" s="9" t="inlineStr">
@@ -11977,7 +11961,7 @@
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Batches exist only as read-only v3 Product includes — no batch resource, no list, no detail (docs/05 #4). GET /v3/batches is the ask.</t>
+          <t>REVISED (docs/05 #17): BF salesChannel has CRUD — our facade write-mapping + live verification is pending.</t>
         </is>
       </c>
       <c r="F180" s="8" t="inlineStr"/>
@@ -11985,17 +11969,17 @@
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>bestBefore</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read, create, update</t>
         </is>
       </c>
       <c r="D181" s="9" t="inlineStr">
@@ -12005,7 +11989,7 @@
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Correcting a best-before date via API — internal web routes only today.</t>
+          <t>The channel type (shop/marketplace/direct/pos) is not on the BF salesChannel record — needed for channel-specific routing.</t>
         </is>
       </c>
       <c r="F181" s="8" t="inlineStr"/>
@@ -12013,17 +11997,17 @@
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>assignee</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D182" s="9" t="inlineStr">
@@ -12033,7 +12017,7 @@
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Blocking/releasing a batch (quality hold) via API — maintenance happens only through internal web routes today.</t>
+          <t>The one thing that would make a task a work item. `assignee` is readOnly upstream: a create or update carrying it answers 2xx and leaves the field null. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F182" s="8" t="inlineStr"/>
@@ -12041,17 +12025,17 @@
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>trace</t>
+          <t>dates.completed</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D183" s="9" t="inlineStr">
@@ -12061,7 +12045,7 @@
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Batch trace (which goods receipts brought it in, which delivery notes shipped it — recall scenario) has no API at all (docs/05 #4).</t>
+          <t>Completing a task through the API does not stamp its completion date: `status: completed` persists, `completionDate` stays null.</t>
         </is>
       </c>
       <c r="F183" s="8" t="inlineStr"/>
@@ -12069,12 +12053,12 @@
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>timeline</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
@@ -12082,260 +12066,20 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D184" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+      <c r="D184" s="12" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>The platform kind (shopify/amazon/…) is not exposed — the BF salesChannel entity carries only a name (05 #17).</t>
-        </is>
-      </c>
-      <c r="F184" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="6" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B185" s="6" t="inlineStr">
-        <is>
-          <t>defaults</t>
-        </is>
-      </c>
-      <c r="C185" s="6" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D185" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
-        </is>
-      </c>
-      <c r="E185" s="8" t="inlineStr">
-        <is>
-          <t>Channel defaults (price list, warehouse) are not exposed (05 #17).</t>
-        </is>
-      </c>
-      <c r="F185" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="6" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B186" s="6" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D186" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E186" s="8" t="inlineStr">
-        <is>
-          <t>REVISED (docs/05 #17): BF salesChannel has CRUD — our facade write-mapping + live verification is pending.</t>
-        </is>
-      </c>
-      <c r="F186" s="8" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="6" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B187" s="6" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C187" s="6" t="inlineStr">
-        <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D187" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E187" s="8" t="inlineStr">
-        <is>
-          <t>The channel type (shop/marketplace/direct/pos) is not on the BF salesChannel record — needed for channel-specific routing.</t>
-        </is>
-      </c>
-      <c r="F187" s="8" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="6" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D188" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
-        </is>
-      </c>
-      <c r="E188" s="8" t="inlineStr">
-        <is>
-          <t>Enable/disable state is not on the BF salesChannel record.</t>
-        </is>
-      </c>
-      <c r="F188" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B189" s="6" t="inlineStr">
-        <is>
-          <t>sync</t>
-        </is>
-      </c>
-      <c r="C189" s="6" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D189" s="10" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
-        </is>
-      </c>
-      <c r="E189" s="8" t="inlineStr">
-        <is>
-          <t>Channel sync-run status (last run, success/failure) is not exposed — needed to monitor shop imports (docs/05 #17, still open after the BF salesChannel entity covered the list).</t>
-        </is>
-      </c>
-      <c r="F189" s="8" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
-        <is>
-          <t>assignee</t>
-        </is>
-      </c>
-      <c r="C190" s="6" t="inlineStr">
-        <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D190" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E190" s="8" t="inlineStr">
-        <is>
-          <t>The one thing that would make a task a work item. `assignee` is readOnly upstream: a create or update carrying it answers 2xx and leaves the field null. Measured on mvp 2026-08-02.</t>
-        </is>
-      </c>
-      <c r="F190" s="8" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="6" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B191" s="6" t="inlineStr">
-        <is>
-          <t>dates.completed</t>
-        </is>
-      </c>
-      <c r="C191" s="6" t="inlineStr">
-        <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D191" s="9" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E191" s="8" t="inlineStr">
-        <is>
-          <t>Completing a task through the API does not stamp its completion date: `status: completed` persists, `completionDate` stays null.</t>
-        </is>
-      </c>
-      <c r="F191" s="8" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="6" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B192" s="6" t="inlineStr">
-        <is>
-          <t>timeline</t>
-        </is>
-      </c>
-      <c r="C192" s="6" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D192" s="12" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
-        </is>
-      </c>
-      <c r="E192" s="8" t="inlineStr">
-        <is>
           <t>The task's comment thread. Declared `readWrite` with a full sub-node and returned by NO read — not the list, not the single read, and no include/expand parameter produces it. Not modelled until it reads back.</t>
         </is>
       </c>
-      <c r="F192" s="8" t="inlineStr"/>
+      <c r="F184" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F192"/>
+  <autoFilter ref="A1:F184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Übersicht'!$A$6:$H$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fähigkeiten'!$A$1:$F$181</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Felder'!$A$1:$F$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Felder'!$A$1:$F$158</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -861,12 +861,10 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="17">
@@ -6856,7 +6854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F171"/>
+  <dimension ref="A1:F158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9387,12 +9385,12 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>defaults.shippingMethod</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
@@ -9402,7 +9400,7 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>Active/archived state is not exposed via v3 suppliers — needed for honest archiving (plan §6.1).</t>
+          <t>The default shipping method is not surfaced by the v3 partner read.</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr"/>
@@ -9415,12 +9413,12 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>defaults.paymentTerms.dueDays</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
@@ -9430,7 +9428,7 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>B2B hierarchy (branch → HQ) is not exposed via the public API (plan §6.1 parent).</t>
+          <t>Default supplier payment term — drives liability due dates.</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr"/>
@@ -9443,12 +9441,12 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>billTo</t>
+          <t>finance.creditorAccountNumber</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
@@ -9458,7 +9456,7 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>Central billing (Zentralregulierung — invoice to association/HQ) is not exposed (plan §6.1 billTo).</t>
+          <t>The creditor account for the FiBu/DATEV export — settable per supplier.</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr"/>
@@ -9471,12 +9469,12 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>channels</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
@@ -9486,7 +9484,7 @@
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>Per-channel external ids (channel links) are not exposed via the public API.</t>
+          <t>Custom field values on the supplier — today only readable, not writable via API.</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr"/>
@@ -9494,17 +9492,17 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>purchasing.confirmationRequired</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
@@ -9514,7 +9512,7 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>Whether an order confirmation (AB) is required from this supplier — drives purchasing workflow; not settable via API today.</t>
+          <t>Carrying a purchase order number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr"/>
@@ -9522,17 +9520,17 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>purchasing.sendOrdersVia</t>
+          <t>supplier</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
@@ -9542,7 +9540,7 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>How POs are sent to the supplier (email/portal/EDI) — a supplier default that must be settable.</t>
+          <t>Reassign the PO's supplier after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr"/>
@@ -9550,12 +9548,12 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>purchasing.deliveryDays</t>
+          <t>references.ourCustomerNumber</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -9570,7 +9568,7 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>Standard supplier lead time in days — feeds replenishment planning.</t>
+          <t>Our customer number at the supplier — belongs on the PO, not settable via API today.</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr"/>
@@ -9578,12 +9576,12 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>addresses.type</t>
+          <t>references.supplierOfferNumber</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
@@ -9591,36 +9589,32 @@
           <t>create, update</t>
         </is>
       </c>
-      <c r="D96" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>Set the address role incl. the 'both' value (one address serving billing AND shipping) — v3 splits billing (primaryAddress/deviating) vs shipping (deliveryAddresses) by store, so the role is not a freely settable field.</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>The supplier's quote number we ordered against — read-only upstream today.</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>defaults.shippingMethod</t>
+          <t>confirmation.status</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
@@ -9630,7 +9624,7 @@
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>The default shipping method is not surfaced by the v3 partner read.</t>
+          <t>Recording the confirmation status (pending/confirmed/deviating) is core purchasing — not writable via API today.</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr"/>
@@ -9638,17 +9632,17 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>defaults.priceList</t>
+          <t>confirmation.supplierOrderNumber</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
@@ -9658,7 +9652,7 @@
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>The assigned price list is not surfaced by the v3 partner read.</t>
+          <t>The AB (order-confirmation) number from the supplier — the whole confirmation block is read-only upstream (docs/05: AB handling).</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr"/>
@@ -9666,17 +9660,17 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>defaults.partialShipping</t>
+          <t>dates.requestedDelivery</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
@@ -9686,7 +9680,7 @@
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>The partial-shipping preference is not surfaced by the v3 partner read.</t>
+          <t>Requested delivery date at the supplier — not writable upstream today.</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr"/>
@@ -9694,12 +9688,12 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>defaults.paymentTerms.dueDays</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
@@ -9714,7 +9708,7 @@
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>Default supplier payment term — drives liability due dates.</t>
+          <t>The receiving warehouse for the PO must be selectable.</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr"/>
@@ -9722,17 +9716,17 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>finance.openAmount</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
@@ -9742,7 +9736,7 @@
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>Aggregated open liabilities per supplier are computed nowhere in the API — must be derived/served.</t>
+          <t>Edit PO positions after creation — the v3 update DTO carries no line-item write path.</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr"/>
@@ -9750,17 +9744,17 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>finance.creditorAccountNumber</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
@@ -9770,7 +9764,7 @@
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>The creditor account for the FiBu/DATEV export — settable per supplier.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr"/>
@@ -9778,17 +9772,17 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>dropship</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, create</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
@@ -9798,7 +9792,7 @@
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>Custom field values on the supplier — today only readable, not writable via API.</t>
+          <t>Dropshipping (Strecke: salesOrder link + customer delivery address) is not exposed via v3 purchaseOrders.</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr"/>
@@ -9806,27 +9800,27 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>contacts.address</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D104" s="13" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>Bind a contact person to a specific address (person-at-location) — v3 stores only a free-text contactPerson on delivery addresses, not a reference.</t>
+          <t>Custom field values on the PO — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr"/>
@@ -9834,27 +9828,27 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>contacts.isPrimary</t>
+          <t>references.supplierDeliveryNoteNumber</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D105" s="13" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create, update, read</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>Mark the main contact person — v3 contactPersons carry no primary flag.</t>
+          <t>The supplier's delivery-note number on the goods receipt — needed for the three-way match; not in the BF record yet.</t>
         </is>
       </c>
       <c r="F105" s="9" t="inlineStr"/>
@@ -9862,17 +9856,17 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>dates.received</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
@@ -9882,7 +9876,7 @@
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>Carrying a purchase order number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr"/>
@@ -9890,17 +9884,17 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>supplier</t>
+          <t>dates.posted</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
@@ -9910,7 +9904,7 @@
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>Reassign the PO's supplier after creation — v3 accepts it only on create.</t>
+          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr"/>
@@ -9918,17 +9912,17 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>references.ourCustomerNumber</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
@@ -9938,7 +9932,7 @@
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>Our customer number at the supplier — belongs on the PO, not settable via API today.</t>
+          <t>Cancel/storno of a posted goods receipt — the remaining upstream gap after the BF entity list covered browsing (docs/05 #9 revised).</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr"/>
@@ -9946,17 +9940,17 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>references.supplierOfferNumber</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, create, update</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
@@ -9966,7 +9960,7 @@
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>The supplier's quote number we ordered against — read-only upstream today.</t>
+          <t>Line items (product × quantity × storage location, quality check per line) are not exposed on the BF goodsReceipt record — creation still goes through the PO action only.</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr"/>
@@ -9974,17 +9968,17 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>confirmation.status</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
@@ -9994,7 +9988,7 @@
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>Recording the confirmation status (pending/confirmed/deviating) is core purchasing — not writable via API today.</t>
+          <t>The document number is system-assigned: sending `documentNumber` on create answers 201 and the record comes back with an empty number (measured on mvp 2026-08-02). Same behaviour as the other documents.</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr"/>
@@ -10002,17 +9996,17 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>confirmation.supplierOrderNumber</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
@@ -10022,7 +10016,7 @@
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>The AB (order-confirmation) number from the supplier — the whole confirmation block is read-only upstream (docs/05: AB handling).</t>
+          <t>Filtering incoming invoices by workflow status is the AP daily view — the BF supplierInvoice API does not allow filtering documentStatus today.</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr"/>
@@ -10030,17 +10024,17 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>dates.requestedDelivery</t>
+          <t>dates.invoiceDate</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>sort</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
@@ -10050,7 +10044,7 @@
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>Requested delivery date at the supplier — not writable upstream today.</t>
+          <t>Sorting incoming invoices by invoice date — dateOfSupplierInvoice is not sortable on the BF API today.</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr"/>
@@ -10058,17 +10052,17 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>match.status</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
@@ -10078,7 +10072,7 @@
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>The receiving warehouse for the PO must be selectable.</t>
+          <t>Re-running/overriding the match verdict via API (rematch) — the check statuses are readable now; a command to re-evaluate is still missing upstream.</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr"/>
@@ -10086,17 +10080,17 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>payment.status</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
@@ -10106,7 +10100,7 @@
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>Edit PO positions after creation — the v3 update DTO carries no line-item write path.</t>
+          <t>Open-liabilities view needs filtering by payment status — not allowed on the BF supplierInvoice API today.</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr"/>
@@ -10114,17 +10108,17 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>approval.status</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
@@ -10134,7 +10128,7 @@
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Approve/reject via API: BF process steps (GoodsCheck/InvoiceCheck/Payment) are reported to exist — wiring + live verification of those steps is pending (steps were empty on the test instance's metadata).</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr"/>
@@ -10142,17 +10136,17 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>dropship</t>
+          <t>approval.by</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>read, create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
@@ -10162,7 +10156,7 @@
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>Dropshipping (Strecke: salesOrder link + customer delivery address) is not exposed via v3 purchaseOrders.</t>
+          <t>The approver is not exposed — BF supplierInvoice carries only the check statuses.</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr"/>
@@ -10170,17 +10164,17 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>approval.at</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
@@ -10190,7 +10184,7 @@
       </c>
       <c r="E117" s="9" t="inlineStr">
         <is>
-          <t>Custom field values on the PO — today only readable via include, not writable via API.</t>
+          <t>The approval timestamp is not exposed by the BF supplierInvoice entity.</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr"/>
@@ -10198,17 +10192,17 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>references.supplierDeliveryNoteNumber</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>create, update, read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
@@ -10218,7 +10212,7 @@
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>The supplier's delivery-note number on the goods receipt — needed for the three-way match; not in the BF record yet.</t>
+          <t>The consolidated product kind (ADR-011) should be settable directly instead of juggling isServiceProduct/isFee/isShippingCostsProduct booleans — the v2 create body only exposes isShippingCostsProduct, so service/digital cannot be expressed.</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr"/>
@@ -10226,17 +10220,17 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>dates.received</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -10246,7 +10240,7 @@
       </c>
       <c r="E119" s="9" t="inlineStr">
         <is>
-          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
+          <t>Tagging products (assortment curation, campaigns) — product writes now go through v2, but the v2 tags shape ({id,key,name,color}) is not yet mapped/verified, so tag writes stay blue.</t>
         </is>
       </c>
       <c r="F119" s="9" t="inlineStr"/>
@@ -10254,12 +10248,12 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>dates.posted</t>
+          <t>prices.sale</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
@@ -10274,7 +10268,7 @@
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
+          <t>WRITE works — the sale price is composed as a separate salesPrices write on create/update. READ is still blue: the v3 read model does not carry the sale price (needs the salesPrices include parsed), so a written price is not read back.</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr"/>
@@ -10282,17 +10276,17 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>tax.profile</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
@@ -10302,7 +10296,7 @@
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>Cancel/storno of a posted goods receipt — the remaining upstream gap after the BF entity list covered browsing (docs/05 #9 revised).</t>
+          <t>The 16-account tax matrix consolidated into a referenceable taxProfile (ADR-011) — today only the raw taxAccounts embed exists, not a clean reference.</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr"/>
@@ -10310,17 +10304,17 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>logistics.packagingUnits</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>read, create, update</t>
+          <t>create, read, update</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
@@ -10330,7 +10324,7 @@
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>Line items (product × quantity × storage location, quality check per line) are not exposed on the BF goodsReceipt record — creation still goes through the PO action only.</t>
+          <t>Packaging units (VPE) need the packagingUnits include parsed — not yet mapped.</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr"/>
@@ -10338,17 +10332,17 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>stock.incoming</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -10358,7 +10352,7 @@
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>The document number is system-assigned: sending `documentNumber` on create answers 201 and the record comes back with an empty number (measured on mvp 2026-08-02). Same behaviour as the other documents.</t>
+          <t>Inbound quantity (ordered but not yet received) is the one stock figure Xentral does not compute: /products/{id}/stocks returns physical, sellable, reserved, correction, pseudo, openSalesOrders, calculated and producible — all mapped — but nothing inbound. The per-warehouse split the same call carries is answered by StockLevel (filter[product], narrowed by warehouse), so it is not duplicated onto the product.</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr"/>
@@ -10366,17 +10360,17 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>suppliers</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -10386,7 +10380,7 @@
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>Filtering incoming invoices by workflow status is the AP daily view — the BF supplierInvoice API does not allow filtering documentStatus today.</t>
+          <t>The default supplier IS writable (mapped to v2 standardSupplier); multi-supplier sourcing (several suppliers with per-supplier price/number) needs a suppliers include/relation not yet mapped, plus a write path.</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr"/>
@@ -10394,17 +10388,17 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>PriceList</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>dates.invoiceDate</t>
+          <t>entries</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>sort</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -10414,7 +10408,7 @@
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>Sorting incoming invoices by invoice date — dateOfSupplierInvoice is not sortable on the BF API today.</t>
+          <t>v1 salesPrices exposes flat price rows (this entity is one row); the grouped priceList with a tier array needs a composer (ADR-012). Write each tier as its own entry (create/update/delete are live via v3/v1 salesPrices).</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr"/>
@@ -10422,17 +10416,17 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>StorageLocation</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>match.status</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
@@ -10442,7 +10436,7 @@
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>Re-running/overriding the match verdict via API (rematch) — the check statuses are readable now; a command to re-evaluate is still missing upstream.</t>
+          <t>Upstream returns the bin description but rejects it on create and update ("The attribute description is not allowed.") — the field is read-only for every API generation we have. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr"/>
@@ -10450,17 +10444,17 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>StorageLocation</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>payment.status</t>
+          <t>contents.reserved</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
@@ -10470,7 +10464,7 @@
       </c>
       <c r="E127" s="9" t="inlineStr">
         <is>
-          <t>Open-liabilities view needs filtering by payment status — not allowed on the BF supplierInvoice API today.</t>
+          <t>Location contents are composed from the StockLevel projection now; the reserved portion per location stays unavailable — upstream reports reservations only as a product total.</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr"/>
@@ -10478,27 +10472,27 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>StorageLocation</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>approval.status</t>
+          <t>locationType</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D128" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D128" s="13" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E128" s="9" t="inlineStr">
         <is>
-          <t>Approve/reject via API: BF process steps (GoodsCheck/InvoiceCheck/Payment) are reported to exist — wiring + live verification of those steps is pending (steps were empty on the test instance's metadata).</t>
+          <t>v1 accepts a `locationType` on write with 204 but never returns it on any read, so a value written there cannot be verified or shown. Not modelled until upstream reads it back. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr"/>
@@ -10506,17 +10500,17 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>approval.by</t>
+          <t>batch</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>read, list</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
@@ -10526,7 +10520,7 @@
       </c>
       <c r="E129" s="9" t="inlineStr">
         <is>
-          <t>The approver is not exposed — BF supplierInvoice carries only the check statuses.</t>
+          <t>The batch split exists on the v2 items path (qualityControlAttributes) but not on /v1/products/{id}/storageLocations. Emitting batch rows on one anchor only would make the grain depend on the filter, so the projection stays product × storage location. A unified GET /v3/stockLevels is the clean ask (docs/05 #18).</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr"/>
@@ -10534,17 +10528,17 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>approval.at</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
@@ -10554,7 +10548,7 @@
       </c>
       <c r="E130" s="9" t="inlineStr">
         <is>
-          <t>The approval timestamp is not exposed by the BF supplierInvoice entity.</t>
+          <t>The list needs an anchor filter (product or storageLocation): upstream has no global stock collection, so an unanchored query would mean fanning out over every product of the tenant.</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr"/>
@@ -10562,17 +10556,17 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
@@ -10582,7 +10576,7 @@
       </c>
       <c r="E131" s="9" t="inlineStr">
         <is>
-          <t>The consolidated product kind (ADR-011) should be settable directly instead of juggling isServiceProduct/isFee/isShippingCostsProduct booleans — the v2 create body only exposes isShippingCostsProduct, so service/digital cannot be expressed.</t>
+          <t>No per-location reservation is exposed upstream; /v1/products/{id}/stocks reports reserved only as a product TOTAL. The projection reports quantity and leaves reserved/available blank rather than spreading a total over locations.</t>
         </is>
       </c>
       <c r="F131" s="9" t="inlineStr"/>
@@ -10590,17 +10584,17 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
@@ -10610,7 +10604,7 @@
       </c>
       <c r="E132" s="9" t="inlineStr">
         <is>
-          <t>Tagging products (assortment curation, campaigns) — product writes now go through v2, but the v2 tags shape ({id,key,name,color}) is not yet mapped/verified, so tag writes stay blue.</t>
+          <t>Same gap as reserved: available = quantity - reserved is only derivable per product, not per storage location.</t>
         </is>
       </c>
       <c r="F132" s="9" t="inlineStr"/>
@@ -10618,17 +10612,17 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>prices.sale</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>list, read</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
@@ -10638,7 +10632,7 @@
       </c>
       <c r="E133" s="9" t="inlineStr">
         <is>
-          <t>WRITE works — the sale price is composed as a separate salesPrices write on create/update. READ is still blue: the v3 read model does not carry the sale price (needs the salesPrices include parsed), so a written price is not read back.</t>
+          <t>The stock ledger (Lagerprotokoll) has NO read API at all — the single biggest gap (docs/05 #1). GET /v3/stockMovements is the ask. Until it ships the entity does not declare list/read at all, so a caller learns this from the contract instead of a 404.</t>
         </is>
       </c>
       <c r="F133" s="9" t="inlineStr"/>
@@ -10646,17 +10640,17 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>tax.profile</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
@@ -10666,7 +10660,7 @@
       </c>
       <c r="E134" s="9" t="inlineStr">
         <is>
-          <t>The 16-account tax matrix consolidated into a referenceable taxProfile (ADR-011) — today only the raw taxAccounts embed exists, not a clean reference.</t>
+          <t>A booking returns no identity: the v1 storage-item endpoints answer 201 with an empty body and — contrary to their own spec — send no Location header (verified on mvp 2026-07-31). Without an id a repeated booking cannot be recognised afterwards, which is why correction+setQuantityTo is the only retry-safe write. The ask: return the specced Location header, or the created movement.</t>
         </is>
       </c>
       <c r="F134" s="9" t="inlineStr"/>
@@ -10674,17 +10668,17 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>logistics.packagingUnits</t>
+          <t>unitCost</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>create, read, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
@@ -10694,7 +10688,7 @@
       </c>
       <c r="E135" s="9" t="inlineStr">
         <is>
-          <t>Packaging units (VPE) need the packagingUnits include parsed — not yet mapped.</t>
+          <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
         </is>
       </c>
       <c r="F135" s="9" t="inlineStr"/>
@@ -10702,17 +10696,17 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>stock.incoming</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
@@ -10722,7 +10716,7 @@
       </c>
       <c r="E136" s="9" t="inlineStr">
         <is>
-          <t>Inbound quantity (ordered but not yet received) is the one stock figure Xentral does not compute: /products/{id}/stocks returns physical, sellable, reserved, correction, pseudo, openSalesOrders, calculated and producible — all mapped — but nothing inbound. The per-warehouse split the same call carries is answered by StockLevel (filter[product], narrowed by warehouse), so it is not duplicated onto the product.</t>
+          <t>Starting a stock take via API (scope: warehouse/locations/products, key date) — the v1 inventory endpoints exist but the write orchestration is not built yet.</t>
         </is>
       </c>
       <c r="F136" s="9" t="inlineStr"/>
@@ -10730,17 +10724,17 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>suppliers</t>
+          <t>dates.keyDate</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
@@ -10750,7 +10744,7 @@
       </c>
       <c r="E137" s="9" t="inlineStr">
         <is>
-          <t>The default supplier IS writable (mapped to v2 standardSupplier); multi-supplier sourcing (several suppliers with per-supplier price/number) needs a suppliers include/relation not yet mapped, plus a write path.</t>
+          <t>The inventory key date (Stichtag) is not exposed by v1 inventoryRuns.</t>
         </is>
       </c>
       <c r="F137" s="9" t="inlineStr"/>
@@ -10758,12 +10752,12 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>PriceList</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>entries</t>
+          <t>dates.posted</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
@@ -10778,7 +10772,7 @@
       </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>v1 salesPrices exposes flat price rows (this entity is one row); the grouped priceList with a tier array needs a composer (ADR-012). Write each tier as its own entry (create/update/delete are live via v3/v1 salesPrices).</t>
+          <t>The posted timestamp is not exposed by v1 inventoryRuns.</t>
         </is>
       </c>
       <c r="F138" s="9" t="inlineStr"/>
@@ -10786,17 +10780,17 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>StorageLocation</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>positions</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
@@ -10806,7 +10800,7 @@
       </c>
       <c r="E139" s="9" t="inlineStr">
         <is>
-          <t>Upstream returns the bin description but rejects it on create and update ("The attribute description is not allowed.") — the field is read-only for every API generation we have. Measured on mvp 2026-08-02.</t>
+          <t>Counting positions (expected/counted/difference with values) live in the counting-list reports — not composed into the API payload yet; needed for the GoBD difference review.</t>
         </is>
       </c>
       <c r="F139" s="9" t="inlineStr"/>
@@ -10814,17 +10808,17 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>StorageLocation</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>contents.reserved</t>
+          <t>positions.counted</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
@@ -10834,7 +10828,7 @@
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>Location contents are composed from the StockLevel projection now; the reserved portion per location stays unavailable — upstream reports reservations only as a product total.</t>
+          <t>Submitting counted quantities via API (mobile counting) — needed for headless inventory.</t>
         </is>
       </c>
       <c r="F140" s="9" t="inlineStr"/>
@@ -10842,12 +10836,12 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>StorageLocation</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>locationType</t>
+          <t>documents.stockMovements</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
@@ -10855,14 +10849,14 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D141" s="13" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+      <c r="D141" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E141" s="9" t="inlineStr">
         <is>
-          <t>v1 accepts a `locationType` on write with 204 but never returns it on any read, so a value written there cannot be verified or shown. Not modelled until upstream reads it back. Measured on mvp 2026-08-02.</t>
+          <t>Posted correction movements per stock take need the stockMovements API (docs/05 #1) to be traceable.</t>
         </is>
       </c>
       <c r="F141" s="9" t="inlineStr"/>
@@ -10870,17 +10864,17 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>batch</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>read, list</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
@@ -10890,7 +10884,7 @@
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>The batch split exists on the v2 items path (qualityControlAttributes) but not on /v1/products/{id}/storageLocations. Emitting batch rows on one anchor only would make the grain depend on the filter, so the projection stays product × storage location. A unified GET /v3/stockLevels is the clean ask (docs/05 #18).</t>
+          <t>Creating a picking run by criteria (wave: channel, shipping method, cutoff, maxOrders) has NO upstream endpoint — the main gap (docs/05 #3); execution (start/complete, totes) already exists.</t>
         </is>
       </c>
       <c r="F142" s="9" t="inlineStr"/>
@@ -10898,17 +10892,17 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>criteria</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
@@ -10918,7 +10912,7 @@
       </c>
       <c r="E143" s="9" t="inlineStr">
         <is>
-          <t>The list needs an anchor filter (product or storageLocation): upstream has no global stock collection, so an unanchored query would mean fanning out over every product of the tenant.</t>
+          <t>Pick-run criteria (channel, shipping method) are not exposed by v1 pickLists.</t>
         </is>
       </c>
       <c r="F143" s="9" t="inlineStr"/>
@@ -10926,12 +10920,12 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
@@ -10946,7 +10940,7 @@
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>No per-location reservation is exposed upstream; /v1/products/{id}/stocks reports reserved only as a product TOTAL. The projection reports quantity and leaves reserved/available blank rather than spreading a total over locations.</t>
+          <t>The picked sales orders are not exposed by v1 pickLists (only counts).</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr"/>
@@ -10954,12 +10948,12 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>containers</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
@@ -10974,7 +10968,7 @@
       </c>
       <c r="E145" s="9" t="inlineStr">
         <is>
-          <t>Same gap as reserved: available = quantity - reserved is only derivable per product, not per storage location.</t>
+          <t>Totes/containers are not exposed by v1 pickLists.</t>
         </is>
       </c>
       <c r="F145" s="9" t="inlineStr"/>
@@ -10982,17 +10976,17 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>StockMovement</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>strategy</t>
         </is>
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>list, read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
@@ -11002,7 +10996,7 @@
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>The stock ledger (Lagerprotokoll) has NO read API at all — the single biggest gap (docs/05 #1). GET /v3/stockMovements is the ask. Until it ships the entity does not declare list/read at all, so a caller learns this from the contract instead of a 404.</t>
+          <t>Choosing the picking strategy (single/multiOrder/wave/zone) at creation — no create endpoint today.</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr"/>
@@ -11010,17 +11004,17 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>StockMovement</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>tasks</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
@@ -11030,7 +11024,7 @@
       </c>
       <c r="E147" s="9" t="inlineStr">
         <is>
-          <t>A booking returns no identity: the v1 storage-item endpoints answer 201 with an empty body and — contrary to their own spec — send no Location header (verified on mvp 2026-07-31). Without an id a repeated booking cannot be recognised afterwards, which is why correction+setQuantityTo is the only retry-safe write. The ask: return the specced Location header, or the created movement.</t>
+          <t>Task-level detail (location, product, quantity, status per pick) is not exposed on the pickLists API — needed for progress boards and pick-path optimisation.</t>
         </is>
       </c>
       <c r="F147" s="9" t="inlineStr"/>
@@ -11038,17 +11032,17 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>StockMovement</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>unitCost</t>
+          <t>tasks.status</t>
         </is>
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
@@ -11058,7 +11052,7 @@
       </c>
       <c r="E148" s="9" t="inlineStr">
         <is>
-          <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
+          <t>Granular task-level pick confirmation with quantity + scans (docs/05 #3) — today only whole-list start/complete exists.</t>
         </is>
       </c>
       <c r="F148" s="9" t="inlineStr"/>
@@ -11066,7 +11060,7 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -11076,7 +11070,7 @@
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>list, read</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
@@ -11086,7 +11080,7 @@
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>Starting a stock take via API (scope: warehouse/locations/products, key date) — the v1 inventory endpoints exist but the write orchestration is not built yet.</t>
+          <t>Batches exist only as read-only v3 Product includes — no batch resource, no list, no detail (docs/05 #4). GET /v3/batches is the ask.</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr"/>
@@ -11094,17 +11088,17 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
-          <t>dates.keyDate</t>
+          <t>bestBefore</t>
         </is>
       </c>
       <c r="C150" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
@@ -11114,7 +11108,7 @@
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>The inventory key date (Stichtag) is not exposed by v1 inventoryRuns.</t>
+          <t>Correcting a best-before date via API — internal web routes only today.</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr"/>
@@ -11122,17 +11116,17 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
-          <t>dates.posted</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
@@ -11142,7 +11136,7 @@
       </c>
       <c r="E151" s="9" t="inlineStr">
         <is>
-          <t>The posted timestamp is not exposed by v1 inventoryRuns.</t>
+          <t>Blocking/releasing a batch (quality hold) via API — maintenance happens only through internal web routes today.</t>
         </is>
       </c>
       <c r="F151" s="9" t="inlineStr"/>
@@ -11150,12 +11144,12 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
         <is>
-          <t>positions</t>
+          <t>trace</t>
         </is>
       </c>
       <c r="C152" s="7" t="inlineStr">
@@ -11170,7 +11164,7 @@
       </c>
       <c r="E152" s="9" t="inlineStr">
         <is>
-          <t>Counting positions (expected/counted/difference with values) live in the counting-list reports — not composed into the API payload yet; needed for the GoBD difference review.</t>
+          <t>Batch trace (which goods receipts brought it in, which delivery notes shipped it — recall scenario) has no API at all (docs/05 #4).</t>
         </is>
       </c>
       <c r="F152" s="9" t="inlineStr"/>
@@ -11178,45 +11172,49 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
         <is>
-          <t>positions.counted</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D153" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E153" s="9" t="inlineStr">
         <is>
-          <t>Submitting counted quantities via API (mobile counting) — needed for headless inventory.</t>
-        </is>
-      </c>
-      <c r="F153" s="9" t="inlineStr"/>
+          <t>The platform kind (shopify/amazon/…) is not exposed — the BF salesChannel entity carries only a name (05 #17).</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>documents.stockMovements</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
@@ -11226,7 +11224,7 @@
       </c>
       <c r="E154" s="9" t="inlineStr">
         <is>
-          <t>Posted correction movements per stock take need the stockMovements API (docs/05 #1) to be traceable.</t>
+          <t>REVISED (docs/05 #17): BF salesChannel has CRUD — our facade write-mapping + live verification is pending.</t>
         </is>
       </c>
       <c r="F154" s="9" t="inlineStr"/>
@@ -11234,17 +11232,17 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read, create, update</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
@@ -11254,7 +11252,7 @@
       </c>
       <c r="E155" s="9" t="inlineStr">
         <is>
-          <t>Creating a picking run by criteria (wave: channel, shipping method, cutoff, maxOrders) has NO upstream endpoint — the main gap (docs/05 #3); execution (start/complete, totes) already exists.</t>
+          <t>The channel type (shop/marketplace/direct/pos) is not on the BF salesChannel record — needed for channel-specific routing.</t>
         </is>
       </c>
       <c r="F155" s="9" t="inlineStr"/>
@@ -11262,17 +11260,17 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
         <is>
-          <t>criteria</t>
+          <t>assignee</t>
         </is>
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
@@ -11282,7 +11280,7 @@
       </c>
       <c r="E156" s="9" t="inlineStr">
         <is>
-          <t>Pick-run criteria (channel, shipping method) are not exposed by v1 pickLists.</t>
+          <t>The one thing that would make a task a work item. `assignee` is readOnly upstream: a create or update carrying it answers 2xx and leaves the field null. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F156" s="9" t="inlineStr"/>
@@ -11290,17 +11288,17 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>dates.completed</t>
         </is>
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
@@ -11310,7 +11308,7 @@
       </c>
       <c r="E157" s="9" t="inlineStr">
         <is>
-          <t>The picked sales orders are not exposed by v1 pickLists (only counts).</t>
+          <t>Completing a task through the API does not stamp its completion date: `status: completed` persists, `completionDate` stays null.</t>
         </is>
       </c>
       <c r="F157" s="9" t="inlineStr"/>
@@ -11318,12 +11316,12 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
-          <t>containers</t>
+          <t>timeline</t>
         </is>
       </c>
       <c r="C158" s="7" t="inlineStr">
@@ -11331,388 +11329,20 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D158" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D158" s="13" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E158" s="9" t="inlineStr">
         <is>
-          <t>Totes/containers are not exposed by v1 pickLists.</t>
+          <t>The task's comment thread. Declared `readWrite` with a full sub-node and returned by NO read — not the list, not the single read, and no include/expand parameter produces it. Not modelled until it reads back.</t>
         </is>
       </c>
       <c r="F158" s="9" t="inlineStr"/>
     </row>
-    <row r="159">
-      <c r="A159" s="7" t="inlineStr">
-        <is>
-          <t>PickingRun</t>
-        </is>
-      </c>
-      <c r="B159" s="7" t="inlineStr">
-        <is>
-          <t>strategy</t>
-        </is>
-      </c>
-      <c r="C159" s="7" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="D159" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E159" s="9" t="inlineStr">
-        <is>
-          <t>Choosing the picking strategy (single/multiOrder/wave/zone) at creation — no create endpoint today.</t>
-        </is>
-      </c>
-      <c r="F159" s="9" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="7" t="inlineStr">
-        <is>
-          <t>PickingRun</t>
-        </is>
-      </c>
-      <c r="B160" s="7" t="inlineStr">
-        <is>
-          <t>tasks</t>
-        </is>
-      </c>
-      <c r="C160" s="7" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D160" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E160" s="9" t="inlineStr">
-        <is>
-          <t>Task-level detail (location, product, quantity, status per pick) is not exposed on the pickLists API — needed for progress boards and pick-path optimisation.</t>
-        </is>
-      </c>
-      <c r="F160" s="9" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="7" t="inlineStr">
-        <is>
-          <t>PickingRun</t>
-        </is>
-      </c>
-      <c r="B161" s="7" t="inlineStr">
-        <is>
-          <t>tasks.status</t>
-        </is>
-      </c>
-      <c r="C161" s="7" t="inlineStr">
-        <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D161" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E161" s="9" t="inlineStr">
-        <is>
-          <t>Granular task-level pick confirmation with quantity + scans (docs/05 #3) — today only whole-list start/complete exists.</t>
-        </is>
-      </c>
-      <c r="F161" s="9" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="7" t="inlineStr">
-        <is>
-          <t>Batch</t>
-        </is>
-      </c>
-      <c r="B162" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C162" s="7" t="inlineStr">
-        <is>
-          <t>list, read</t>
-        </is>
-      </c>
-      <c r="D162" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E162" s="9" t="inlineStr">
-        <is>
-          <t>Batches exist only as read-only v3 Product includes — no batch resource, no list, no detail (docs/05 #4). GET /v3/batches is the ask.</t>
-        </is>
-      </c>
-      <c r="F162" s="9" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="7" t="inlineStr">
-        <is>
-          <t>Batch</t>
-        </is>
-      </c>
-      <c r="B163" s="7" t="inlineStr">
-        <is>
-          <t>bestBefore</t>
-        </is>
-      </c>
-      <c r="C163" s="7" t="inlineStr">
-        <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D163" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E163" s="9" t="inlineStr">
-        <is>
-          <t>Correcting a best-before date via API — internal web routes only today.</t>
-        </is>
-      </c>
-      <c r="F163" s="9" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="7" t="inlineStr">
-        <is>
-          <t>Batch</t>
-        </is>
-      </c>
-      <c r="B164" s="7" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C164" s="7" t="inlineStr">
-        <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D164" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E164" s="9" t="inlineStr">
-        <is>
-          <t>Blocking/releasing a batch (quality hold) via API — maintenance happens only through internal web routes today.</t>
-        </is>
-      </c>
-      <c r="F164" s="9" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="7" t="inlineStr">
-        <is>
-          <t>Batch</t>
-        </is>
-      </c>
-      <c r="B165" s="7" t="inlineStr">
-        <is>
-          <t>trace</t>
-        </is>
-      </c>
-      <c r="C165" s="7" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D165" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E165" s="9" t="inlineStr">
-        <is>
-          <t>Batch trace (which goods receipts brought it in, which delivery notes shipped it — recall scenario) has no API at all (docs/05 #4).</t>
-        </is>
-      </c>
-      <c r="F165" s="9" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="7" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B166" s="7" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C166" s="7" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D166" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
-        </is>
-      </c>
-      <c r="E166" s="9" t="inlineStr">
-        <is>
-          <t>The platform kind (shopify/amazon/…) is not exposed — the BF salesChannel entity carries only a name (05 #17).</t>
-        </is>
-      </c>
-      <c r="F166" s="9" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="7" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B167" s="7" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C167" s="7" t="inlineStr">
-        <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D167" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E167" s="9" t="inlineStr">
-        <is>
-          <t>REVISED (docs/05 #17): BF salesChannel has CRUD — our facade write-mapping + live verification is pending.</t>
-        </is>
-      </c>
-      <c r="F167" s="9" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="7" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B168" s="7" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C168" s="7" t="inlineStr">
-        <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D168" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E168" s="9" t="inlineStr">
-        <is>
-          <t>The channel type (shop/marketplace/direct/pos) is not on the BF salesChannel record — needed for channel-specific routing.</t>
-        </is>
-      </c>
-      <c r="F168" s="9" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="7" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B169" s="7" t="inlineStr">
-        <is>
-          <t>assignee</t>
-        </is>
-      </c>
-      <c r="C169" s="7" t="inlineStr">
-        <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D169" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E169" s="9" t="inlineStr">
-        <is>
-          <t>The one thing that would make a task a work item. `assignee` is readOnly upstream: a create or update carrying it answers 2xx and leaves the field null. Measured on mvp 2026-08-02.</t>
-        </is>
-      </c>
-      <c r="F169" s="9" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="7" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B170" s="7" t="inlineStr">
-        <is>
-          <t>dates.completed</t>
-        </is>
-      </c>
-      <c r="C170" s="7" t="inlineStr">
-        <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D170" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E170" s="9" t="inlineStr">
-        <is>
-          <t>Completing a task through the API does not stamp its completion date: `status: completed` persists, `completionDate` stays null.</t>
-        </is>
-      </c>
-      <c r="F170" s="9" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="7" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B171" s="7" t="inlineStr">
-        <is>
-          <t>timeline</t>
-        </is>
-      </c>
-      <c r="C171" s="7" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D171" s="13" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
-        </is>
-      </c>
-      <c r="E171" s="9" t="inlineStr">
-        <is>
-          <t>The task's comment thread. Declared `readWrite` with a full sub-node and returned by NO read — not the list, not the single read, and no include/expand parameter produces it. Not modelled until it reads back.</t>
-        </is>
-      </c>
-      <c r="F171" s="9" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F171"/>
+  <autoFilter ref="A1:F158"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Übersicht'!$A$6:$H$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fähigkeiten'!$A$1:$F$181</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Felder'!$A$1:$F$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Felder'!$A$1:$F$153</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -621,12 +621,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="9">
@@ -681,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
@@ -801,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
@@ -889,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
@@ -6854,7 +6852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F158"/>
+  <dimension ref="A1:F153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7101,12 +7099,12 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -7116,7 +7114,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Carrying a quote number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+          <t>Reassign the quote's partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr"/>
@@ -7129,12 +7127,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>references.customerInquiryNumber</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -7144,7 +7142,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Reassign the quote's partner after creation — v3 accepts it only on create.</t>
+          <t>The customer's inquiry / RFQ number — B2B standard; read-only upstream today.</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr"/>
@@ -7157,7 +7155,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>references.customerInquiryNumber</t>
+          <t>dates.validUntil</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -7172,7 +7170,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>The customer's inquiry / RFQ number — B2B standard; read-only upstream today.</t>
+          <t>Offer validity date — drives auto-expiry and follow-up; must be settable per quote.</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr"/>
@@ -7185,7 +7183,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>dates.validUntil</t>
+          <t>dates.requestedDelivery</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -7200,7 +7198,7 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Offer validity date — drives auto-expiry and follow-up; must be settable per quote.</t>
+          <t>Desired delivery date on the quote — not writable upstream today.</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr"/>
@@ -7213,7 +7211,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>dates.expectedOrderDate</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -7228,7 +7226,7 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Expected order date feeds the sales forecast — settable per quote.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr"/>
@@ -7241,7 +7239,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>dates.requestedDelivery</t>
+          <t>items.isOptional</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -7256,7 +7254,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Desired delivery date on the quote — not writable upstream today.</t>
+          <t>Optional line items (not counted in totals) are a core quoting feature — not settable upstream today.</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr"/>
@@ -7269,7 +7267,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>payment.method</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -7284,7 +7282,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Payment method proposed on the quote — frequently set per offer.</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr"/>
@@ -7297,7 +7295,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>items.isOptional</t>
+          <t>payment.terms.dueDays</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -7312,7 +7310,7 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Optional line items (not counted in totals) are a core quoting feature — not settable upstream today.</t>
+          <t>Payment term proposed on the quote.</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr"/>
@@ -7325,7 +7323,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>payment.method</t>
+          <t>shipping.method</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -7333,17 +7331,21 @@
           <t>create, update</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Payment method proposed on the quote — frequently set per offer.</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr"/>
+          <t>Shipping method proposed on the quote.</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create, update</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -7353,7 +7355,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>payment.terms.dueDays</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -7368,7 +7370,7 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Payment term proposed on the quote.</t>
+          <t>Custom field values on the quote — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr"/>
@@ -7381,44 +7383,40 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>shipping.method</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Shipping method proposed on the quote.</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>SalesOrder</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -7428,7 +7426,7 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Custom field values on the quote — today only readable via include, not writable via API.</t>
+          <t>Correcting a sales order number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr"/>
@@ -7436,27 +7434,27 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>SalesOrder</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+          <t>Reassign the order to the correct customer after creation — v3 accepts the partner only on create today.</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr"/>
@@ -7469,25 +7467,29 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Correcting a sales order number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr"/>
+          <t>The customer's own order / PO number (B2B standard field). Read-only upstream today; a clerk must be able to set and correct it.</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -7497,12 +7499,12 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>references.externalId</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -7512,7 +7514,7 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Reassign the order to the correct customer after creation — v3 accepts the partner only on create today.</t>
+          <t>Automated reconciliation matches by the external id.</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr"/>
@@ -7525,12 +7527,12 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>dates.requestedDelivery</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -7540,12 +7542,12 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>The customer's own order / PO number (B2B standard field). Read-only upstream today; a clerk must be able to set and correct it.</t>
+          <t>Desired delivery date — core fulfilment field; one of the first things entered on an order. Not writable upstream today.</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Schema deklariert: create</t>
+          <t>Schema deklariert: update</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7559,12 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>references.externalId</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -7572,7 +7574,7 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Automated reconciliation matches by the external id.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr"/>
@@ -7585,12 +7587,12 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>dates.requestedDelivery</t>
+          <t>shipping.method</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -7600,12 +7602,12 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>Desired delivery date — core fulfilment field; one of the first things entered on an order. Not writable upstream today.</t>
+          <t>Carrier / shipping method — core to fulfilment; must be selectable per order.</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Schema deklariert: update</t>
+          <t>Schema deklariert: create, update</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7619,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>fulfillmentPolicy.partialShipping</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -7632,7 +7634,7 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Partial-shipping policy has no upstream slot — the read reports a hardcoded "allowed". Needs a real v3 field before it can be written or trusted.</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr"/>
@@ -7645,29 +7647,25 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>shipping.method</t>
+          <t>discounts</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Carrier / shipping method — core to fulfilment; must be selectable per order.</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create, update</t>
-        </is>
-      </c>
+          <t>Header discounts/vouchers (e-commerce) are not exposed by v3 salesOrders — only line-level discounts exist.</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -7677,7 +7675,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>fulfillmentPolicy.partialShipping</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -7692,7 +7690,7 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Partial-shipping policy has no upstream slot — the read reports a hardcoded "allowed". Needs a real v3 field before it can be written or trusted.</t>
+          <t>Custom field values carry company-specific data — today only readable via include, not writable via API (all documents).</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr"/>
@@ -7705,12 +7703,12 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>discounts</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
@@ -7720,7 +7718,7 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>Header discounts/vouchers (e-commerce) are not exposed by v3 salesOrders — only line-level discounts exist.</t>
+          <t>Companies segment and find orders by their own custom-field values.</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr"/>
@@ -7733,22 +7731,22 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Custom field values carry company-specific data — today only readable via include, not writable via API (all documents).</t>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr"/>
@@ -7756,17 +7754,17 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>SalesOrder</t>
+          <t>DeliveryNote</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
@@ -7776,7 +7774,7 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Companies segment and find orders by their own custom-field values.</t>
+          <t>Reassign the delivery note's partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr"/>
@@ -7784,30 +7782,34 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>SalesOrder</t>
+          <t>DeliveryNote</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr"/>
+          <t>The customer's PO number on the delivery note (B2B) — read-only upstream today; must be settable.</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -7817,12 +7819,12 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
@@ -7832,7 +7834,7 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Carrying a delivery note number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+          <t>Warehouse/support find a delivery note by the customer's PO number.</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr"/>
@@ -7845,12 +7847,12 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -7860,7 +7862,7 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Reassign the delivery note's partner after creation — v3 accepts it only on create.</t>
+          <t>The picking/shipping warehouse — must be selectable per delivery note, not fixed to the default.</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr"/>
@@ -7873,29 +7875,25 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>The customer's PO number on the delivery note (B2B) — read-only upstream today; must be settable.</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Adjust delivered positions/quantities after creation — the v3 update DTO carries no line-item write path.</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -7905,12 +7903,12 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>shipments</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -7920,7 +7918,7 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Warehouse/support find a delivery note by the customer's PO number.</t>
+          <t>Tracking numbers need a nachlade GET /v1/deliveryNotes/{id}/shipments — not yet composed into the read payload.</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr"/>
@@ -7933,7 +7931,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>customs.totalWeight</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -7948,7 +7946,7 @@
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>The picking/shipping warehouse — must be selectable per delivery note, not fixed to the default.</t>
+          <t>Total shipment weight for the customs declaration / carrier — needs to be settable.</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr"/>
@@ -7961,12 +7959,12 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>customs.incoterm</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -7976,7 +7974,7 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Adjust delivered positions/quantities after creation — the v3 update DTO carries no line-item write path.</t>
+          <t>Incoterm for export shipments — a customs-declaration essential, not settable via API today.</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr"/>
@@ -7989,12 +7987,12 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>shipments</t>
+          <t>customs.note</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
@@ -8004,7 +8002,7 @@
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Tracking numbers need a nachlade GET /v1/deliveryNotes/{id}/shipments — not yet composed into the read payload.</t>
+          <t>Customs note for export paperwork.</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr"/>
@@ -8017,7 +8015,7 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>customs.totalWeight</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -8032,7 +8030,7 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>Total shipment weight for the customs declaration / carrier — needs to be settable.</t>
+          <t>Custom field values on the delivery note — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr"/>
@@ -8040,17 +8038,17 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>DeliveryNote</t>
+          <t>Shipment</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>customs.incoterm</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
@@ -8060,7 +8058,7 @@
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>Incoterm for export shipments — a customs-declaration essential, not settable via API today.</t>
+          <t>Creating a shipment + label via the facade (POST /v1/shipments + createLabel exists upstream) is not orchestrated here yet — needed for headless fulfilment.</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr"/>
@@ -8068,17 +8066,17 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>DeliveryNote</t>
+          <t>Shipment</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>customs.note</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
@@ -8088,7 +8086,7 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Customs note for export paperwork.</t>
+          <t>The shipment lifecycle status is not exposed by v1 shipments — only sentAt exists.</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr"/>
@@ -8096,17 +8094,17 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>DeliveryNote</t>
+          <t>Shipment</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
@@ -8116,7 +8114,7 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>Custom field values on the delivery note — today only readable via include, not writable via API.</t>
+          <t>Package weight is not exposed by v1 shipments.</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr"/>
@@ -8129,12 +8127,12 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>events</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
@@ -8144,7 +8142,7 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Creating a shipment + label via the facade (POST /v1/shipments + createLabel exists upstream) is not orchestrated here yet — needed for headless fulfilment.</t>
+          <t>Carrier tracking events are not exposed — needs a carrier-events feed.</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr"/>
@@ -8157,12 +8155,12 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>tracking.number</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
@@ -8172,7 +8170,7 @@
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>The shipment lifecycle status is not exposed by v1 shipments — only sentAt exists.</t>
+          <t>Support looks up a shipment by tracking number — needs a filterable/searchable upstream list parameter.</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr"/>
@@ -8180,17 +8178,17 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>Shipment</t>
+          <t>SalesInvoice</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -8200,7 +8198,7 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>Package weight is not exposed by v1 shipments.</t>
+          <t>Correcting a invoice number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr"/>
@@ -8208,17 +8206,17 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>Shipment</t>
+          <t>SalesInvoice</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>events</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
@@ -8228,7 +8226,7 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Carrier tracking events are not exposed — needs a carrier-events feed.</t>
+          <t>Reassign the invoice's partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr"/>
@@ -8236,30 +8234,34 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Shipment</t>
+          <t>SalesInvoice</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>tracking.number</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>search</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Support looks up a shipment by tracking number — needs a filterable/searchable upstream list parameter.</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="inlineStr"/>
+          <t>The customer's PO number on the invoice (B2B) — read-only upstream today; must be settable and correctable.</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -8269,12 +8271,12 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
@@ -8284,7 +8286,7 @@
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Correcting a invoice number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
+          <t>Support and accounting find invoices by the customer's PO number.</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr"/>
@@ -8297,12 +8299,12 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>references.debtorAccountNumber</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
@@ -8312,7 +8314,7 @@
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Reassign the invoice's partner after creation — v3 accepts it only on create.</t>
+          <t>Deviating debtor account for the FiBu/DATEV export — settable when it differs from the customer default.</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr"/>
@@ -8325,29 +8327,25 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>The customer's PO number on the invoice (B2B) — read-only upstream today; must be settable and correctable.</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -8357,25 +8355,29 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>totals.outstanding</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>search</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Support and accounting find invoices by the customer's PO number.</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="inlineStr"/>
+          <t>Exact open amount needs readable payment↔invoice allocations (docs/05 #2); today only derived from paymentStatus.</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -8385,7 +8387,7 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>references.debtorAccountNumber</t>
+          <t>payment.method</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
@@ -8400,7 +8402,7 @@
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Deviating debtor account for the FiBu/DATEV export — settable when it differs from the customer default.</t>
+          <t>Payment method on the invoice — central to order-to-cash; frequently overridden.</t>
         </is>
       </c>
       <c r="F54" s="9" t="inlineStr"/>
@@ -8413,7 +8415,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>payment.terms.dueDays</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -8428,7 +8430,7 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Net payment term in days — drives the due date and dunning.</t>
         </is>
       </c>
       <c r="F55" s="9" t="inlineStr"/>
@@ -8441,29 +8443,25 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>totals.outstanding</t>
+          <t>payment.terms.discountPercent</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Exact open amount needs readable payment↔invoice allocations (docs/05 #2); today only derived from paymentStatus.</t>
-        </is>
-      </c>
-      <c r="F56" s="9" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>Cash-discount percentage — standard DACH B2B.</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -8473,7 +8471,7 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>payment.method</t>
+          <t>payment.terms.discountDays</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -8488,7 +8486,7 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Payment method on the invoice — central to order-to-cash; frequently overridden.</t>
+          <t>Cash-discount period in days — pairs with the discount.</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr"/>
@@ -8501,25 +8499,29 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>payment.terms.dueDays</t>
+          <t>eInvoice</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Net payment term in days — drives the due date and dunning.</t>
-        </is>
-      </c>
-      <c r="F58" s="9" t="inlineStr"/>
+          <t>The finished ZUGFeRD/XRechnung artefact + delivery status is a missing upstream API (docs/05 #7) — only XML raw data exists today.</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -8529,7 +8531,7 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>payment.terms.discountPercent</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -8544,7 +8546,7 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Cash-discount percentage — standard DACH B2B.</t>
+          <t>Custom field values on the invoice — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F59" s="9" t="inlineStr"/>
@@ -8557,22 +8559,22 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>payment.terms.discountDays</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D60" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Cash-discount period in days — pairs with the discount.</t>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr"/>
@@ -8580,49 +8582,45 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>eInvoice</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>The finished ZUGFeRD/XRechnung artefact + delivery status is a missing upstream API (docs/05 #7) — only XML raw data exists today.</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>No payment LIST/filter exists upstream — only GET /paymentTransactions/{id} (docs/05 #2). GET /v3/payments with filters is the ask.</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
@@ -8632,7 +8630,7 @@
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>Custom field values on the invoice — today only readable via include, not writable via API.</t>
+          <t>Payout/settlement aggregation (fees, chargebacks) per provider needs docs/05 #8.</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr"/>
@@ -8640,27 +8638,27 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>allocations</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D63" s="13" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>read, update</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+          <t>Payment↔invoice allocations (n:m) are neither readable nor writable — without them exact outstanding amounts are impossible (docs/05 #2).</t>
         </is>
       </c>
       <c r="F63" s="9" t="inlineStr"/>
@@ -8668,17 +8666,17 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
@@ -8688,7 +8686,7 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>No payment LIST/filter exists upstream — only GET /paymentTransactions/{id} (docs/05 #2). GET /v3/payments with filters is the ask.</t>
+          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr"/>
@@ -8696,17 +8694,17 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>references.rmaNumber</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
@@ -8716,7 +8714,7 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>Payout/settlement aggregation (fees, chargebacks) per provider needs docs/05 #8.</t>
+          <t>The RMA number the customer quotes — no upstream field today; core to returns handling.</t>
         </is>
       </c>
       <c r="F65" s="9" t="inlineStr"/>
@@ -8724,17 +8722,17 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>allocations</t>
+          <t>references.rmaNumber</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
@@ -8744,7 +8742,7 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>Payment↔invoice allocations (n:m) are neither readable nor writable — without them exact outstanding amounts are impossible (docs/05 #2).</t>
+          <t>Support finds a return by the RMA number the customer has.</t>
         </is>
       </c>
       <c r="F66" s="9" t="inlineStr"/>
@@ -8757,12 +8755,12 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -8772,7 +8770,7 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>Carrying a return number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+          <t>The customer's PO number on the return — read-only upstream today.</t>
         </is>
       </c>
       <c r="F67" s="9" t="inlineStr"/>
@@ -8785,12 +8783,12 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
@@ -8800,7 +8798,7 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
+          <t>The returns warehouse must be selectable per return.</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr"/>
@@ -8813,12 +8811,12 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>references.rmaNumber</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
@@ -8828,7 +8826,7 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>The RMA number the customer quotes — no upstream field today; core to returns handling.</t>
+          <t>Edit return positions after creation — the v3 update DTO carries no line-item write path.</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr"/>
@@ -8841,25 +8839,29 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>references.rmaNumber</t>
+          <t>items.reason</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>search</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Support finds a return by the RMA number the customer has.</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr"/>
+          <t>The return reason per line — essential for returns analytics; not settable via API today.</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -8869,7 +8871,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>items.condition</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -8884,7 +8886,7 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>The customer's PO number on the return — read-only upstream today.</t>
+          <t>Item condition (resellable/damaged/disposal) drives restocking — not in the v3 payload yet.</t>
         </is>
       </c>
       <c r="F71" s="9" t="inlineStr"/>
@@ -8897,12 +8899,12 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>items.condition</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
@@ -8912,7 +8914,7 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>The returns warehouse must be selectable per return.</t>
+          <t>Item condition is not surfaced by the v3 return payload yet (docs/05 #4 batch/trace family).</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr"/>
@@ -8925,12 +8927,12 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>items.action</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
@@ -8940,7 +8942,7 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Edit return positions after creation — the v3 update DTO carries no line-item write path.</t>
+          <t>Resolution per line (credit/replace/repair) — not in the v3 payload yet.</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr"/>
@@ -8953,7 +8955,7 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>items.reason</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
@@ -8961,36 +8963,32 @@
           <t>create, update</t>
         </is>
       </c>
-      <c r="D74" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>The return reason per line — essential for returns analytics; not settable via API today.</t>
-        </is>
-      </c>
-      <c r="F74" s="9" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Custom field values on the return — today only readable via include, not writable via API.</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>items.condition</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
@@ -9000,7 +8998,7 @@
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>Item condition (resellable/damaged/disposal) drives restocking — not in the v3 payload yet.</t>
+          <t>Correcting a credit note number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr"/>
@@ -9008,17 +9006,17 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>items.condition</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
@@ -9028,7 +9026,7 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>Item condition is not surfaced by the v3 return payload yet (docs/05 #4 batch/trace family).</t>
+          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr"/>
@@ -9036,40 +9034,44 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>items.action</t>
+          <t>references.customerOrderNumber</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>Resolution per line (credit/replace/repair) — not in the v3 payload yet.</t>
-        </is>
-      </c>
-      <c r="F77" s="9" t="inlineStr"/>
+          <t>The customer's PO number on the credit note (B2B) — read-only upstream today.</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>references.debtorAccountNumber</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
@@ -9084,7 +9086,7 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>Custom field values on the return — today only readable via include, not writable via API.</t>
+          <t>Deviating debtor account for the FiBu/DATEV export of the credit note.</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr"/>
@@ -9097,12 +9099,12 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>dates.serviceDate</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
@@ -9112,7 +9114,7 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>Correcting a credit note number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
+          <t>Leistungsdatum — a §14 UStG mandatory field on the credit note; must be settable.</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr"/>
@@ -9125,12 +9127,12 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
@@ -9140,7 +9142,7 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr"/>
@@ -9153,12 +9155,12 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>totals.outstanding</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
@@ -9168,12 +9170,12 @@
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>The customer's PO number on the credit note (B2B) — read-only upstream today.</t>
+          <t>Exact open amount needs readable refund/offset allocations (docs/05 #2); today derived from paymentStatus only.</t>
         </is>
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>Schema deklariert: create</t>
+          <t>live bewiesen für: read</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9187,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>references.debtorAccountNumber</t>
+          <t>settlement.mode</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
@@ -9200,7 +9202,7 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>Deviating debtor account for the FiBu/DATEV export of the credit note.</t>
+          <t>Refund vs offset-against-invoice is a per-credit-note decision — not settable upstream today.</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr"/>
@@ -9213,7 +9215,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>dates.serviceDate</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -9228,7 +9230,7 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>Leistungsdatum — a §14 UStG mandatory field on the credit note; must be settable.</t>
+          <t>Custom field values on the credit note — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr"/>
@@ -9241,22 +9243,22 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D84" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr"/>
@@ -9264,44 +9266,40 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>totals.outstanding</t>
+          <t>defaults.shippingMethod</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D85" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>Exact open amount needs readable refund/offset allocations (docs/05 #2); today derived from paymentStatus only.</t>
-        </is>
-      </c>
-      <c r="F85" s="9" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>The default shipping method is not surfaced by the v3 partner read.</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>settlement.mode</t>
+          <t>defaults.paymentTerms.dueDays</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
@@ -9316,7 +9314,7 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Refund vs offset-against-invoice is a per-credit-note decision — not settable upstream today.</t>
+          <t>Default supplier payment term — drives liability due dates.</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr"/>
@@ -9324,17 +9322,17 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>finance.creditorAccountNumber</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
@@ -9344,7 +9342,7 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>Custom field values on the credit note — today only readable via include, not writable via API.</t>
+          <t>The creditor account for the FiBu/DATEV export — settable per supplier.</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr"/>
@@ -9352,27 +9350,27 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D88" s="13" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+          <t>Custom field values on the supplier — today only readable, not writable via API.</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr"/>
@@ -9380,12 +9378,12 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>defaults.shippingMethod</t>
+          <t>supplier</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -9400,7 +9398,7 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>The default shipping method is not surfaced by the v3 partner read.</t>
+          <t>Reassign the PO's supplier after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr"/>
@@ -9408,12 +9406,12 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>defaults.paymentTerms.dueDays</t>
+          <t>references.ourCustomerNumber</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
@@ -9428,7 +9426,7 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Default supplier payment term — drives liability due dates.</t>
+          <t>Our customer number at the supplier — belongs on the PO, not settable via API today.</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr"/>
@@ -9436,17 +9434,17 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>finance.creditorAccountNumber</t>
+          <t>references.supplierOfferNumber</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
@@ -9456,7 +9454,7 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>The creditor account for the FiBu/DATEV export — settable per supplier.</t>
+          <t>The supplier's quote number we ordered against — read-only upstream today.</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr"/>
@@ -9464,17 +9462,17 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>confirmation.status</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
@@ -9484,7 +9482,7 @@
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>Custom field values on the supplier — today only readable, not writable via API.</t>
+          <t>Recording the confirmation status (pending/confirmed/deviating) is core purchasing — not writable via API today.</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr"/>
@@ -9497,12 +9495,12 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>confirmation.supplierOrderNumber</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
@@ -9512,7 +9510,7 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>Carrying a purchase order number over from another system. The v3 create does not declare documentNumber for this document type and ignores a supplied value without an error, so the core refuses it instead. salesOrder, invoice and creditNote do accept one.</t>
+          <t>The AB (order-confirmation) number from the supplier — the whole confirmation block is read-only upstream (docs/05: AB handling).</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr"/>
@@ -9525,12 +9523,12 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>supplier</t>
+          <t>dates.requestedDelivery</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
@@ -9540,7 +9538,7 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Reassign the PO's supplier after creation — v3 accepts it only on create.</t>
+          <t>Requested delivery date at the supplier — not writable upstream today.</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr"/>
@@ -9553,7 +9551,7 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>references.ourCustomerNumber</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -9568,7 +9566,7 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>Our customer number at the supplier — belongs on the PO, not settable via API today.</t>
+          <t>The receiving warehouse for the PO must be selectable.</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr"/>
@@ -9581,12 +9579,12 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>references.supplierOfferNumber</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
@@ -9596,7 +9594,7 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>The supplier's quote number we ordered against — read-only upstream today.</t>
+          <t>Edit PO positions after creation — the v3 update DTO carries no line-item write path.</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr"/>
@@ -9609,12 +9607,12 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>confirmation.status</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
@@ -9624,7 +9622,7 @@
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>Recording the confirmation status (pending/confirmed/deviating) is core purchasing — not writable via API today.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr"/>
@@ -9637,12 +9635,12 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>confirmation.supplierOrderNumber</t>
+          <t>dropship</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read, create</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
@@ -9652,7 +9650,7 @@
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>The AB (order-confirmation) number from the supplier — the whole confirmation block is read-only upstream (docs/05: AB handling).</t>
+          <t>Dropshipping (Strecke: salesOrder link + customer delivery address) is not exposed via v3 purchaseOrders.</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr"/>
@@ -9665,7 +9663,7 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>dates.requestedDelivery</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -9680,7 +9678,7 @@
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>Requested delivery date at the supplier — not writable upstream today.</t>
+          <t>Custom field values on the PO — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr"/>
@@ -9688,17 +9686,17 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>references.supplierDeliveryNoteNumber</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>create, update, read</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -9708,7 +9706,7 @@
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>The receiving warehouse for the PO must be selectable.</t>
+          <t>The supplier's delivery-note number on the goods receipt — needed for the three-way match; not in the BF record yet.</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr"/>
@@ -9716,17 +9714,17 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>dates.received</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
@@ -9736,7 +9734,7 @@
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>Edit PO positions after creation — the v3 update DTO carries no line-item write path.</t>
+          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr"/>
@@ -9744,17 +9742,17 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>dates.posted</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
@@ -9764,7 +9762,7 @@
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr"/>
@@ -9772,17 +9770,17 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>dropship</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>read, create</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
@@ -9792,7 +9790,7 @@
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>Dropshipping (Strecke: salesOrder link + customer delivery address) is not exposed via v3 purchaseOrders.</t>
+          <t>Cancel/storno of a posted goods receipt — the remaining upstream gap after the BF entity list covered browsing (docs/05 #9 revised).</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr"/>
@@ -9800,17 +9798,17 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, create, update</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -9820,7 +9818,7 @@
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>Custom field values on the PO — today only readable via include, not writable via API.</t>
+          <t>Line items (product × quantity × storage location, quality check per line) are not exposed on the BF goodsReceipt record — creation still goes through the PO action only.</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr"/>
@@ -9828,17 +9826,17 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>references.supplierDeliveryNoteNumber</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>create, update, read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
@@ -9848,7 +9846,7 @@
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>The supplier's delivery-note number on the goods receipt — needed for the three-way match; not in the BF record yet.</t>
+          <t>The document number is system-assigned: sending `documentNumber` on create answers 201 and the record comes back with an empty number (measured on mvp 2026-08-02). Same behaviour as the other documents.</t>
         </is>
       </c>
       <c r="F105" s="9" t="inlineStr"/>
@@ -9856,17 +9854,17 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>dates.received</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
@@ -9876,7 +9874,7 @@
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
+          <t>Filtering incoming invoices by workflow status is the AP daily view — the BF supplierInvoice API does not allow filtering documentStatus today.</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr"/>
@@ -9884,17 +9882,17 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>dates.posted</t>
+          <t>dates.invoiceDate</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>sort</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
@@ -9904,7 +9902,7 @@
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
+          <t>Sorting incoming invoices by invoice date — dateOfSupplierInvoice is not sortable on the BF API today.</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr"/>
@@ -9912,12 +9910,12 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>match.status</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -9932,7 +9930,7 @@
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>Cancel/storno of a posted goods receipt — the remaining upstream gap after the BF entity list covered browsing (docs/05 #9 revised).</t>
+          <t>Re-running/overriding the match verdict via API (rematch) — the check statuses are readable now; a command to re-evaluate is still missing upstream.</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr"/>
@@ -9940,17 +9938,17 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>payment.status</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>read, create, update</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
@@ -9960,7 +9958,7 @@
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>Line items (product × quantity × storage location, quality check per line) are not exposed on the BF goodsReceipt record — creation still goes through the PO action only.</t>
+          <t>Open-liabilities view needs filtering by payment status — not allowed on the BF supplierInvoice API today.</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr"/>
@@ -9973,12 +9971,12 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>approval.status</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
@@ -9988,7 +9986,7 @@
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>The document number is system-assigned: sending `documentNumber` on create answers 201 and the record comes back with an empty number (measured on mvp 2026-08-02). Same behaviour as the other documents.</t>
+          <t>Approve/reject via API: BF process steps (GoodsCheck/InvoiceCheck/Payment) are reported to exist — wiring + live verification of those steps is pending (steps were empty on the test instance's metadata).</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr"/>
@@ -10001,12 +9999,12 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>approval.by</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
@@ -10016,7 +10014,7 @@
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>Filtering incoming invoices by workflow status is the AP daily view — the BF supplierInvoice API does not allow filtering documentStatus today.</t>
+          <t>The approver is not exposed — BF supplierInvoice carries only the check statuses.</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr"/>
@@ -10029,12 +10027,12 @@
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>dates.invoiceDate</t>
+          <t>approval.at</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>sort</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
@@ -10044,7 +10042,7 @@
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>Sorting incoming invoices by invoice date — dateOfSupplierInvoice is not sortable on the BF API today.</t>
+          <t>The approval timestamp is not exposed by the BF supplierInvoice entity.</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr"/>
@@ -10052,17 +10050,17 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>match.status</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
@@ -10072,7 +10070,7 @@
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>Re-running/overriding the match verdict via API (rematch) — the check statuses are readable now; a command to re-evaluate is still missing upstream.</t>
+          <t>The consolidated product kind (ADR-011) should be settable directly instead of juggling isServiceProduct/isFee/isShippingCostsProduct booleans — the v2 create body only exposes isShippingCostsProduct, so service/digital cannot be expressed.</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr"/>
@@ -10080,17 +10078,17 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>payment.status</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
@@ -10100,7 +10098,7 @@
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>Open-liabilities view needs filtering by payment status — not allowed on the BF supplierInvoice API today.</t>
+          <t>Tagging products (assortment curation, campaigns) — product writes now go through v2, but the v2 tags shape ({id,key,name,color}) is not yet mapped/verified, so tag writes stay blue.</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr"/>
@@ -10108,17 +10106,17 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>approval.status</t>
+          <t>prices.sale</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
@@ -10128,7 +10126,7 @@
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>Approve/reject via API: BF process steps (GoodsCheck/InvoiceCheck/Payment) are reported to exist — wiring + live verification of those steps is pending (steps were empty on the test instance's metadata).</t>
+          <t>WRITE works — the sale price is composed as a separate salesPrices write on create/update. READ is still blue: the v3 read model does not carry the sale price (needs the salesPrices include parsed), so a written price is not read back.</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr"/>
@@ -10136,17 +10134,17 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>approval.by</t>
+          <t>tax.profile</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
@@ -10156,7 +10154,7 @@
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>The approver is not exposed — BF supplierInvoice carries only the check statuses.</t>
+          <t>The 16-account tax matrix consolidated into a referenceable taxProfile (ADR-011) — today only the raw taxAccounts embed exists, not a clean reference.</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr"/>
@@ -10164,17 +10162,17 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>approval.at</t>
+          <t>logistics.packagingUnits</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, read, update</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
@@ -10184,7 +10182,7 @@
       </c>
       <c r="E117" s="9" t="inlineStr">
         <is>
-          <t>The approval timestamp is not exposed by the BF supplierInvoice entity.</t>
+          <t>Packaging units (VPE) need the packagingUnits include parsed — not yet mapped.</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr"/>
@@ -10197,12 +10195,12 @@
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>stock.incoming</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
@@ -10212,7 +10210,7 @@
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>The consolidated product kind (ADR-011) should be settable directly instead of juggling isServiceProduct/isFee/isShippingCostsProduct booleans — the v2 create body only exposes isShippingCostsProduct, so service/digital cannot be expressed.</t>
+          <t>Inbound quantity (ordered but not yet received) is the one stock figure Xentral does not compute: /products/{id}/stocks returns physical, sellable, reserved, correction, pseudo, openSalesOrders, calculated and producible — all mapped — but nothing inbound. The per-warehouse split the same call carries is answered by StockLevel (filter[product], narrowed by warehouse), so it is not duplicated onto the product.</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr"/>
@@ -10225,7 +10223,7 @@
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>suppliers</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
@@ -10240,7 +10238,7 @@
       </c>
       <c r="E119" s="9" t="inlineStr">
         <is>
-          <t>Tagging products (assortment curation, campaigns) — product writes now go through v2, but the v2 tags shape ({id,key,name,color}) is not yet mapped/verified, so tag writes stay blue.</t>
+          <t>The default supplier IS writable (mapped to v2 standardSupplier); multi-supplier sourcing (several suppliers with per-supplier price/number) needs a suppliers include/relation not yet mapped, plus a write path.</t>
         </is>
       </c>
       <c r="F119" s="9" t="inlineStr"/>
@@ -10248,12 +10246,12 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>PriceList</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>prices.sale</t>
+          <t>entries</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
@@ -10268,7 +10266,7 @@
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>WRITE works — the sale price is composed as a separate salesPrices write on create/update. READ is still blue: the v3 read model does not carry the sale price (needs the salesPrices include parsed), so a written price is not read back.</t>
+          <t>v1 salesPrices exposes flat price rows (this entity is one row); the grouped priceList with a tier array needs a composer (ADR-012). Write each tier as its own entry (create/update/delete are live via v3/v1 salesPrices).</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr"/>
@@ -10276,12 +10274,12 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StorageLocation</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>tax.profile</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
@@ -10296,7 +10294,7 @@
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>The 16-account tax matrix consolidated into a referenceable taxProfile (ADR-011) — today only the raw taxAccounts embed exists, not a clean reference.</t>
+          <t>Upstream returns the bin description but rejects it on create and update ("The attribute description is not allowed.") — the field is read-only for every API generation we have. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr"/>
@@ -10304,17 +10302,17 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StorageLocation</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>logistics.packagingUnits</t>
+          <t>contents.reserved</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>create, read, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
@@ -10324,7 +10322,7 @@
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>Packaging units (VPE) need the packagingUnits include parsed — not yet mapped.</t>
+          <t>Location contents are composed from the StockLevel projection now; the reserved portion per location stays unavailable — upstream reports reservations only as a product total.</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr"/>
@@ -10332,12 +10330,12 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StorageLocation</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>stock.incoming</t>
+          <t>locationType</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
@@ -10345,14 +10343,14 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D123" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D123" s="13" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>Inbound quantity (ordered but not yet received) is the one stock figure Xentral does not compute: /products/{id}/stocks returns physical, sellable, reserved, correction, pseudo, openSalesOrders, calculated and producible — all mapped — but nothing inbound. The per-warehouse split the same call carries is answered by StockLevel (filter[product], narrowed by warehouse), so it is not duplicated onto the product.</t>
+          <t>v1 accepts a `locationType` on write with 204 but never returns it on any read, so a value written there cannot be verified or shown. Not modelled until upstream reads it back. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr"/>
@@ -10360,17 +10358,17 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>suppliers</t>
+          <t>batch</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, list</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -10380,7 +10378,7 @@
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>The default supplier IS writable (mapped to v2 standardSupplier); multi-supplier sourcing (several suppliers with per-supplier price/number) needs a suppliers include/relation not yet mapped, plus a write path.</t>
+          <t>The batch split exists on the v2 items path (qualityControlAttributes) but not on /v1/products/{id}/storageLocations. Emitting batch rows on one anchor only would make the grain depend on the filter, so the projection stays product × storage location. A unified GET /v3/stockLevels is the clean ask (docs/05 #18).</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr"/>
@@ -10388,17 +10386,17 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>PriceList</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>entries</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -10408,7 +10406,7 @@
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>v1 salesPrices exposes flat price rows (this entity is one row); the grouped priceList with a tier array needs a composer (ADR-012). Write each tier as its own entry (create/update/delete are live via v3/v1 salesPrices).</t>
+          <t>The list needs an anchor filter (product or storageLocation): upstream has no global stock collection, so an unanchored query would mean fanning out over every product of the tenant.</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr"/>
@@ -10416,17 +10414,17 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>StorageLocation</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
@@ -10436,7 +10434,7 @@
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>Upstream returns the bin description but rejects it on create and update ("The attribute description is not allowed.") — the field is read-only for every API generation we have. Measured on mvp 2026-08-02.</t>
+          <t>No per-location reservation is exposed upstream; /v1/products/{id}/stocks reports reserved only as a product TOTAL. The projection reports quantity and leaves reserved/available blank rather than spreading a total over locations.</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr"/>
@@ -10444,12 +10442,12 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>StorageLocation</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>contents.reserved</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
@@ -10464,7 +10462,7 @@
       </c>
       <c r="E127" s="9" t="inlineStr">
         <is>
-          <t>Location contents are composed from the StockLevel projection now; the reserved portion per location stays unavailable — upstream reports reservations only as a product total.</t>
+          <t>Same gap as reserved: available = quantity - reserved is only derivable per product, not per storage location.</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr"/>
@@ -10472,27 +10470,27 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>StorageLocation</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>locationType</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D128" s="13" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>list, read</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E128" s="9" t="inlineStr">
         <is>
-          <t>v1 accepts a `locationType` on write with 204 but never returns it on any read, so a value written there cannot be verified or shown. Not modelled until upstream reads it back. Measured on mvp 2026-08-02.</t>
+          <t>The stock ledger (Lagerprotokoll) has NO read API at all — the single biggest gap (docs/05 #1). GET /v3/stockMovements is the ask. Until it ships the entity does not declare list/read at all, so a caller learns this from the contract instead of a 404.</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr"/>
@@ -10500,17 +10498,17 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>batch</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>read, list</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
@@ -10520,7 +10518,7 @@
       </c>
       <c r="E129" s="9" t="inlineStr">
         <is>
-          <t>The batch split exists on the v2 items path (qualityControlAttributes) but not on /v1/products/{id}/storageLocations. Emitting batch rows on one anchor only would make the grain depend on the filter, so the projection stays product × storage location. A unified GET /v3/stockLevels is the clean ask (docs/05 #18).</t>
+          <t>A booking returns no identity: the v1 storage-item endpoints answer 201 with an empty body and — contrary to their own spec — send no Location header (verified on mvp 2026-07-31). Without an id a repeated booking cannot be recognised afterwards, which is why correction+setQuantityTo is the only retry-safe write. The ask: return the specced Location header, or the created movement.</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr"/>
@@ -10528,17 +10526,17 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>unitCost</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
@@ -10548,7 +10546,7 @@
       </c>
       <c r="E130" s="9" t="inlineStr">
         <is>
-          <t>The list needs an anchor filter (product or storageLocation): upstream has no global stock collection, so an unanchored query would mean fanning out over every product of the tenant.</t>
+          <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr"/>
@@ -10556,17 +10554,17 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
@@ -10576,7 +10574,7 @@
       </c>
       <c r="E131" s="9" t="inlineStr">
         <is>
-          <t>No per-location reservation is exposed upstream; /v1/products/{id}/stocks reports reserved only as a product TOTAL. The projection reports quantity and leaves reserved/available blank rather than spreading a total over locations.</t>
+          <t>Starting a stock take via API (scope: warehouse/locations/products, key date) — the v1 inventory endpoints exist but the write orchestration is not built yet.</t>
         </is>
       </c>
       <c r="F131" s="9" t="inlineStr"/>
@@ -10584,12 +10582,12 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>dates.keyDate</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
@@ -10604,7 +10602,7 @@
       </c>
       <c r="E132" s="9" t="inlineStr">
         <is>
-          <t>Same gap as reserved: available = quantity - reserved is only derivable per product, not per storage location.</t>
+          <t>The inventory key date (Stichtag) is not exposed by v1 inventoryRuns.</t>
         </is>
       </c>
       <c r="F132" s="9" t="inlineStr"/>
@@ -10612,17 +10610,17 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>StockMovement</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>dates.posted</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>list, read</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
@@ -10632,7 +10630,7 @@
       </c>
       <c r="E133" s="9" t="inlineStr">
         <is>
-          <t>The stock ledger (Lagerprotokoll) has NO read API at all — the single biggest gap (docs/05 #1). GET /v3/stockMovements is the ask. Until it ships the entity does not declare list/read at all, so a caller learns this from the contract instead of a 404.</t>
+          <t>The posted timestamp is not exposed by v1 inventoryRuns.</t>
         </is>
       </c>
       <c r="F133" s="9" t="inlineStr"/>
@@ -10640,17 +10638,17 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>StockMovement</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>positions</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
@@ -10660,7 +10658,7 @@
       </c>
       <c r="E134" s="9" t="inlineStr">
         <is>
-          <t>A booking returns no identity: the v1 storage-item endpoints answer 201 with an empty body and — contrary to their own spec — send no Location header (verified on mvp 2026-07-31). Without an id a repeated booking cannot be recognised afterwards, which is why correction+setQuantityTo is the only retry-safe write. The ask: return the specced Location header, or the created movement.</t>
+          <t>Counting positions (expected/counted/difference with values) live in the counting-list reports — not composed into the API payload yet; needed for the GoBD difference review.</t>
         </is>
       </c>
       <c r="F134" s="9" t="inlineStr"/>
@@ -10668,17 +10666,17 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>StockMovement</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>unitCost</t>
+          <t>positions.counted</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
@@ -10688,7 +10686,7 @@
       </c>
       <c r="E135" s="9" t="inlineStr">
         <is>
-          <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
+          <t>Submitting counted quantities via API (mobile counting) — needed for headless inventory.</t>
         </is>
       </c>
       <c r="F135" s="9" t="inlineStr"/>
@@ -10701,12 +10699,12 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>documents.stockMovements</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
@@ -10716,7 +10714,7 @@
       </c>
       <c r="E136" s="9" t="inlineStr">
         <is>
-          <t>Starting a stock take via API (scope: warehouse/locations/products, key date) — the v1 inventory endpoints exist but the write orchestration is not built yet.</t>
+          <t>Posted correction movements per stock take need the stockMovements API (docs/05 #1) to be traceable.</t>
         </is>
       </c>
       <c r="F136" s="9" t="inlineStr"/>
@@ -10724,17 +10722,17 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>dates.keyDate</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
@@ -10744,7 +10742,7 @@
       </c>
       <c r="E137" s="9" t="inlineStr">
         <is>
-          <t>The inventory key date (Stichtag) is not exposed by v1 inventoryRuns.</t>
+          <t>Creating a picking run by criteria (wave: channel, shipping method, cutoff, maxOrders) has NO upstream endpoint — the main gap (docs/05 #3); execution (start/complete, totes) already exists.</t>
         </is>
       </c>
       <c r="F137" s="9" t="inlineStr"/>
@@ -10752,12 +10750,12 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>dates.posted</t>
+          <t>criteria</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
@@ -10772,7 +10770,7 @@
       </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>The posted timestamp is not exposed by v1 inventoryRuns.</t>
+          <t>Pick-run criteria (channel, shipping method) are not exposed by v1 pickLists.</t>
         </is>
       </c>
       <c r="F138" s="9" t="inlineStr"/>
@@ -10780,12 +10778,12 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>positions</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
@@ -10800,7 +10798,7 @@
       </c>
       <c r="E139" s="9" t="inlineStr">
         <is>
-          <t>Counting positions (expected/counted/difference with values) live in the counting-list reports — not composed into the API payload yet; needed for the GoBD difference review.</t>
+          <t>The picked sales orders are not exposed by v1 pickLists (only counts).</t>
         </is>
       </c>
       <c r="F139" s="9" t="inlineStr"/>
@@ -10808,17 +10806,17 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>positions.counted</t>
+          <t>containers</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
@@ -10828,7 +10826,7 @@
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>Submitting counted quantities via API (mobile counting) — needed for headless inventory.</t>
+          <t>Totes/containers are not exposed by v1 pickLists.</t>
         </is>
       </c>
       <c r="F140" s="9" t="inlineStr"/>
@@ -10836,17 +10834,17 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>documents.stockMovements</t>
+          <t>strategy</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
@@ -10856,7 +10854,7 @@
       </c>
       <c r="E141" s="9" t="inlineStr">
         <is>
-          <t>Posted correction movements per stock take need the stockMovements API (docs/05 #1) to be traceable.</t>
+          <t>Choosing the picking strategy (single/multiOrder/wave/zone) at creation — no create endpoint today.</t>
         </is>
       </c>
       <c r="F141" s="9" t="inlineStr"/>
@@ -10869,12 +10867,12 @@
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>tasks</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
@@ -10884,7 +10882,7 @@
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>Creating a picking run by criteria (wave: channel, shipping method, cutoff, maxOrders) has NO upstream endpoint — the main gap (docs/05 #3); execution (start/complete, totes) already exists.</t>
+          <t>Task-level detail (location, product, quantity, status per pick) is not exposed on the pickLists API — needed for progress boards and pick-path optimisation.</t>
         </is>
       </c>
       <c r="F142" s="9" t="inlineStr"/>
@@ -10897,12 +10895,12 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>criteria</t>
+          <t>tasks.status</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
@@ -10912,7 +10910,7 @@
       </c>
       <c r="E143" s="9" t="inlineStr">
         <is>
-          <t>Pick-run criteria (channel, shipping method) are not exposed by v1 pickLists.</t>
+          <t>Granular task-level pick confirmation with quantity + scans (docs/05 #3) — today only whole-list start/complete exists.</t>
         </is>
       </c>
       <c r="F143" s="9" t="inlineStr"/>
@@ -10920,17 +10918,17 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>list, read</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
@@ -10940,7 +10938,7 @@
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>The picked sales orders are not exposed by v1 pickLists (only counts).</t>
+          <t>Batches exist only as read-only v3 Product includes — no batch resource, no list, no detail (docs/05 #4). GET /v3/batches is the ask.</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr"/>
@@ -10948,17 +10946,17 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>containers</t>
+          <t>bestBefore</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
@@ -10968,7 +10966,7 @@
       </c>
       <c r="E145" s="9" t="inlineStr">
         <is>
-          <t>Totes/containers are not exposed by v1 pickLists.</t>
+          <t>Correcting a best-before date via API — internal web routes only today.</t>
         </is>
       </c>
       <c r="F145" s="9" t="inlineStr"/>
@@ -10976,17 +10974,17 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>strategy</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
@@ -10996,7 +10994,7 @@
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>Choosing the picking strategy (single/multiOrder/wave/zone) at creation — no create endpoint today.</t>
+          <t>Blocking/releasing a batch (quality hold) via API — maintenance happens only through internal web routes today.</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr"/>
@@ -11004,12 +11002,12 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>tasks</t>
+          <t>trace</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
@@ -11024,7 +11022,7 @@
       </c>
       <c r="E147" s="9" t="inlineStr">
         <is>
-          <t>Task-level detail (location, product, quantity, status per pick) is not exposed on the pickLists API — needed for progress boards and pick-path optimisation.</t>
+          <t>Batch trace (which goods receipts brought it in, which delivery notes shipped it — recall scenario) has no API at all (docs/05 #4).</t>
         </is>
       </c>
       <c r="F147" s="9" t="inlineStr"/>
@@ -11032,45 +11030,49 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>tasks.status</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D148" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D148" s="11" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E148" s="9" t="inlineStr">
         <is>
-          <t>Granular task-level pick confirmation with quantity + scans (docs/05 #3) — today only whole-list start/complete exists.</t>
-        </is>
-      </c>
-      <c r="F148" s="9" t="inlineStr"/>
+          <t>The platform kind (shopify/amazon/…) is not exposed — the BF salesChannel entity carries only a name (05 #17).</t>
+        </is>
+      </c>
+      <c r="F148" s="9" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>list, read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
@@ -11080,7 +11082,7 @@
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>Batches exist only as read-only v3 Product includes — no batch resource, no list, no detail (docs/05 #4). GET /v3/batches is the ask.</t>
+          <t>REVISED (docs/05 #17): BF salesChannel has CRUD — our facade write-mapping + live verification is pending.</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr"/>
@@ -11088,17 +11090,17 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
-          <t>bestBefore</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C150" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read, create, update</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
@@ -11108,7 +11110,7 @@
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>Correcting a best-before date via API — internal web routes only today.</t>
+          <t>The channel type (shop/marketplace/direct/pos) is not on the BF salesChannel record — needed for channel-specific routing.</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr"/>
@@ -11116,17 +11118,17 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>assignee</t>
         </is>
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
@@ -11136,7 +11138,7 @@
       </c>
       <c r="E151" s="9" t="inlineStr">
         <is>
-          <t>Blocking/releasing a batch (quality hold) via API — maintenance happens only through internal web routes today.</t>
+          <t>The one thing that would make a task a work item. `assignee` is readOnly upstream: a create or update carrying it answers 2xx and leaves the field null. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F151" s="9" t="inlineStr"/>
@@ -11144,17 +11146,17 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
         <is>
-          <t>trace</t>
+          <t>dates.completed</t>
         </is>
       </c>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
@@ -11164,7 +11166,7 @@
       </c>
       <c r="E152" s="9" t="inlineStr">
         <is>
-          <t>Batch trace (which goods receipts brought it in, which delivery notes shipped it — recall scenario) has no API at all (docs/05 #4).</t>
+          <t>Completing a task through the API does not stamp its completion date: `status: completed` persists, `completionDate` stays null.</t>
         </is>
       </c>
       <c r="F152" s="9" t="inlineStr"/>
@@ -11172,12 +11174,12 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>timeline</t>
         </is>
       </c>
       <c r="C153" s="7" t="inlineStr">
@@ -11185,164 +11187,20 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+      <c r="D153" s="13" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E153" s="9" t="inlineStr">
         <is>
-          <t>The platform kind (shopify/amazon/…) is not exposed — the BF salesChannel entity carries only a name (05 #17).</t>
-        </is>
-      </c>
-      <c r="F153" s="9" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="7" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B154" s="7" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C154" s="7" t="inlineStr">
-        <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D154" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E154" s="9" t="inlineStr">
-        <is>
-          <t>REVISED (docs/05 #17): BF salesChannel has CRUD — our facade write-mapping + live verification is pending.</t>
-        </is>
-      </c>
-      <c r="F154" s="9" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="7" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B155" s="7" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C155" s="7" t="inlineStr">
-        <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D155" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E155" s="9" t="inlineStr">
-        <is>
-          <t>The channel type (shop/marketplace/direct/pos) is not on the BF salesChannel record — needed for channel-specific routing.</t>
-        </is>
-      </c>
-      <c r="F155" s="9" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="7" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B156" s="7" t="inlineStr">
-        <is>
-          <t>assignee</t>
-        </is>
-      </c>
-      <c r="C156" s="7" t="inlineStr">
-        <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D156" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E156" s="9" t="inlineStr">
-        <is>
-          <t>The one thing that would make a task a work item. `assignee` is readOnly upstream: a create or update carrying it answers 2xx and leaves the field null. Measured on mvp 2026-08-02.</t>
-        </is>
-      </c>
-      <c r="F156" s="9" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="7" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B157" s="7" t="inlineStr">
-        <is>
-          <t>dates.completed</t>
-        </is>
-      </c>
-      <c r="C157" s="7" t="inlineStr">
-        <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D157" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E157" s="9" t="inlineStr">
-        <is>
-          <t>Completing a task through the API does not stamp its completion date: `status: completed` persists, `completionDate` stays null.</t>
-        </is>
-      </c>
-      <c r="F157" s="9" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="7" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B158" s="7" t="inlineStr">
-        <is>
-          <t>timeline</t>
-        </is>
-      </c>
-      <c r="C158" s="7" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D158" s="13" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
-        </is>
-      </c>
-      <c r="E158" s="9" t="inlineStr">
-        <is>
           <t>The task's comment thread. Declared `readWrite` with a full sub-node and returned by NO read — not the list, not the single read, and no include/expand parameter produces it. Not modelled until it reads back.</t>
         </is>
       </c>
-      <c r="F158" s="9" t="inlineStr"/>
+      <c r="F153" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F158"/>
+  <autoFilter ref="A1:F153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Übersicht'!$A$6:$H$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fähigkeiten'!$A$1:$F$181</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Felder'!$A$1:$F$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Felder'!$A$1:$F$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -651,10 +651,8 @@
       <c r="G9" t="n">
         <v>12</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+      <c r="H9" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="10">
@@ -679,12 +677,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="11">
@@ -739,12 +735,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>14</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="13">
@@ -799,12 +793,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>11</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="15">
@@ -829,12 +821,10 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="16">
@@ -889,10 +879,8 @@
       <c r="G17" t="n">
         <v>11</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+      <c r="H17" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="18">
@@ -6852,7 +6840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F153"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7787,29 +7775,25 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>The customer's PO number on the delivery note (B2B) — read-only upstream today; must be settable.</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>The picking/shipping warehouse — must be selectable per delivery note, not fixed to the default.</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -7819,12 +7803,12 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
@@ -7834,7 +7818,7 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Warehouse/support find a delivery note by the customer's PO number.</t>
+          <t>Adjust delivered positions/quantities after creation — the v3 update DTO carries no line-item write path.</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr"/>
@@ -7847,12 +7831,12 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>shipments</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -7862,7 +7846,7 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>The picking/shipping warehouse — must be selectable per delivery note, not fixed to the default.</t>
+          <t>Tracking numbers need a nachlade GET /v1/deliveryNotes/{id}/shipments — not yet composed into the read payload.</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr"/>
@@ -7875,12 +7859,12 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>customs.totalWeight</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
@@ -7890,7 +7874,7 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Adjust delivered positions/quantities after creation — the v3 update DTO carries no line-item write path.</t>
+          <t>Total shipment weight for the customs declaration / carrier — needs to be settable.</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr"/>
@@ -7903,12 +7887,12 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>shipments</t>
+          <t>customs.incoterm</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -7918,7 +7902,7 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Tracking numbers need a nachlade GET /v1/deliveryNotes/{id}/shipments — not yet composed into the read payload.</t>
+          <t>Incoterm for export shipments — a customs-declaration essential, not settable via API today.</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr"/>
@@ -7931,7 +7915,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>customs.totalWeight</t>
+          <t>customs.note</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -7946,7 +7930,7 @@
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Total shipment weight for the customs declaration / carrier — needs to be settable.</t>
+          <t>Customs note for export paperwork.</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr"/>
@@ -7959,7 +7943,7 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>customs.incoterm</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -7974,7 +7958,7 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Incoterm for export shipments — a customs-declaration essential, not settable via API today.</t>
+          <t>Custom field values on the delivery note — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr"/>
@@ -7982,17 +7966,17 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>DeliveryNote</t>
+          <t>Shipment</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>customs.note</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
@@ -8002,7 +7986,7 @@
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Customs note for export paperwork.</t>
+          <t>Creating a shipment + label via the facade (POST /v1/shipments + createLabel exists upstream) is not orchestrated here yet — needed for headless fulfilment.</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr"/>
@@ -8010,17 +7994,17 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>DeliveryNote</t>
+          <t>Shipment</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
@@ -8030,7 +8014,7 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>Custom field values on the delivery note — today only readable via include, not writable via API.</t>
+          <t>The shipment lifecycle status is not exposed by v1 shipments — only sentAt exists.</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr"/>
@@ -8043,12 +8027,12 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
@@ -8058,7 +8042,7 @@
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>Creating a shipment + label via the facade (POST /v1/shipments + createLabel exists upstream) is not orchestrated here yet — needed for headless fulfilment.</t>
+          <t>Package weight is not exposed by v1 shipments.</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr"/>
@@ -8071,7 +8055,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>events</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -8086,7 +8070,7 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>The shipment lifecycle status is not exposed by v1 shipments — only sentAt exists.</t>
+          <t>Carrier tracking events are not exposed — needs a carrier-events feed.</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr"/>
@@ -8099,12 +8083,12 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>tracking.number</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
@@ -8114,7 +8098,7 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>Package weight is not exposed by v1 shipments.</t>
+          <t>Support looks up a shipment by tracking number — needs a filterable/searchable upstream list parameter.</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr"/>
@@ -8122,17 +8106,17 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Shipment</t>
+          <t>SalesInvoice</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>events</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
@@ -8142,7 +8126,7 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Carrier tracking events are not exposed — needs a carrier-events feed.</t>
+          <t>Correcting a invoice number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr"/>
@@ -8150,17 +8134,17 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Shipment</t>
+          <t>SalesInvoice</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>tracking.number</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
@@ -8170,7 +8154,7 @@
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>Support looks up a shipment by tracking number — needs a filterable/searchable upstream list parameter.</t>
+          <t>Reassign the invoice's partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr"/>
@@ -8183,12 +8167,12 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>references.debtorAccountNumber</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -8198,7 +8182,7 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>Correcting a invoice number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
+          <t>Deviating debtor account for the FiBu/DATEV export — settable when it differs from the customer default.</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr"/>
@@ -8211,12 +8195,12 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
@@ -8226,7 +8210,7 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Reassign the invoice's partner after creation — v3 accepts it only on create.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr"/>
@@ -8239,12 +8223,12 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>totals.outstanding</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -8254,12 +8238,12 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>The customer's PO number on the invoice (B2B) — read-only upstream today; must be settable and correctable.</t>
+          <t>Exact open amount needs readable payment↔invoice allocations (docs/05 #2); today only derived from paymentStatus.</t>
         </is>
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>Schema deklariert: create</t>
+          <t>live bewiesen für: read</t>
         </is>
       </c>
     </row>
@@ -8271,12 +8255,12 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>payment.method</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
@@ -8286,7 +8270,7 @@
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Support and accounting find invoices by the customer's PO number.</t>
+          <t>Payment method on the invoice — central to order-to-cash; frequently overridden.</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr"/>
@@ -8299,7 +8283,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>references.debtorAccountNumber</t>
+          <t>payment.terms.dueDays</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -8314,7 +8298,7 @@
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Deviating debtor account for the FiBu/DATEV export — settable when it differs from the customer default.</t>
+          <t>Net payment term in days — drives the due date and dunning.</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr"/>
@@ -8327,7 +8311,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>payment.terms.discountPercent</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
@@ -8342,7 +8326,7 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Cash-discount percentage — standard DACH B2B.</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr"/>
@@ -8355,29 +8339,25 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>totals.outstanding</t>
+          <t>payment.terms.discountDays</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Exact open amount needs readable payment↔invoice allocations (docs/05 #2); today only derived from paymentStatus.</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>Cash-discount period in days — pairs with the discount.</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -8387,25 +8367,29 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>payment.method</t>
+          <t>eInvoice</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Payment method on the invoice — central to order-to-cash; frequently overridden.</t>
-        </is>
-      </c>
-      <c r="F54" s="9" t="inlineStr"/>
+          <t>The finished ZUGFeRD/XRechnung artefact + delivery status is a missing upstream API (docs/05 #7) — only XML raw data exists today.</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -8415,7 +8399,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>payment.terms.dueDays</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -8430,7 +8414,7 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Net payment term in days — drives the due date and dunning.</t>
+          <t>Custom field values on the invoice — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F55" s="9" t="inlineStr"/>
@@ -8443,22 +8427,22 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>payment.terms.discountPercent</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Cash-discount percentage — standard DACH B2B.</t>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr"/>
@@ -8466,17 +8450,17 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>payment.terms.discountDays</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
@@ -8486,7 +8470,7 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Cash-discount period in days — pairs with the discount.</t>
+          <t>No payment LIST/filter exists upstream — only GET /paymentTransactions/{id} (docs/05 #2). GET /v3/payments with filters is the ask.</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr"/>
@@ -8494,12 +8478,12 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>eInvoice</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -8507,36 +8491,32 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>The finished ZUGFeRD/XRechnung artefact + delivery status is a missing upstream API (docs/05 #7) — only XML raw data exists today.</t>
-        </is>
-      </c>
-      <c r="F58" s="9" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>Payout/settlement aggregation (fees, chargebacks) per provider needs docs/05 #8.</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>allocations</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, update</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
@@ -8546,7 +8526,7 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Custom field values on the invoice — today only readable via include, not writable via API.</t>
+          <t>Payment↔invoice allocations (n:m) are neither readable nor writable — without them exact outstanding amounts are impossible (docs/05 #2).</t>
         </is>
       </c>
       <c r="F59" s="9" t="inlineStr"/>
@@ -8554,27 +8534,27 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>SalesInvoice</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D60" s="13" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr"/>
@@ -8582,17 +8562,17 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>references.rmaNumber</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -8602,7 +8582,7 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>No payment LIST/filter exists upstream — only GET /paymentTransactions/{id} (docs/05 #2). GET /v3/payments with filters is the ask.</t>
+          <t>The RMA number the customer quotes — no upstream field today; core to returns handling.</t>
         </is>
       </c>
       <c r="F61" s="9" t="inlineStr"/>
@@ -8610,17 +8590,17 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>references.rmaNumber</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
@@ -8630,7 +8610,7 @@
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>Payout/settlement aggregation (fees, chargebacks) per provider needs docs/05 #8.</t>
+          <t>Support finds a return by the RMA number the customer has.</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr"/>
@@ -8638,17 +8618,17 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>allocations</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>read, update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
@@ -8658,7 +8638,7 @@
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Payment↔invoice allocations (n:m) are neither readable nor writable — without them exact outstanding amounts are impossible (docs/05 #2).</t>
+          <t>The returns warehouse must be selectable per return.</t>
         </is>
       </c>
       <c r="F63" s="9" t="inlineStr"/>
@@ -8671,7 +8651,7 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
@@ -8686,7 +8666,7 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
+          <t>Edit return positions after creation — the v3 update DTO carries no line-item write path.</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr"/>
@@ -8699,7 +8679,7 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>references.rmaNumber</t>
+          <t>items.reason</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
@@ -8707,17 +8687,21 @@
           <t>create, update</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>The RMA number the customer quotes — no upstream field today; core to returns handling.</t>
-        </is>
-      </c>
-      <c r="F65" s="9" t="inlineStr"/>
+          <t>The return reason per line — essential for returns analytics; not settable via API today.</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>Schema deklariert: create</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
@@ -8727,12 +8711,12 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>references.rmaNumber</t>
+          <t>items.condition</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
@@ -8742,7 +8726,7 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>Support finds a return by the RMA number the customer has.</t>
+          <t>Item condition (resellable/damaged/disposal) drives restocking — not in the v3 payload yet.</t>
         </is>
       </c>
       <c r="F66" s="9" t="inlineStr"/>
@@ -8755,12 +8739,12 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>items.condition</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -8770,7 +8754,7 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>The customer's PO number on the return — read-only upstream today.</t>
+          <t>Item condition is not surfaced by the v3 return payload yet (docs/05 #4 batch/trace family).</t>
         </is>
       </c>
       <c r="F67" s="9" t="inlineStr"/>
@@ -8783,7 +8767,7 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>items.action</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
@@ -8798,7 +8782,7 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>The returns warehouse must be selectable per return.</t>
+          <t>Resolution per line (credit/replace/repair) — not in the v3 payload yet.</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr"/>
@@ -8811,12 +8795,12 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
@@ -8826,7 +8810,7 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>Edit return positions after creation — the v3 update DTO carries no line-item write path.</t>
+          <t>Custom field values on the return — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr"/>
@@ -8834,49 +8818,45 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>items.reason</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>The return reason per line — essential for returns analytics; not settable via API today.</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Correcting a credit note number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>items.condition</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
@@ -8886,7 +8866,7 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Item condition (resellable/damaged/disposal) drives restocking — not in the v3 payload yet.</t>
+          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F71" s="9" t="inlineStr"/>
@@ -8894,17 +8874,17 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>items.condition</t>
+          <t>references.debtorAccountNumber</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
@@ -8914,7 +8894,7 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Item condition is not surfaced by the v3 return payload yet (docs/05 #4 batch/trace family).</t>
+          <t>Deviating debtor account for the FiBu/DATEV export of the credit note.</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr"/>
@@ -8922,12 +8902,12 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>items.action</t>
+          <t>dates.serviceDate</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -8942,7 +8922,7 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Resolution per line (credit/replace/repair) — not in the v3 payload yet.</t>
+          <t>Leistungsdatum — a §14 UStG mandatory field on the credit note; must be settable.</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr"/>
@@ -8950,12 +8930,12 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>CreditNote</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
@@ -8970,7 +8950,7 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>Custom field values on the return — today only readable via include, not writable via API.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr"/>
@@ -8983,25 +8963,29 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>totals.outstanding</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>Correcting a credit note number after the fact. The v3 create accepts one, but PATCH has no slot for it — a number carried over from another system must be right the first time.</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr"/>
+          <t>Exact open amount needs readable refund/offset allocations (docs/05 #2); today derived from paymentStatus only.</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
@@ -9011,12 +8995,12 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>settlement.mode</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
@@ -9026,7 +9010,7 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>Reassign the partner after creation — v3 accepts it only on create.</t>
+          <t>Refund vs offset-against-invoice is a per-credit-note decision — not settable upstream today.</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr"/>
@@ -9039,29 +9023,25 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>references.customerOrderNumber</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>The customer's PO number on the credit note (B2B) — read-only upstream today.</t>
-        </is>
-      </c>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>Schema deklariert: create</t>
-        </is>
-      </c>
+          <t>Custom field values on the credit note — today only readable via include, not writable via API.</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -9071,22 +9051,22 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>references.debtorAccountNumber</t>
+          <t>items.totals.tax</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>Deviating debtor account for the FiBu/DATEV export of the credit note.</t>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr"/>
@@ -9094,17 +9074,17 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>dates.serviceDate</t>
+          <t>defaults.shippingMethod</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
@@ -9114,7 +9094,7 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>Leistungsdatum — a §14 UStG mandatory field on the credit note; must be settable.</t>
+          <t>The default shipping method is not surfaced by the v3 partner read.</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr"/>
@@ -9122,12 +9102,12 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>defaults.paymentTerms.dueDays</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
@@ -9142,7 +9122,7 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Default supplier payment term — drives liability due dates.</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr"/>
@@ -9150,44 +9130,40 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>totals.outstanding</t>
+          <t>finance.creditorAccountNumber</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>Exact open amount needs readable refund/offset allocations (docs/05 #2); today derived from paymentStatus only.</t>
-        </is>
-      </c>
-      <c r="F81" s="9" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>The creditor account for the FiBu/DATEV export — settable per supplier.</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>settlement.mode</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
@@ -9202,7 +9178,7 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>Refund vs offset-against-invoice is a per-credit-note decision — not settable upstream today.</t>
+          <t>Custom field values on the supplier — today only readable, not writable via API.</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr"/>
@@ -9210,17 +9186,17 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>supplier</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
@@ -9230,7 +9206,7 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>Custom field values on the credit note — today only readable via include, not writable via API.</t>
+          <t>Reassign the PO's supplier after creation — v3 accepts it only on create.</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr"/>
@@ -9238,27 +9214,27 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>CreditNote</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>items.totals.tax</t>
+          <t>references.ourCustomerNumber</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D84" s="13" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create, update</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+          <t>Our customer number at the supplier — belongs on the PO, not settable via API today.</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr"/>
@@ -9266,17 +9242,17 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>defaults.shippingMethod</t>
+          <t>references.supplierOfferNumber</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
@@ -9286,7 +9262,7 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>The default shipping method is not surfaced by the v3 partner read.</t>
+          <t>The supplier's quote number we ordered against — read-only upstream today.</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr"/>
@@ -9294,17 +9270,17 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>defaults.paymentTerms.dueDays</t>
+          <t>confirmation.status</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
@@ -9314,7 +9290,7 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Default supplier payment term — drives liability due dates.</t>
+          <t>Recording the confirmation status (pending/confirmed/deviating) is core purchasing — not writable via API today.</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr"/>
@@ -9322,12 +9298,12 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>finance.creditorAccountNumber</t>
+          <t>confirmation.supplierOrderNumber</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
@@ -9342,7 +9318,7 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>The creditor account for the FiBu/DATEV export — settable per supplier.</t>
+          <t>The AB (order-confirmation) number from the supplier — the whole confirmation block is read-only upstream (docs/05: AB handling).</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr"/>
@@ -9350,12 +9326,12 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>PurchaseOrder</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>dates.requestedDelivery</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
@@ -9370,7 +9346,7 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>Custom field values on the supplier — today only readable, not writable via API.</t>
+          <t>Requested delivery date at the supplier — not writable upstream today.</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr"/>
@@ -9383,12 +9359,12 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>supplier</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
@@ -9398,7 +9374,7 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>Reassign the PO's supplier after creation — v3 accepts it only on create.</t>
+          <t>The receiving warehouse for the PO must be selectable.</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr"/>
@@ -9411,12 +9387,12 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>references.ourCustomerNumber</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
@@ -9426,7 +9402,7 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Our customer number at the supplier — belongs on the PO, not settable via API today.</t>
+          <t>Edit PO positions after creation — the v3 update DTO carries no line-item write path.</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr"/>
@@ -9439,7 +9415,7 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>references.supplierOfferNumber</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
@@ -9454,7 +9430,7 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>The supplier's quote number we ordered against — read-only upstream today.</t>
+          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr"/>
@@ -9467,12 +9443,12 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>confirmation.status</t>
+          <t>dropship</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read, create</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
@@ -9482,7 +9458,7 @@
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>Recording the confirmation status (pending/confirmed/deviating) is core purchasing — not writable via API today.</t>
+          <t>Dropshipping (Strecke: salesOrder link + customer delivery address) is not exposed via v3 purchaseOrders.</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr"/>
@@ -9495,12 +9471,12 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>confirmation.supplierOrderNumber</t>
+          <t>customFields</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
@@ -9510,7 +9486,7 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>The AB (order-confirmation) number from the supplier — the whole confirmation block is read-only upstream (docs/05: AB handling).</t>
+          <t>Custom field values on the PO — today only readable via include, not writable via API.</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr"/>
@@ -9518,17 +9494,17 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>dates.requestedDelivery</t>
+          <t>references.supplierDeliveryNoteNumber</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>create, update, read</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
@@ -9538,7 +9514,7 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Requested delivery date at the supplier — not writable upstream today.</t>
+          <t>The supplier's delivery-note number on the goods receipt — needed for the three-way match; not in the BF record yet.</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr"/>
@@ -9546,17 +9522,17 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>dates.received</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
@@ -9566,7 +9542,7 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>The receiving warehouse for the PO must be selectable.</t>
+          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr"/>
@@ -9574,17 +9550,17 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>dates.posted</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
@@ -9594,7 +9570,7 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>Edit PO positions after creation — the v3 update DTO carries no line-item write path.</t>
+          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr"/>
@@ -9602,17 +9578,17 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>items.taxRate</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
@@ -9622,7 +9598,7 @@
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+          <t>Cancel/storno of a posted goods receipt — the remaining upstream gap after the BF entity list covered browsing (docs/05 #9 revised).</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr"/>
@@ -9630,17 +9606,17 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>dropship</t>
+          <t>items</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>read, create</t>
+          <t>read, create, update</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
@@ -9650,7 +9626,7 @@
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>Dropshipping (Strecke: salesOrder link + customer delivery address) is not exposed via v3 purchaseOrders.</t>
+          <t>Line items (product × quantity × storage location, quality check per line) are not exposed on the BF goodsReceipt record — creation still goes through the PO action only.</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr"/>
@@ -9658,17 +9634,17 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>customFields</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
@@ -9678,7 +9654,7 @@
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>Custom field values on the PO — today only readable via include, not writable via API.</t>
+          <t>The document number is system-assigned: sending `documentNumber` on create answers 201 and the record comes back with an empty number (measured on mvp 2026-08-02). Same behaviour as the other documents.</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr"/>
@@ -9686,17 +9662,17 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>references.supplierDeliveryNoteNumber</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>create, update, read</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -9706,7 +9682,7 @@
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>The supplier's delivery-note number on the goods receipt — needed for the three-way match; not in the BF record yet.</t>
+          <t>Filtering incoming invoices by workflow status is the AP daily view — the BF supplierInvoice API does not allow filtering documentStatus today.</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr"/>
@@ -9714,17 +9690,17 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>dates.received</t>
+          <t>dates.invoiceDate</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>sort</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
@@ -9734,7 +9710,7 @@
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
+          <t>Sorting incoming invoices by invoice date — dateOfSupplierInvoice is not sortable on the BF API today.</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr"/>
@@ -9742,17 +9718,17 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>dates.posted</t>
+          <t>match.status</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
@@ -9762,7 +9738,7 @@
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>Received/posted dates are not exposed — only createdAt/updatedAt exist on the BF entity.</t>
+          <t>Re-running/overriding the match verdict via API (rematch) — the check statuses are readable now; a command to re-evaluate is still missing upstream.</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr"/>
@@ -9770,17 +9746,17 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>payment.status</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
@@ -9790,7 +9766,7 @@
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>Cancel/storno of a posted goods receipt — the remaining upstream gap after the BF entity list covered browsing (docs/05 #9 revised).</t>
+          <t>Open-liabilities view needs filtering by payment status — not allowed on the BF supplierInvoice API today.</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr"/>
@@ -9798,17 +9774,17 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>PurchaseInvoice</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>approval.status</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>read, create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -9818,7 +9794,7 @@
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>Line items (product × quantity × storage location, quality check per line) are not exposed on the BF goodsReceipt record — creation still goes through the PO action only.</t>
+          <t>Approve/reject via API: BF process steps (GoodsCheck/InvoiceCheck/Payment) are reported to exist — wiring + live verification of those steps is pending (steps were empty on the test instance's metadata).</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr"/>
@@ -9831,12 +9807,12 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>approval.by</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
@@ -9846,7 +9822,7 @@
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>The document number is system-assigned: sending `documentNumber` on create answers 201 and the record comes back with an empty number (measured on mvp 2026-08-02). Same behaviour as the other documents.</t>
+          <t>The approver is not exposed — BF supplierInvoice carries only the check statuses.</t>
         </is>
       </c>
       <c r="F105" s="9" t="inlineStr"/>
@@ -9859,12 +9835,12 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>approval.at</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
@@ -9874,7 +9850,7 @@
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>Filtering incoming invoices by workflow status is the AP daily view — the BF supplierInvoice API does not allow filtering documentStatus today.</t>
+          <t>The approval timestamp is not exposed by the BF supplierInvoice entity.</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr"/>
@@ -9882,17 +9858,17 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>dates.invoiceDate</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>sort</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
@@ -9902,7 +9878,7 @@
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>Sorting incoming invoices by invoice date — dateOfSupplierInvoice is not sortable on the BF API today.</t>
+          <t>The consolidated product kind (ADR-011) should be settable directly instead of juggling isServiceProduct/isFee/isShippingCostsProduct booleans — the v2 create body only exposes isShippingCostsProduct, so service/digital cannot be expressed.</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr"/>
@@ -9910,17 +9886,17 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>match.status</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
@@ -9930,7 +9906,7 @@
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>Re-running/overriding the match verdict via API (rematch) — the check statuses are readable now; a command to re-evaluate is still missing upstream.</t>
+          <t>Tagging products (assortment curation, campaigns) — product writes now go through v2, but the v2 tags shape ({id,key,name,color}) is not yet mapped/verified, so tag writes stay blue.</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr"/>
@@ -9938,17 +9914,17 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>payment.status</t>
+          <t>prices.sale</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
@@ -9958,7 +9934,7 @@
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>Open-liabilities view needs filtering by payment status — not allowed on the BF supplierInvoice API today.</t>
+          <t>WRITE works — the sale price is composed as a separate salesPrices write on create/update. READ is still blue: the v3 read model does not carry the sale price (needs the salesPrices include parsed), so a written price is not read back.</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr"/>
@@ -9966,17 +9942,17 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>approval.status</t>
+          <t>tax.profile</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
@@ -9986,7 +9962,7 @@
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>Approve/reject via API: BF process steps (GoodsCheck/InvoiceCheck/Payment) are reported to exist — wiring + live verification of those steps is pending (steps were empty on the test instance's metadata).</t>
+          <t>The 16-account tax matrix consolidated into a referenceable taxProfile (ADR-011) — today only the raw taxAccounts embed exists, not a clean reference.</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr"/>
@@ -9994,17 +9970,17 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>approval.by</t>
+          <t>logistics.packagingUnits</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, read, update</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
@@ -10014,7 +9990,7 @@
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>The approver is not exposed — BF supplierInvoice carries only the check statuses.</t>
+          <t>Packaging units (VPE) need the packagingUnits include parsed — not yet mapped.</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr"/>
@@ -10022,12 +9998,12 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>approval.at</t>
+          <t>stock.incoming</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
@@ -10042,7 +10018,7 @@
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>The approval timestamp is not exposed by the BF supplierInvoice entity.</t>
+          <t>Inbound quantity (ordered but not yet received) is the one stock figure Xentral does not compute: /products/{id}/stocks returns physical, sellable, reserved, correction, pseudo, openSalesOrders, calculated and producible — all mapped — but nothing inbound. The per-warehouse split the same call carries is answered by StockLevel (filter[product], narrowed by warehouse), so it is not duplicated onto the product.</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr"/>
@@ -10055,7 +10031,7 @@
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>suppliers</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
@@ -10070,7 +10046,7 @@
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>The consolidated product kind (ADR-011) should be settable directly instead of juggling isServiceProduct/isFee/isShippingCostsProduct booleans — the v2 create body only exposes isShippingCostsProduct, so service/digital cannot be expressed.</t>
+          <t>The default supplier IS writable (mapped to v2 standardSupplier); multi-supplier sourcing (several suppliers with per-supplier price/number) needs a suppliers include/relation not yet mapped, plus a write path.</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr"/>
@@ -10078,17 +10054,17 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>PriceList</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>entries</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
@@ -10098,7 +10074,7 @@
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>Tagging products (assortment curation, campaigns) — product writes now go through v2, but the v2 tags shape ({id,key,name,color}) is not yet mapped/verified, so tag writes stay blue.</t>
+          <t>v1 salesPrices exposes flat price rows (this entity is one row); the grouped priceList with a tier array needs a composer (ADR-012). Write each tier as its own entry (create/update/delete are live via v3/v1 salesPrices).</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr"/>
@@ -10106,17 +10082,17 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StorageLocation</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>prices.sale</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
@@ -10126,7 +10102,7 @@
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>WRITE works — the sale price is composed as a separate salesPrices write on create/update. READ is still blue: the v3 read model does not carry the sale price (needs the salesPrices include parsed), so a written price is not read back.</t>
+          <t>Upstream returns the bin description but rejects it on create and update ("The attribute description is not allowed.") — the field is read-only for every API generation we have. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr"/>
@@ -10134,17 +10110,17 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StorageLocation</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>tax.profile</t>
+          <t>contents.reserved</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
@@ -10154,7 +10130,7 @@
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>The 16-account tax matrix consolidated into a referenceable taxProfile (ADR-011) — today only the raw taxAccounts embed exists, not a clean reference.</t>
+          <t>Location contents are composed from the StockLevel projection now; the reserved portion per location stays unavailable — upstream reports reservations only as a product total.</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr"/>
@@ -10162,27 +10138,27 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StorageLocation</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>logistics.packagingUnits</t>
+          <t>locationType</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>create, read, update</t>
-        </is>
-      </c>
-      <c r="D117" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D117" s="13" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E117" s="9" t="inlineStr">
         <is>
-          <t>Packaging units (VPE) need the packagingUnits include parsed — not yet mapped.</t>
+          <t>v1 accepts a `locationType` on write with 204 but never returns it on any read, so a value written there cannot be verified or shown. Not modelled until upstream reads it back. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr"/>
@@ -10190,17 +10166,17 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>stock.incoming</t>
+          <t>batch</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>read, list</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
@@ -10210,7 +10186,7 @@
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>Inbound quantity (ordered but not yet received) is the one stock figure Xentral does not compute: /products/{id}/stocks returns physical, sellable, reserved, correction, pseudo, openSalesOrders, calculated and producible — all mapped — but nothing inbound. The per-warehouse split the same call carries is answered by StockLevel (filter[product], narrowed by warehouse), so it is not duplicated onto the product.</t>
+          <t>The batch split exists on the v2 items path (qualityControlAttributes) but not on /v1/products/{id}/storageLocations. Emitting batch rows on one anchor only would make the grain depend on the filter, so the projection stays product × storage location. A unified GET /v3/stockLevels is the clean ask (docs/05 #18).</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr"/>
@@ -10218,17 +10194,17 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>suppliers</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -10238,7 +10214,7 @@
       </c>
       <c r="E119" s="9" t="inlineStr">
         <is>
-          <t>The default supplier IS writable (mapped to v2 standardSupplier); multi-supplier sourcing (several suppliers with per-supplier price/number) needs a suppliers include/relation not yet mapped, plus a write path.</t>
+          <t>The list needs an anchor filter (product or storageLocation): upstream has no global stock collection, so an unanchored query would mean fanning out over every product of the tenant.</t>
         </is>
       </c>
       <c r="F119" s="9" t="inlineStr"/>
@@ -10246,12 +10222,12 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>PriceList</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>entries</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
@@ -10266,7 +10242,7 @@
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>v1 salesPrices exposes flat price rows (this entity is one row); the grouped priceList with a tier array needs a composer (ADR-012). Write each tier as its own entry (create/update/delete are live via v3/v1 salesPrices).</t>
+          <t>No per-location reservation is exposed upstream; /v1/products/{id}/stocks reports reserved only as a product TOTAL. The projection reports quantity and leaves reserved/available blank rather than spreading a total over locations.</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr"/>
@@ -10274,17 +10250,17 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>StorageLocation</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
@@ -10294,7 +10270,7 @@
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>Upstream returns the bin description but rejects it on create and update ("The attribute description is not allowed.") — the field is read-only for every API generation we have. Measured on mvp 2026-08-02.</t>
+          <t>Same gap as reserved: available = quantity - reserved is only derivable per product, not per storage location.</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr"/>
@@ -10302,17 +10278,17 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>StorageLocation</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>contents.reserved</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>list, read</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
@@ -10322,7 +10298,7 @@
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>Location contents are composed from the StockLevel projection now; the reserved portion per location stays unavailable — upstream reports reservations only as a product total.</t>
+          <t>The stock ledger (Lagerprotokoll) has NO read API at all — the single biggest gap (docs/05 #1). GET /v3/stockMovements is the ask. Until it ships the entity does not declare list/read at all, so a caller learns this from the contract instead of a 404.</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr"/>
@@ -10330,27 +10306,27 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>StorageLocation</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>locationType</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D123" s="13" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>v1 accepts a `locationType` on write with 204 but never returns it on any read, so a value written there cannot be verified or shown. Not modelled until upstream reads it back. Measured on mvp 2026-08-02.</t>
+          <t>A booking returns no identity: the v1 storage-item endpoints answer 201 with an empty body and — contrary to their own spec — send no Location header (verified on mvp 2026-07-31). Without an id a repeated booking cannot be recognised afterwards, which is why correction+setQuantityTo is the only retry-safe write. The ask: return the specced Location header, or the created movement.</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr"/>
@@ -10358,17 +10334,17 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>batch</t>
+          <t>unitCost</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>read, list</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -10378,7 +10354,7 @@
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>The batch split exists on the v2 items path (qualityControlAttributes) but not on /v1/products/{id}/storageLocations. Emitting batch rows on one anchor only would make the grain depend on the filter, so the projection stays product × storage location. A unified GET /v3/stockLevels is the clean ask (docs/05 #18).</t>
+          <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr"/>
@@ -10386,17 +10362,17 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -10406,7 +10382,7 @@
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>The list needs an anchor filter (product or storageLocation): upstream has no global stock collection, so an unanchored query would mean fanning out over every product of the tenant.</t>
+          <t>Starting a stock take via API (scope: warehouse/locations/products, key date) — the v1 inventory endpoints exist but the write orchestration is not built yet.</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr"/>
@@ -10414,12 +10390,12 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>dates.keyDate</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
@@ -10434,7 +10410,7 @@
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>No per-location reservation is exposed upstream; /v1/products/{id}/stocks reports reserved only as a product TOTAL. The projection reports quantity and leaves reserved/available blank rather than spreading a total over locations.</t>
+          <t>The inventory key date (Stichtag) is not exposed by v1 inventoryRuns.</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr"/>
@@ -10442,12 +10418,12 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>dates.posted</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
@@ -10462,7 +10438,7 @@
       </c>
       <c r="E127" s="9" t="inlineStr">
         <is>
-          <t>Same gap as reserved: available = quantity - reserved is only derivable per product, not per storage location.</t>
+          <t>The posted timestamp is not exposed by v1 inventoryRuns.</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr"/>
@@ -10470,17 +10446,17 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>StockMovement</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>positions</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>list, read</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
@@ -10490,7 +10466,7 @@
       </c>
       <c r="E128" s="9" t="inlineStr">
         <is>
-          <t>The stock ledger (Lagerprotokoll) has NO read API at all — the single biggest gap (docs/05 #1). GET /v3/stockMovements is the ask. Until it ships the entity does not declare list/read at all, so a caller learns this from the contract instead of a 404.</t>
+          <t>Counting positions (expected/counted/difference with values) live in the counting-list reports — not composed into the API payload yet; needed for the GoBD difference review.</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr"/>
@@ -10498,17 +10474,17 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>StockMovement</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>positions.counted</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
@@ -10518,7 +10494,7 @@
       </c>
       <c r="E129" s="9" t="inlineStr">
         <is>
-          <t>A booking returns no identity: the v1 storage-item endpoints answer 201 with an empty body and — contrary to their own spec — send no Location header (verified on mvp 2026-07-31). Without an id a repeated booking cannot be recognised afterwards, which is why correction+setQuantityTo is the only retry-safe write. The ask: return the specced Location header, or the created movement.</t>
+          <t>Submitting counted quantities via API (mobile counting) — needed for headless inventory.</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr"/>
@@ -10526,12 +10502,12 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>StockMovement</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>unitCost</t>
+          <t>documents.stockMovements</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
@@ -10546,7 +10522,7 @@
       </c>
       <c r="E130" s="9" t="inlineStr">
         <is>
-          <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
+          <t>Posted correction movements per stock take need the stockMovements API (docs/05 #1) to be traceable.</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr"/>
@@ -10554,7 +10530,7 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -10574,7 +10550,7 @@
       </c>
       <c r="E131" s="9" t="inlineStr">
         <is>
-          <t>Starting a stock take via API (scope: warehouse/locations/products, key date) — the v1 inventory endpoints exist but the write orchestration is not built yet.</t>
+          <t>Creating a picking run by criteria (wave: channel, shipping method, cutoff, maxOrders) has NO upstream endpoint — the main gap (docs/05 #3); execution (start/complete, totes) already exists.</t>
         </is>
       </c>
       <c r="F131" s="9" t="inlineStr"/>
@@ -10582,12 +10558,12 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>dates.keyDate</t>
+          <t>criteria</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
@@ -10602,7 +10578,7 @@
       </c>
       <c r="E132" s="9" t="inlineStr">
         <is>
-          <t>The inventory key date (Stichtag) is not exposed by v1 inventoryRuns.</t>
+          <t>Pick-run criteria (channel, shipping method) are not exposed by v1 pickLists.</t>
         </is>
       </c>
       <c r="F132" s="9" t="inlineStr"/>
@@ -10610,12 +10586,12 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>dates.posted</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
@@ -10630,7 +10606,7 @@
       </c>
       <c r="E133" s="9" t="inlineStr">
         <is>
-          <t>The posted timestamp is not exposed by v1 inventoryRuns.</t>
+          <t>The picked sales orders are not exposed by v1 pickLists (only counts).</t>
         </is>
       </c>
       <c r="F133" s="9" t="inlineStr"/>
@@ -10638,12 +10614,12 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>positions</t>
+          <t>containers</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
@@ -10658,7 +10634,7 @@
       </c>
       <c r="E134" s="9" t="inlineStr">
         <is>
-          <t>Counting positions (expected/counted/difference with values) live in the counting-list reports — not composed into the API payload yet; needed for the GoBD difference review.</t>
+          <t>Totes/containers are not exposed by v1 pickLists.</t>
         </is>
       </c>
       <c r="F134" s="9" t="inlineStr"/>
@@ -10666,17 +10642,17 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>positions.counted</t>
+          <t>strategy</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
@@ -10686,7 +10662,7 @@
       </c>
       <c r="E135" s="9" t="inlineStr">
         <is>
-          <t>Submitting counted quantities via API (mobile counting) — needed for headless inventory.</t>
+          <t>Choosing the picking strategy (single/multiOrder/wave/zone) at creation — no create endpoint today.</t>
         </is>
       </c>
       <c r="F135" s="9" t="inlineStr"/>
@@ -10694,12 +10670,12 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>documents.stockMovements</t>
+          <t>tasks</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
@@ -10714,7 +10690,7 @@
       </c>
       <c r="E136" s="9" t="inlineStr">
         <is>
-          <t>Posted correction movements per stock take need the stockMovements API (docs/05 #1) to be traceable.</t>
+          <t>Task-level detail (location, product, quantity, status per pick) is not exposed on the pickLists API — needed for progress boards and pick-path optimisation.</t>
         </is>
       </c>
       <c r="F136" s="9" t="inlineStr"/>
@@ -10727,12 +10703,12 @@
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>tasks.status</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
@@ -10742,7 +10718,7 @@
       </c>
       <c r="E137" s="9" t="inlineStr">
         <is>
-          <t>Creating a picking run by criteria (wave: channel, shipping method, cutoff, maxOrders) has NO upstream endpoint — the main gap (docs/05 #3); execution (start/complete, totes) already exists.</t>
+          <t>Granular task-level pick confirmation with quantity + scans (docs/05 #3) — today only whole-list start/complete exists.</t>
         </is>
       </c>
       <c r="F137" s="9" t="inlineStr"/>
@@ -10750,17 +10726,17 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>criteria</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>list, read</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
@@ -10770,7 +10746,7 @@
       </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>Pick-run criteria (channel, shipping method) are not exposed by v1 pickLists.</t>
+          <t>Batches exist only as read-only v3 Product includes — no batch resource, no list, no detail (docs/05 #4). GET /v3/batches is the ask.</t>
         </is>
       </c>
       <c r="F138" s="9" t="inlineStr"/>
@@ -10778,17 +10754,17 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>bestBefore</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
@@ -10798,7 +10774,7 @@
       </c>
       <c r="E139" s="9" t="inlineStr">
         <is>
-          <t>The picked sales orders are not exposed by v1 pickLists (only counts).</t>
+          <t>Correcting a best-before date via API — internal web routes only today.</t>
         </is>
       </c>
       <c r="F139" s="9" t="inlineStr"/>
@@ -10806,17 +10782,17 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>containers</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
@@ -10826,7 +10802,7 @@
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>Totes/containers are not exposed by v1 pickLists.</t>
+          <t>Blocking/releasing a batch (quality hold) via API — maintenance happens only through internal web routes today.</t>
         </is>
       </c>
       <c r="F140" s="9" t="inlineStr"/>
@@ -10834,17 +10810,17 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>strategy</t>
+          <t>trace</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
@@ -10854,7 +10830,7 @@
       </c>
       <c r="E141" s="9" t="inlineStr">
         <is>
-          <t>Choosing the picking strategy (single/multiOrder/wave/zone) at creation — no create endpoint today.</t>
+          <t>Batch trace (which goods receipts brought it in, which delivery notes shipped it — recall scenario) has no API at all (docs/05 #4).</t>
         </is>
       </c>
       <c r="F141" s="9" t="inlineStr"/>
@@ -10862,12 +10838,12 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>tasks</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
@@ -10875,32 +10851,36 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D142" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D142" s="11" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>Task-level detail (location, product, quantity, status per pick) is not exposed on the pickLists API — needed for progress boards and pick-path optimisation.</t>
-        </is>
-      </c>
-      <c r="F142" s="9" t="inlineStr"/>
+          <t>The platform kind (shopify/amazon/…) is not exposed — the BF salesChannel entity carries only a name (05 #17).</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>tasks.status</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
@@ -10910,7 +10890,7 @@
       </c>
       <c r="E143" s="9" t="inlineStr">
         <is>
-          <t>Granular task-level pick confirmation with quantity + scans (docs/05 #3) — today only whole-list start/complete exists.</t>
+          <t>REVISED (docs/05 #17): BF salesChannel has CRUD — our facade write-mapping + live verification is pending.</t>
         </is>
       </c>
       <c r="F143" s="9" t="inlineStr"/>
@@ -10918,17 +10898,17 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>list, read</t>
+          <t>read, create, update</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
@@ -10938,7 +10918,7 @@
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>Batches exist only as read-only v3 Product includes — no batch resource, no list, no detail (docs/05 #4). GET /v3/batches is the ask.</t>
+          <t>The channel type (shop/marketplace/direct/pos) is not on the BF salesChannel record — needed for channel-specific routing.</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr"/>
@@ -10946,17 +10926,17 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>bestBefore</t>
+          <t>assignee</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
@@ -10966,7 +10946,7 @@
       </c>
       <c r="E145" s="9" t="inlineStr">
         <is>
-          <t>Correcting a best-before date via API — internal web routes only today.</t>
+          <t>The one thing that would make a task a work item. `assignee` is readOnly upstream: a create or update carrying it answers 2xx and leaves the field null. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F145" s="9" t="inlineStr"/>
@@ -10974,12 +10954,12 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>dates.completed</t>
         </is>
       </c>
       <c r="C146" s="7" t="inlineStr">
@@ -10994,7 +10974,7 @@
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>Blocking/releasing a batch (quality hold) via API — maintenance happens only through internal web routes today.</t>
+          <t>Completing a task through the API does not stamp its completion date: `status: completed` persists, `completionDate` stays null.</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr"/>
@@ -11002,12 +10982,12 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>trace</t>
+          <t>timeline</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
@@ -11015,192 +10995,20 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D147" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D147" s="13" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
         <is>
-          <t>Batch trace (which goods receipts brought it in, which delivery notes shipped it — recall scenario) has no API at all (docs/05 #4).</t>
+          <t>The task's comment thread. Declared `readWrite` with a full sub-node and returned by NO read — not the list, not the single read, and no include/expand parameter produces it. Not modelled until it reads back.</t>
         </is>
       </c>
       <c r="F147" s="9" t="inlineStr"/>
     </row>
-    <row r="148">
-      <c r="A148" s="7" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B148" s="7" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C148" s="7" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D148" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
-        </is>
-      </c>
-      <c r="E148" s="9" t="inlineStr">
-        <is>
-          <t>The platform kind (shopify/amazon/…) is not exposed — the BF salesChannel entity carries only a name (05 #17).</t>
-        </is>
-      </c>
-      <c r="F148" s="9" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="7" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B149" s="7" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C149" s="7" t="inlineStr">
-        <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D149" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E149" s="9" t="inlineStr">
-        <is>
-          <t>REVISED (docs/05 #17): BF salesChannel has CRUD — our facade write-mapping + live verification is pending.</t>
-        </is>
-      </c>
-      <c r="F149" s="9" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="7" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B150" s="7" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C150" s="7" t="inlineStr">
-        <is>
-          <t>read, create, update</t>
-        </is>
-      </c>
-      <c r="D150" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E150" s="9" t="inlineStr">
-        <is>
-          <t>The channel type (shop/marketplace/direct/pos) is not on the BF salesChannel record — needed for channel-specific routing.</t>
-        </is>
-      </c>
-      <c r="F150" s="9" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="7" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B151" s="7" t="inlineStr">
-        <is>
-          <t>assignee</t>
-        </is>
-      </c>
-      <c r="C151" s="7" t="inlineStr">
-        <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D151" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E151" s="9" t="inlineStr">
-        <is>
-          <t>The one thing that would make a task a work item. `assignee` is readOnly upstream: a create or update carrying it answers 2xx and leaves the field null. Measured on mvp 2026-08-02.</t>
-        </is>
-      </c>
-      <c r="F151" s="9" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="7" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B152" s="7" t="inlineStr">
-        <is>
-          <t>dates.completed</t>
-        </is>
-      </c>
-      <c r="C152" s="7" t="inlineStr">
-        <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D152" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E152" s="9" t="inlineStr">
-        <is>
-          <t>Completing a task through the API does not stamp its completion date: `status: completed` persists, `completionDate` stays null.</t>
-        </is>
-      </c>
-      <c r="F152" s="9" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="7" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B153" s="7" t="inlineStr">
-        <is>
-          <t>timeline</t>
-        </is>
-      </c>
-      <c r="C153" s="7" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D153" s="13" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
-        </is>
-      </c>
-      <c r="E153" s="9" t="inlineStr">
-        <is>
-          <t>The task's comment thread. Declared `readWrite` with a full sub-node and returned by NO read — not the list, not the single read, and no include/expand parameter produces it. Not modelled until it reads back.</t>
-        </is>
-      </c>
-      <c r="F153" s="9" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F153"/>
+  <autoFilter ref="A1:F147"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -707,10 +707,8 @@
       <c r="G11" t="n">
         <v>5</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+      <c r="H11" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="12">
@@ -907,10 +905,8 @@
       <c r="G18" t="n">
         <v>5</v>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+      <c r="H18" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="19">
@@ -1027,10 +1023,8 @@
       <c r="G22" t="n">
         <v>3</v>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+      <c r="H22" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="23">
@@ -1057,10 +1051,8 @@
       <c r="G23" t="n">
         <v>4</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+      <c r="H23" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="24">
@@ -1087,10 +1079,8 @@
       <c r="G24" t="n">
         <v>3</v>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+      <c r="H24" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="25">
@@ -1117,10 +1107,8 @@
       <c r="G25" t="n">
         <v>6</v>
       </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+      <c r="H25" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="26">
@@ -1147,10 +1135,8 @@
       <c r="G26" t="n">
         <v>7</v>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+      <c r="H26" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="27">
@@ -1177,10 +1163,8 @@
       <c r="G27" t="n">
         <v>4</v>
       </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+      <c r="H27" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="28">

--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Übersicht'!$A$6:$H$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fähigkeiten'!$A$1:$F$181</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Felder'!$A$1:$F$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Felder'!$A$1:$F$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -763,10 +763,8 @@
       <c r="G13" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+      <c r="H13" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="14">
@@ -931,12 +929,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="20">
@@ -963,10 +959,8 @@
       <c r="G20" t="n">
         <v>7</v>
       </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+      <c r="H20" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="21">
@@ -993,10 +987,8 @@
       <c r="G21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+      <c r="H21" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="22">
@@ -1189,12 +1181,10 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
     <row r="29">
@@ -1311,10 +1301,8 @@
       <c r="G32" t="n">
         <v>3</v>
       </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
+      <c r="H32" s="4" t="n">
+        <v>46243</v>
       </c>
     </row>
   </sheetData>
@@ -6824,7 +6812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9623,12 +9611,12 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
@@ -9638,7 +9626,7 @@
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>The document number is system-assigned: sending `documentNumber` on create answers 201 and the record comes back with an empty number (measured on mvp 2026-08-02). Same behaviour as the other documents.</t>
+          <t>Filtering incoming invoices by workflow status is the AP daily view — the BF supplierInvoice API does not allow filtering documentStatus today.</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr"/>
@@ -9651,12 +9639,12 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>dates.invoiceDate</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>sort</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -9666,7 +9654,7 @@
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>Filtering incoming invoices by workflow status is the AP daily view — the BF supplierInvoice API does not allow filtering documentStatus today.</t>
+          <t>Sorting incoming invoices by invoice date — dateOfSupplierInvoice is not sortable on the BF API today.</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr"/>
@@ -9679,12 +9667,12 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>dates.invoiceDate</t>
+          <t>match.status</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>sort</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
@@ -9694,7 +9682,7 @@
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>Sorting incoming invoices by invoice date — dateOfSupplierInvoice is not sortable on the BF API today.</t>
+          <t>Re-running/overriding the match verdict via API (rematch) — the check statuses are readable now; a command to re-evaluate is still missing upstream.</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr"/>
@@ -9707,12 +9695,12 @@
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>match.status</t>
+          <t>payment.status</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
@@ -9722,7 +9710,7 @@
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>Re-running/overriding the match verdict via API (rematch) — the check statuses are readable now; a command to re-evaluate is still missing upstream.</t>
+          <t>Open-liabilities view needs filtering by payment status — not allowed on the BF supplierInvoice API today.</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr"/>
@@ -9735,12 +9723,12 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>payment.status</t>
+          <t>approval.status</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
@@ -9750,7 +9738,7 @@
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>Open-liabilities view needs filtering by payment status — not allowed on the BF supplierInvoice API today.</t>
+          <t>Approve/reject via API: BF process steps (GoodsCheck/InvoiceCheck/Payment) are reported to exist — wiring + live verification of those steps is pending (steps were empty on the test instance's metadata).</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr"/>
@@ -9763,12 +9751,12 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>approval.status</t>
+          <t>approval.by</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -9778,7 +9766,7 @@
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>Approve/reject via API: BF process steps (GoodsCheck/InvoiceCheck/Payment) are reported to exist — wiring + live verification of those steps is pending (steps were empty on the test instance's metadata).</t>
+          <t>The approver is not exposed — BF supplierInvoice carries only the check statuses.</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr"/>
@@ -9791,7 +9779,7 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>approval.by</t>
+          <t>approval.at</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
@@ -9806,7 +9794,7 @@
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>The approver is not exposed — BF supplierInvoice carries only the check statuses.</t>
+          <t>The approval timestamp is not exposed by the BF supplierInvoice entity.</t>
         </is>
       </c>
       <c r="F105" s="9" t="inlineStr"/>
@@ -9814,17 +9802,17 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>PurchaseInvoice</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>approval.at</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
@@ -9834,7 +9822,7 @@
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>The approval timestamp is not exposed by the BF supplierInvoice entity.</t>
+          <t>The consolidated product kind (ADR-011) should be settable directly instead of juggling isServiceProduct/isFee/isShippingCostsProduct booleans — the v2 create body only exposes isShippingCostsProduct, so service/digital cannot be expressed.</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr"/>
@@ -9847,7 +9835,7 @@
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
@@ -9862,7 +9850,7 @@
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>The consolidated product kind (ADR-011) should be settable directly instead of juggling isServiceProduct/isFee/isShippingCostsProduct booleans — the v2 create body only exposes isShippingCostsProduct, so service/digital cannot be expressed.</t>
+          <t>Tagging products (assortment curation, campaigns) — product writes now go through v2, but the v2 tags shape ({id,key,name,color}) is not yet mapped/verified, so tag writes stay blue.</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr"/>
@@ -9875,12 +9863,12 @@
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>prices.sale</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
@@ -9890,7 +9878,7 @@
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>Tagging products (assortment curation, campaigns) — product writes now go through v2, but the v2 tags shape ({id,key,name,color}) is not yet mapped/verified, so tag writes stay blue.</t>
+          <t>WRITE works — the sale price is composed as a separate salesPrices write on create/update. READ is still blue: the v3 read model does not carry the sale price (needs the salesPrices include parsed), so a written price is not read back.</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr"/>
@@ -9903,12 +9891,12 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>prices.sale</t>
+          <t>tax.profile</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
@@ -9918,7 +9906,7 @@
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>WRITE works — the sale price is composed as a separate salesPrices write on create/update. READ is still blue: the v3 read model does not carry the sale price (needs the salesPrices include parsed), so a written price is not read back.</t>
+          <t>The 16-account tax matrix consolidated into a referenceable taxProfile (ADR-011) — today only the raw taxAccounts embed exists, not a clean reference.</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr"/>
@@ -9931,12 +9919,12 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>tax.profile</t>
+          <t>logistics.packagingUnits</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>create, read, update</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
@@ -9946,7 +9934,7 @@
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>The 16-account tax matrix consolidated into a referenceable taxProfile (ADR-011) — today only the raw taxAccounts embed exists, not a clean reference.</t>
+          <t>Packaging units (VPE) need the packagingUnits include parsed — not yet mapped.</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr"/>
@@ -9959,12 +9947,12 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>logistics.packagingUnits</t>
+          <t>stock.incoming</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>create, read, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
@@ -9974,7 +9962,7 @@
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>Packaging units (VPE) need the packagingUnits include parsed — not yet mapped.</t>
+          <t>Inbound quantity (ordered but not yet received) is the one stock figure Xentral does not compute: /products/{id}/stocks returns physical, sellable, reserved, correction, pseudo, openSalesOrders, calculated and producible — all mapped — but nothing inbound. The per-warehouse split the same call carries is answered by StockLevel (filter[product], narrowed by warehouse), so it is not duplicated onto the product.</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr"/>
@@ -9987,12 +9975,12 @@
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>stock.incoming</t>
+          <t>suppliers</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
@@ -10002,7 +9990,7 @@
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>Inbound quantity (ordered but not yet received) is the one stock figure Xentral does not compute: /products/{id}/stocks returns physical, sellable, reserved, correction, pseudo, openSalesOrders, calculated and producible — all mapped — but nothing inbound. The per-warehouse split the same call carries is answered by StockLevel (filter[product], narrowed by warehouse), so it is not duplicated onto the product.</t>
+          <t>The default supplier IS writable (mapped to v2 standardSupplier); multi-supplier sourcing (several suppliers with per-supplier price/number) needs a suppliers include/relation not yet mapped, plus a write path.</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr"/>
@@ -10010,17 +9998,17 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>PriceList</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>suppliers</t>
+          <t>entries</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
@@ -10030,7 +10018,7 @@
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>The default supplier IS writable (mapped to v2 standardSupplier); multi-supplier sourcing (several suppliers with per-supplier price/number) needs a suppliers include/relation not yet mapped, plus a write path.</t>
+          <t>v1 salesPrices exposes flat price rows (this entity is one row); the grouped priceList with a tier array needs a composer (ADR-012). Write each tier as its own entry (create/update/delete are live via v3/v1 salesPrices).</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr"/>
@@ -10038,17 +10026,17 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>PriceList</t>
+          <t>StorageLocation</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>entries</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
@@ -10058,7 +10046,7 @@
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>v1 salesPrices exposes flat price rows (this entity is one row); the grouped priceList with a tier array needs a composer (ADR-012). Write each tier as its own entry (create/update/delete are live via v3/v1 salesPrices).</t>
+          <t>Upstream returns the bin description but rejects it on create and update ("The attribute description is not allowed.") — the field is read-only for every API generation we have. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr"/>
@@ -10071,12 +10059,12 @@
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>contents.reserved</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
@@ -10086,7 +10074,7 @@
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>Upstream returns the bin description but rejects it on create and update ("The attribute description is not allowed.") — the field is read-only for every API generation we have. Measured on mvp 2026-08-02.</t>
+          <t>Location contents are composed from the StockLevel projection now; the reserved portion per location stays unavailable — upstream reports reservations only as a product total.</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr"/>
@@ -10099,7 +10087,7 @@
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>contents.reserved</t>
+          <t>locationType</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
@@ -10107,14 +10095,14 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D116" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D116" s="13" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>Location contents are composed from the StockLevel projection now; the reserved portion per location stays unavailable — upstream reports reservations only as a product total.</t>
+          <t>v1 accepts a `locationType` on write with 204 but never returns it on any read, so a value written there cannot be verified or shown. Not modelled until upstream reads it back. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr"/>
@@ -10122,27 +10110,27 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>StorageLocation</t>
+          <t>StockLevel</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>locationType</t>
+          <t>batch</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D117" s="13" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
+          <t>read, list</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E117" s="9" t="inlineStr">
         <is>
-          <t>v1 accepts a `locationType` on write with 204 but never returns it on any read, so a value written there cannot be verified or shown. Not modelled until upstream reads it back. Measured on mvp 2026-08-02.</t>
+          <t>The batch split exists on the v2 items path (qualityControlAttributes) but not on /v1/products/{id}/storageLocations. Emitting batch rows on one anchor only would make the grain depend on the filter, so the projection stays product × storage location. A unified GET /v3/stockLevels is the clean ask (docs/05 #18).</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr"/>
@@ -10155,12 +10143,12 @@
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>batch</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>read, list</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
@@ -10170,7 +10158,7 @@
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>The batch split exists on the v2 items path (qualityControlAttributes) but not on /v1/products/{id}/storageLocations. Emitting batch rows on one anchor only would make the grain depend on the filter, so the projection stays product × storage location. A unified GET /v3/stockLevels is the clean ask (docs/05 #18).</t>
+          <t>The list needs an anchor filter (product or storageLocation): upstream has no global stock collection, so an unanchored query would mean fanning out over every product of the tenant.</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr"/>
@@ -10183,12 +10171,12 @@
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -10198,7 +10186,7 @@
       </c>
       <c r="E119" s="9" t="inlineStr">
         <is>
-          <t>The list needs an anchor filter (product or storageLocation): upstream has no global stock collection, so an unanchored query would mean fanning out over every product of the tenant.</t>
+          <t>No per-location reservation is exposed upstream; /v1/products/{id}/stocks reports reserved only as a product TOTAL. The projection reports quantity and leaves reserved/available blank rather than spreading a total over locations.</t>
         </is>
       </c>
       <c r="F119" s="9" t="inlineStr"/>
@@ -10211,7 +10199,7 @@
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
@@ -10226,7 +10214,7 @@
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>No per-location reservation is exposed upstream; /v1/products/{id}/stocks reports reserved only as a product TOTAL. The projection reports quantity and leaves reserved/available blank rather than spreading a total over locations.</t>
+          <t>Same gap as reserved: available = quantity - reserved is only derivable per product, not per storage location.</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr"/>
@@ -10234,17 +10222,17 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>StockLevel</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>list, read</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
@@ -10254,7 +10242,7 @@
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>Same gap as reserved: available = quantity - reserved is only derivable per product, not per storage location.</t>
+          <t>The stock ledger (Lagerprotokoll) has NO read API at all — the single biggest gap (docs/05 #1). GET /v3/stockMovements is the ask. Until it ships the entity does not declare list/read at all, so a caller learns this from the contract instead of a 404.</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr"/>
@@ -10272,7 +10260,7 @@
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>list, read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
@@ -10282,7 +10270,7 @@
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>The stock ledger (Lagerprotokoll) has NO read API at all — the single biggest gap (docs/05 #1). GET /v3/stockMovements is the ask. Until it ships the entity does not declare list/read at all, so a caller learns this from the contract instead of a 404.</t>
+          <t>A booking returns no identity: the v1 storage-item endpoints answer 201 with an empty body and — contrary to their own spec — send no Location header (verified on mvp 2026-07-31). Without an id a repeated booking cannot be recognised afterwards, which is why correction+setQuantityTo is the only retry-safe write. The ask: return the specced Location header, or the created movement.</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr"/>
@@ -10295,12 +10283,12 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>unitCost</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -10310,7 +10298,7 @@
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>A booking returns no identity: the v1 storage-item endpoints answer 201 with an empty body and — contrary to their own spec — send no Location header (verified on mvp 2026-07-31). Without an id a repeated booking cannot be recognised afterwards, which is why correction+setQuantityTo is the only retry-safe write. The ask: return the specced Location header, or the created movement.</t>
+          <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr"/>
@@ -10318,17 +10306,17 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>StockMovement</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>unitCost</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -10338,7 +10326,7 @@
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
+          <t>Starting a stock take via API (scope: warehouse/locations/products, key date) — the v1 inventory endpoints exist but the write orchestration is not built yet.</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr"/>
@@ -10351,12 +10339,12 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>dates.keyDate</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -10366,7 +10354,7 @@
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>Starting a stock take via API (scope: warehouse/locations/products, key date) — the v1 inventory endpoints exist but the write orchestration is not built yet.</t>
+          <t>The inventory key date (Stichtag) is not exposed by v1 inventoryRuns.</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr"/>
@@ -10379,7 +10367,7 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>dates.keyDate</t>
+          <t>dates.posted</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
@@ -10394,7 +10382,7 @@
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>The inventory key date (Stichtag) is not exposed by v1 inventoryRuns.</t>
+          <t>The posted timestamp is not exposed by v1 inventoryRuns.</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr"/>
@@ -10407,7 +10395,7 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>dates.posted</t>
+          <t>positions</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
@@ -10422,7 +10410,7 @@
       </c>
       <c r="E127" s="9" t="inlineStr">
         <is>
-          <t>The posted timestamp is not exposed by v1 inventoryRuns.</t>
+          <t>Counting positions (expected/counted/difference with values) live in the counting-list reports — not composed into the API payload yet; needed for the GoBD difference review.</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr"/>
@@ -10435,12 +10423,12 @@
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>positions</t>
+          <t>positions.counted</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
@@ -10450,7 +10438,7 @@
       </c>
       <c r="E128" s="9" t="inlineStr">
         <is>
-          <t>Counting positions (expected/counted/difference with values) live in the counting-list reports — not composed into the API payload yet; needed for the GoBD difference review.</t>
+          <t>Submitting counted quantities via API (mobile counting) — needed for headless inventory.</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr"/>
@@ -10463,12 +10451,12 @@
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>positions.counted</t>
+          <t>documents.stockMovements</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
@@ -10478,7 +10466,7 @@
       </c>
       <c r="E129" s="9" t="inlineStr">
         <is>
-          <t>Submitting counted quantities via API (mobile counting) — needed for headless inventory.</t>
+          <t>Posted correction movements per stock take need the stockMovements API (docs/05 #1) to be traceable.</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr"/>
@@ -10486,17 +10474,17 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>documents.stockMovements</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
@@ -10506,7 +10494,7 @@
       </c>
       <c r="E130" s="9" t="inlineStr">
         <is>
-          <t>Posted correction movements per stock take need the stockMovements API (docs/05 #1) to be traceable.</t>
+          <t>Creating a picking run by criteria (wave: channel, shipping method, cutoff, maxOrders) has NO upstream endpoint — the main gap (docs/05 #3); execution (start/complete, totes) already exists.</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr"/>
@@ -10519,12 +10507,12 @@
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>criteria</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
@@ -10534,7 +10522,7 @@
       </c>
       <c r="E131" s="9" t="inlineStr">
         <is>
-          <t>Creating a picking run by criteria (wave: channel, shipping method, cutoff, maxOrders) has NO upstream endpoint — the main gap (docs/05 #3); execution (start/complete, totes) already exists.</t>
+          <t>Pick-run criteria (channel, shipping method) are not exposed by v1 pickLists.</t>
         </is>
       </c>
       <c r="F131" s="9" t="inlineStr"/>
@@ -10547,7 +10535,7 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>criteria</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
@@ -10562,7 +10550,7 @@
       </c>
       <c r="E132" s="9" t="inlineStr">
         <is>
-          <t>Pick-run criteria (channel, shipping method) are not exposed by v1 pickLists.</t>
+          <t>The picked sales orders are not exposed by v1 pickLists (only counts).</t>
         </is>
       </c>
       <c r="F132" s="9" t="inlineStr"/>
@@ -10575,7 +10563,7 @@
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>containers</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
@@ -10590,7 +10578,7 @@
       </c>
       <c r="E133" s="9" t="inlineStr">
         <is>
-          <t>The picked sales orders are not exposed by v1 pickLists (only counts).</t>
+          <t>Totes/containers are not exposed by v1 pickLists.</t>
         </is>
       </c>
       <c r="F133" s="9" t="inlineStr"/>
@@ -10603,12 +10591,12 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>containers</t>
+          <t>strategy</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
@@ -10618,7 +10606,7 @@
       </c>
       <c r="E134" s="9" t="inlineStr">
         <is>
-          <t>Totes/containers are not exposed by v1 pickLists.</t>
+          <t>Choosing the picking strategy (single/multiOrder/wave/zone) at creation — no create endpoint today.</t>
         </is>
       </c>
       <c r="F134" s="9" t="inlineStr"/>
@@ -10631,12 +10619,12 @@
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>strategy</t>
+          <t>tasks</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
@@ -10646,7 +10634,7 @@
       </c>
       <c r="E135" s="9" t="inlineStr">
         <is>
-          <t>Choosing the picking strategy (single/multiOrder/wave/zone) at creation — no create endpoint today.</t>
+          <t>Task-level detail (location, product, quantity, status per pick) is not exposed on the pickLists API — needed for progress boards and pick-path optimisation.</t>
         </is>
       </c>
       <c r="F135" s="9" t="inlineStr"/>
@@ -10659,12 +10647,12 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>tasks</t>
+          <t>tasks.status</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
@@ -10674,7 +10662,7 @@
       </c>
       <c r="E136" s="9" t="inlineStr">
         <is>
-          <t>Task-level detail (location, product, quantity, status per pick) is not exposed on the pickLists API — needed for progress boards and pick-path optimisation.</t>
+          <t>Granular task-level pick confirmation with quantity + scans (docs/05 #3) — today only whole-list start/complete exists.</t>
         </is>
       </c>
       <c r="F136" s="9" t="inlineStr"/>
@@ -10682,17 +10670,17 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>tasks.status</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>list, read</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
@@ -10702,7 +10690,7 @@
       </c>
       <c r="E137" s="9" t="inlineStr">
         <is>
-          <t>Granular task-level pick confirmation with quantity + scans (docs/05 #3) — today only whole-list start/complete exists.</t>
+          <t>Batches exist only as read-only v3 Product includes — no batch resource, no list, no detail (docs/05 #4). GET /v3/batches is the ask.</t>
         </is>
       </c>
       <c r="F137" s="9" t="inlineStr"/>
@@ -10715,12 +10703,12 @@
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>bestBefore</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>list, read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
@@ -10730,7 +10718,7 @@
       </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>Batches exist only as read-only v3 Product includes — no batch resource, no list, no detail (docs/05 #4). GET /v3/batches is the ask.</t>
+          <t>Correcting a best-before date via API — internal web routes only today.</t>
         </is>
       </c>
       <c r="F138" s="9" t="inlineStr"/>
@@ -10743,7 +10731,7 @@
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>bestBefore</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
@@ -10758,7 +10746,7 @@
       </c>
       <c r="E139" s="9" t="inlineStr">
         <is>
-          <t>Correcting a best-before date via API — internal web routes only today.</t>
+          <t>Blocking/releasing a batch (quality hold) via API — maintenance happens only through internal web routes today.</t>
         </is>
       </c>
       <c r="F139" s="9" t="inlineStr"/>
@@ -10771,12 +10759,12 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>trace</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
@@ -10786,7 +10774,7 @@
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>Blocking/releasing a batch (quality hold) via API — maintenance happens only through internal web routes today.</t>
+          <t>Batch trace (which goods receipts brought it in, which delivery notes shipped it — recall scenario) has no API at all (docs/05 #4).</t>
         </is>
       </c>
       <c r="F140" s="9" t="inlineStr"/>
@@ -10794,17 +10782,17 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>trace</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
@@ -10814,7 +10802,7 @@
       </c>
       <c r="E141" s="9" t="inlineStr">
         <is>
-          <t>Batch trace (which goods receipts brought it in, which delivery notes shipped it — recall scenario) has no API at all (docs/05 #4).</t>
+          <t>REVISED (docs/05 #17): BF salesChannel has CRUD — our facade write-mapping + live verification is pending.</t>
         </is>
       </c>
       <c r="F141" s="9" t="inlineStr"/>
@@ -10827,39 +10815,35 @@
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D142" s="11" t="inlineStr">
-        <is>
-          <t>offen — prüfen, evtl. erledigt</t>
+          <t>read, create, update</t>
+        </is>
+      </c>
+      <c r="D142" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>The platform kind (shopify/amazon/…) is not exposed — the BF salesChannel entity carries only a name (05 #17).</t>
-        </is>
-      </c>
-      <c r="F142" s="9" t="inlineStr">
-        <is>
-          <t>live bewiesen für: read</t>
-        </is>
-      </c>
+          <t>The channel type (shop/marketplace/direct/pos) is not on the BF salesChannel record — needed for channel-specific routing.</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>assignee</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
@@ -10874,7 +10858,7 @@
       </c>
       <c r="E143" s="9" t="inlineStr">
         <is>
-          <t>REVISED (docs/05 #17): BF salesChannel has CRUD — our facade write-mapping + live verification is pending.</t>
+          <t>The one thing that would make a task a work item. `assignee` is readOnly upstream: a create or update carrying it answers 2xx and leaves the field null. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F143" s="9" t="inlineStr"/>
@@ -10882,17 +10866,17 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>dates.completed</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>read, create, update</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
@@ -10902,7 +10886,7 @@
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>The channel type (shop/marketplace/direct/pos) is not on the BF salesChannel record — needed for channel-specific routing.</t>
+          <t>Completing a task through the API does not stamp its completion date: `status: completed` persists, `completionDate` stays null.</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr"/>
@@ -10915,84 +10899,28 @@
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>assignee</t>
+          <t>timeline</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
-        </is>
-      </c>
-      <c r="D145" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D145" s="13" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
         <is>
-          <t>The one thing that would make a task a work item. `assignee` is readOnly upstream: a create or update carrying it answers 2xx and leaves the field null. Measured on mvp 2026-08-02.</t>
+          <t>The task's comment thread. Declared `readWrite` with a full sub-node and returned by NO read — not the list, not the single read, and no include/expand parameter produces it. Not modelled until it reads back.</t>
         </is>
       </c>
       <c r="F145" s="9" t="inlineStr"/>
     </row>
-    <row r="146">
-      <c r="A146" s="7" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B146" s="7" t="inlineStr">
-        <is>
-          <t>dates.completed</t>
-        </is>
-      </c>
-      <c r="C146" s="7" t="inlineStr">
-        <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="D146" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E146" s="9" t="inlineStr">
-        <is>
-          <t>Completing a task through the API does not stamp its completion date: `status: completed` persists, `completionDate` stays null.</t>
-        </is>
-      </c>
-      <c r="F146" s="9" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="7" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B147" s="7" t="inlineStr">
-        <is>
-          <t>timeline</t>
-        </is>
-      </c>
-      <c r="C147" s="7" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="D147" s="13" t="inlineStr">
-        <is>
-          <t>Feld fehlt im Modell</t>
-        </is>
-      </c>
-      <c r="E147" s="9" t="inlineStr">
-        <is>
-          <t>The task's comment thread. Declared `readWrite` with a full sub-node and returned by NO read — not the list, not the single read, and no include/expand parameter produces it. Not modelled until it reads back.</t>
-        </is>
-      </c>
-      <c r="F147" s="9" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F147"/>
+  <autoFilter ref="A1:F145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -7587,14 +7587,14 @@
           <t>create, update</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Feld fehlt im Modell</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Partial-shipping policy has no upstream slot — the read reports a hardcoded "allowed". Needs a real v3 field before it can be written or trusted.</t>
+          <t>Partial-shipping policy has no upstream slot. The read used to report a hardcoded "allowed" for every order; that was removed, so the field is now absent rather than wrong. Needs a real v3 field before it can be written or read.</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr"/>

--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Messlauf: 2026-08-08T15:46:22+00:00</t>
+          <t>Messlauf: 2026-08-09T19:43:15+00:00</t>
         </is>
       </c>
     </row>

--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Messlauf: 2026-08-09T19:43:15+00:00</t>
+          <t>Messlauf: 2026-08-09T20:34:15+00:00</t>
         </is>
       </c>
     </row>

--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Messlauf: 2026-08-09T20:34:15+00:00</t>
+          <t>Messlauf: 2026-08-16T07:13:59+00:00</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25 von 80 geforderten Fähigkeiten sind live bewiesen. „nur erreichbar“ heißt: die Route existiert und hat unsere Probe abgelehnt — das ist kein Nachweis.</t>
+          <t>39 von 80 geforderten Fähigkeiten sind live bewiesen. „nur erreichbar“ heißt: die Route existiert und hat unsere Probe abgelehnt — das ist kein Nachweis.</t>
         </is>
       </c>
     </row>
@@ -609,10 +609,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
@@ -637,10 +637,10 @@
         <v>13</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
@@ -665,10 +665,10 @@
         <v>10</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -721,10 +721,10 @@
         <v>8</v>
       </c>
       <c r="C12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
@@ -805,10 +805,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>3</v>
@@ -861,10 +861,10 @@
         <v>10</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
         <v>4</v>
@@ -1929,9 +1929,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr"/>
@@ -1985,9 +1985,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr"/>
@@ -2429,9 +2429,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr"/>
@@ -2485,9 +2485,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr"/>
@@ -2857,9 +2857,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr"/>
@@ -2885,9 +2885,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr"/>
@@ -3309,9 +3309,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E67" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F67" s="9" t="inlineStr"/>
@@ -3365,9 +3365,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E69" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr"/>
@@ -3813,9 +3813,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E84" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr"/>
@@ -3901,9 +3901,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E87" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr"/>
@@ -4165,9 +4165,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E96" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr"/>
@@ -4221,9 +4221,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E98" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr"/>
@@ -4789,9 +4789,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E117" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr"/>
@@ -4877,9 +4877,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E120" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr"/>

--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Übersicht'!$A$6:$H$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fähigkeiten'!$A$1:$F$181</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Felder'!$A$1:$F$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Felder'!$A$1:$F$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,10 +1069,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>46243</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="25">
@@ -6812,7 +6812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10227,12 +10227,12 @@
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>quantity.unit</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>list, read</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>The stock ledger (Lagerprotokoll) has NO read API at all — the single biggest gap (docs/05 #1). GET /v3/stockMovements is the ask. Until it ships the entity does not declare list/read at all, so a caller learns this from the contract instead of a 404.</t>
+          <t>The ledger reports a bare number, no unit. Reading one would cost a product call per row, so the field stays empty until the payload carries it.</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr"/>
@@ -10255,12 +10255,12 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>batch</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>A booking returns no identity: the v1 storage-item endpoints answer 201 with an empty body and — contrary to their own spec — send no Location header (verified on mvp 2026-07-31). Without an id a repeated booking cannot be recognised afterwards, which is why correction+setQuantityTo is the only retry-safe write. The ask: return the specced Location header, or the created movement.</t>
+          <t>A booking can name a batch, but the ledger does not report which one the posting hit — so a batch's movement history is not reconstructable from it (docs/05 #4).</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr"/>
@@ -10283,12 +10283,12 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>unitCost</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
+          <t>A booking returns no identity: the v1 storage-item endpoints answer 201 with an empty body and — contrary to their own spec — send no Location header (verified on mvp 2026-07-31). Without an id a repeated booking cannot be recognised afterwards, which is why correction+setQuantityTo is the only retry-safe write. The ask: return the specced Location header, or the created movement.</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr"/>
@@ -10306,17 +10306,17 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>StockTake</t>
+          <t>StockMovement</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>unitCost</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>Starting a stock take via API (scope: warehouse/locations/products, key date) — the v1 inventory endpoints exist but the write orchestration is not built yet.</t>
+          <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr"/>
@@ -10339,12 +10339,12 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>dates.keyDate</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>The inventory key date (Stichtag) is not exposed by v1 inventoryRuns.</t>
+          <t>Starting a stock take via API (scope: warehouse/locations/products, key date) — the v1 inventory endpoints exist but the write orchestration is not built yet.</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr"/>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>dates.posted</t>
+          <t>dates.keyDate</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>The posted timestamp is not exposed by v1 inventoryRuns.</t>
+          <t>The inventory key date (Stichtag) is not exposed by v1 inventoryRuns.</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr"/>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>positions</t>
+          <t>dates.posted</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="E127" s="9" t="inlineStr">
         <is>
-          <t>Counting positions (expected/counted/difference with values) live in the counting-list reports — not composed into the API payload yet; needed for the GoBD difference review.</t>
+          <t>The posted timestamp is not exposed by v1 inventoryRuns.</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr"/>
@@ -10423,12 +10423,12 @@
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>positions.counted</t>
+          <t>positions</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="E128" s="9" t="inlineStr">
         <is>
-          <t>Submitting counted quantities via API (mobile counting) — needed for headless inventory.</t>
+          <t>Counting positions (expected/counted/difference with values) live in the counting-list reports — not composed into the API payload yet; needed for the GoBD difference review.</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr"/>
@@ -10451,12 +10451,12 @@
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>documents.stockMovements</t>
+          <t>positions.counted</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E129" s="9" t="inlineStr">
         <is>
-          <t>Posted correction movements per stock take need the stockMovements API (docs/05 #1) to be traceable.</t>
+          <t>Submitting counted quantities via API (mobile counting) — needed for headless inventory.</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr"/>
@@ -10474,17 +10474,17 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>PickingRun</t>
+          <t>StockTake</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>documents.stockMovements</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="E130" s="9" t="inlineStr">
         <is>
-          <t>Creating a picking run by criteria (wave: channel, shipping method, cutoff, maxOrders) has NO upstream endpoint — the main gap (docs/05 #3); execution (start/complete, totes) already exists.</t>
+          <t>Posted correction movements per stock take are no longer unreachable — StockMovement lists them via filter[causedBy.type]=inventoryRun + filter[causedBy.id]=&lt;run&gt;. What is missing is composing that into the stock take's own payload.</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr"/>
@@ -10507,12 +10507,12 @@
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>criteria</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="E131" s="9" t="inlineStr">
         <is>
-          <t>Pick-run criteria (channel, shipping method) are not exposed by v1 pickLists.</t>
+          <t>Creating a picking run by criteria (wave: channel, shipping method, cutoff, maxOrders) has NO upstream endpoint — the main gap (docs/05 #3); execution (start/complete, totes) already exists.</t>
         </is>
       </c>
       <c r="F131" s="9" t="inlineStr"/>
@@ -10535,7 +10535,7 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>criteria</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="E132" s="9" t="inlineStr">
         <is>
-          <t>The picked sales orders are not exposed by v1 pickLists (only counts).</t>
+          <t>Pick-run criteria (channel, shipping method) are not exposed by v1 pickLists.</t>
         </is>
       </c>
       <c r="F132" s="9" t="inlineStr"/>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>containers</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="E133" s="9" t="inlineStr">
         <is>
-          <t>Totes/containers are not exposed by v1 pickLists.</t>
+          <t>The picked sales orders are not exposed by v1 pickLists (only counts).</t>
         </is>
       </c>
       <c r="F133" s="9" t="inlineStr"/>
@@ -10591,12 +10591,12 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>strategy</t>
+          <t>containers</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="E134" s="9" t="inlineStr">
         <is>
-          <t>Choosing the picking strategy (single/multiOrder/wave/zone) at creation — no create endpoint today.</t>
+          <t>Totes/containers are not exposed by v1 pickLists.</t>
         </is>
       </c>
       <c r="F134" s="9" t="inlineStr"/>
@@ -10619,12 +10619,12 @@
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>tasks</t>
+          <t>strategy</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>create</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="E135" s="9" t="inlineStr">
         <is>
-          <t>Task-level detail (location, product, quantity, status per pick) is not exposed on the pickLists API — needed for progress boards and pick-path optimisation.</t>
+          <t>Choosing the picking strategy (single/multiOrder/wave/zone) at creation — no create endpoint today.</t>
         </is>
       </c>
       <c r="F135" s="9" t="inlineStr"/>
@@ -10647,12 +10647,12 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>tasks.status</t>
+          <t>tasks</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="E136" s="9" t="inlineStr">
         <is>
-          <t>Granular task-level pick confirmation with quantity + scans (docs/05 #3) — today only whole-list start/complete exists.</t>
+          <t>Task-level detail (location, product, quantity, status per pick) is not exposed on the pickLists API — needed for progress boards and pick-path optimisation.</t>
         </is>
       </c>
       <c r="F136" s="9" t="inlineStr"/>
@@ -10670,17 +10670,17 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>PickingRun</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>tasks.status</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>list, read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="E137" s="9" t="inlineStr">
         <is>
-          <t>Batches exist only as read-only v3 Product includes — no batch resource, no list, no detail (docs/05 #4). GET /v3/batches is the ask.</t>
+          <t>Granular task-level pick confirmation with quantity + scans (docs/05 #3) — today only whole-list start/complete exists.</t>
         </is>
       </c>
       <c r="F137" s="9" t="inlineStr"/>
@@ -10703,12 +10703,12 @@
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>bestBefore</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>list, read</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>Correcting a best-before date via API — internal web routes only today.</t>
+          <t>Batches exist only as read-only v3 Product includes — no batch resource, no list, no detail (docs/05 #4). GET /v3/batches is the ask.</t>
         </is>
       </c>
       <c r="F138" s="9" t="inlineStr"/>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>bestBefore</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="E139" s="9" t="inlineStr">
         <is>
-          <t>Blocking/releasing a batch (quality hold) via API — maintenance happens only through internal web routes today.</t>
+          <t>Correcting a best-before date via API — internal web routes only today.</t>
         </is>
       </c>
       <c r="F139" s="9" t="inlineStr"/>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>trace</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>update</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>Batch trace (which goods receipts brought it in, which delivery notes shipped it — recall scenario) has no API at all (docs/05 #4).</t>
+          <t>Blocking/releasing a batch (quality hold) via API — maintenance happens only through internal web routes today.</t>
         </is>
       </c>
       <c r="F140" s="9" t="inlineStr"/>
@@ -10782,17 +10782,17 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>trace</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="E141" s="9" t="inlineStr">
         <is>
-          <t>REVISED (docs/05 #17): BF salesChannel has CRUD — our facade write-mapping + live verification is pending.</t>
+          <t>Batch trace (which goods receipts brought it in, which delivery notes shipped it — recall scenario) has no API at all (docs/05 #4).</t>
         </is>
       </c>
       <c r="F141" s="9" t="inlineStr"/>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>read, create, update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>The channel type (shop/marketplace/direct/pos) is not on the BF salesChannel record — needed for channel-specific routing.</t>
+          <t>REVISED (docs/05 #17): BF salesChannel has CRUD — our facade write-mapping + live verification is pending.</t>
         </is>
       </c>
       <c r="F142" s="9" t="inlineStr"/>
@@ -10838,17 +10838,17 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>assignee</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>create, update</t>
+          <t>read, create, update</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="E143" s="9" t="inlineStr">
         <is>
-          <t>The one thing that would make a task a work item. `assignee` is readOnly upstream: a create or update carrying it answers 2xx and leaves the field null. Measured on mvp 2026-08-02.</t>
+          <t>The channel type (shop/marketplace/direct/pos) is not on the BF salesChannel record — needed for channel-specific routing.</t>
         </is>
       </c>
       <c r="F143" s="9" t="inlineStr"/>
@@ -10871,12 +10871,12 @@
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>dates.completed</t>
+          <t>assignee</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>create, update</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>Completing a task through the API does not stamp its completion date: `status: completed` persists, `completionDate` stays null.</t>
+          <t>The one thing that would make a task a work item. `assignee` is readOnly upstream: a create or update carrying it answers 2xx and leaves the field null. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr"/>
@@ -10899,28 +10899,56 @@
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
+          <t>dates.completed</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="inlineStr">
+        <is>
+          <t>Completing a task through the API does not stamp its completion date: `status: completed` persists, `completionDate` stays null.</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
           <t>timeline</t>
         </is>
       </c>
-      <c r="C145" s="7" t="inlineStr">
+      <c r="C146" s="7" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="D145" s="13" t="inlineStr">
+      <c r="D146" s="13" t="inlineStr">
         <is>
           <t>Feld fehlt im Modell</t>
         </is>
       </c>
-      <c r="E145" s="9" t="inlineStr">
+      <c r="E146" s="9" t="inlineStr">
         <is>
           <t>The task's comment thread. Declared `readWrite` with a full sub-node and returned by NO read — not the list, not the single read, and no include/expand parameter produces it. Not modelled until it reads back.</t>
         </is>
       </c>
-      <c r="F145" s="9" t="inlineStr"/>
+      <c r="F146" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F145"/>
+  <autoFilter ref="A1:F146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Messlauf: 2026-08-16T07:13:59+00:00</t>
+          <t>Messlauf: 2026-08-16T08:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -10319,9 +10319,9 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D124" s="10" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>offen — prüfen, evtl. erledigt</t>
         </is>
       </c>
       <c r="E124" s="9" t="inlineStr">
@@ -10329,7 +10329,11 @@
           <t>Movement valuation (unitCost at booking time) is required for GoBD-clean stock accounting (ADR-009e) — nothing upstream.</t>
         </is>
       </c>
-      <c r="F124" s="9" t="inlineStr"/>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>live bewiesen für: read</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="inlineStr">

--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Messlauf: 2026-08-16T08:14:05+00:00</t>
+          <t>Messlauf: 2026-08-16T10:49:50+00:00</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>39 von 80 geforderten Fähigkeiten sind live bewiesen. „nur erreichbar“ heißt: die Route existiert und hat unsere Probe abgelehnt — das ist kein Nachweis.</t>
+          <t>49 von 80 geforderten Fähigkeiten sind live bewiesen. „nur erreichbar“ heißt: die Route existiert und hat unsere Probe abgelehnt — das ist kein Nachweis.</t>
         </is>
       </c>
     </row>
@@ -609,10 +609,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
@@ -637,10 +637,10 @@
         <v>13</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
@@ -665,10 +665,10 @@
         <v>10</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -777,10 +777,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
@@ -861,10 +861,10 @@
         <v>10</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>4</v>
@@ -1721,9 +1721,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>nur erreichbar — kein Nachweis</t>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr"/>
@@ -1873,9 +1873,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>nur erreichbar — kein Nachweis</t>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr"/>
@@ -2105,9 +2105,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>nur erreichbar — kein Nachweis</t>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr"/>
@@ -2341,9 +2341,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>nur erreichbar — kein Nachweis</t>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr"/>
@@ -2597,9 +2597,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
-        <is>
-          <t>nur erreichbar — kein Nachweis</t>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr"/>
@@ -2801,9 +2801,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>nur erreichbar — kein Nachweis</t>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr"/>
@@ -3549,9 +3549,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>nur erreichbar — kein Nachweis</t>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr"/>
@@ -3757,9 +3757,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E82" s="11" t="inlineStr">
-        <is>
-          <t>nur erreichbar — kein Nachweis</t>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr"/>
@@ -4557,9 +4557,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E109" s="11" t="inlineStr">
-        <is>
-          <t>nur erreichbar — kein Nachweis</t>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr"/>
@@ -4733,9 +4733,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E115" s="11" t="inlineStr">
-        <is>
-          <t>nur erreichbar — kein Nachweis</t>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr"/>

--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -117,10 +117,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Messlauf: 2026-08-16T10:49:50+00:00</t>
+          <t>Messlauf: 2026-08-16T11:04:39+00:00</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>49 von 80 geforderten Fähigkeiten sind live bewiesen. „nur erreichbar“ heißt: die Route existiert und hat unsere Probe abgelehnt — das ist kein Nachweis.</t>
+          <t>50 von 80 geforderten Fähigkeiten sind live bewiesen. „nur erreichbar“ heißt: die Route existiert und hat unsere Probe abgelehnt — das ist kein Nachweis.</t>
         </is>
       </c>
     </row>
@@ -721,10 +721,10 @@
         <v>8</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>4</v>
@@ -3101,9 +3101,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>ausgeführt, nicht nachgelesen</t>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>FEHLER</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr"/>
@@ -3221,9 +3221,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E64" s="11" t="inlineStr">
-        <is>
-          <t>nur erreichbar — kein Nachweis</t>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr"/>
@@ -3841,7 +3841,7 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E85" s="12" t="inlineStr">
+      <c r="E85" s="13" t="inlineStr">
         <is>
           <t>ungetestet</t>
         </is>
@@ -4613,7 +4613,7 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E111" s="12" t="inlineStr">
+      <c r="E111" s="13" t="inlineStr">
         <is>
           <t>ungetestet</t>
         </is>
@@ -5289,7 +5289,7 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E133" s="12" t="inlineStr">
+      <c r="E133" s="13" t="inlineStr">
         <is>
           <t>ungetestet</t>
         </is>
@@ -5381,7 +5381,7 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E136" s="12" t="inlineStr">
+      <c r="E136" s="13" t="inlineStr">
         <is>
           <t>ungetestet</t>
         </is>
@@ -7351,7 +7351,7 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Feld fehlt im Modell</t>
         </is>
@@ -7587,7 +7587,7 @@
           <t>create, update</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Feld fehlt im Modell</t>
         </is>
@@ -7699,7 +7699,7 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Feld fehlt im Modell</t>
         </is>
@@ -8407,7 +8407,7 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>Feld fehlt im Modell</t>
         </is>
@@ -9031,7 +9031,7 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr">
+      <c r="D78" s="12" t="inlineStr">
         <is>
           <t>Feld fehlt im Modell</t>
         </is>
@@ -10095,7 +10095,7 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D116" s="13" t="inlineStr">
+      <c r="D116" s="12" t="inlineStr">
         <is>
           <t>Feld fehlt im Modell</t>
         </is>
@@ -10939,7 +10939,7 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D146" s="13" t="inlineStr">
+      <c r="D146" s="12" t="inlineStr">
         <is>
           <t>Feld fehlt im Modell</t>
         </is>

--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -117,10 +117,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Messlauf: 2026-08-16T11:04:39+00:00</t>
+          <t>Messlauf: 2026-08-16T11:21:51+00:00</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>50 von 80 geforderten Fähigkeiten sind live bewiesen. „nur erreichbar“ heißt: die Route existiert und hat unsere Probe abgelehnt — das ist kein Nachweis.</t>
+          <t>51 von 80 geforderten Fähigkeiten sind live bewiesen. „nur erreichbar“ heißt: die Route existiert und hat unsere Probe abgelehnt — das ist kein Nachweis.</t>
         </is>
       </c>
     </row>
@@ -721,10 +721,10 @@
         <v>8</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>4</v>
@@ -3101,9 +3101,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E60" s="12" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr"/>
@@ -3841,7 +3841,7 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E85" s="13" t="inlineStr">
+      <c r="E85" s="12" t="inlineStr">
         <is>
           <t>ungetestet</t>
         </is>
@@ -4613,7 +4613,7 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E111" s="13" t="inlineStr">
+      <c r="E111" s="12" t="inlineStr">
         <is>
           <t>ungetestet</t>
         </is>
@@ -5289,7 +5289,7 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E133" s="13" t="inlineStr">
+      <c r="E133" s="12" t="inlineStr">
         <is>
           <t>ungetestet</t>
         </is>
@@ -5381,7 +5381,7 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E136" s="13" t="inlineStr">
+      <c r="E136" s="12" t="inlineStr">
         <is>
           <t>ungetestet</t>
         </is>
@@ -7351,7 +7351,7 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Feld fehlt im Modell</t>
         </is>
@@ -7587,7 +7587,7 @@
           <t>create, update</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>Feld fehlt im Modell</t>
         </is>
@@ -7699,7 +7699,7 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Feld fehlt im Modell</t>
         </is>
@@ -8407,7 +8407,7 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>Feld fehlt im Modell</t>
         </is>
@@ -9031,7 +9031,7 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D78" s="12" t="inlineStr">
+      <c r="D78" s="13" t="inlineStr">
         <is>
           <t>Feld fehlt im Modell</t>
         </is>
@@ -10095,7 +10095,7 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D116" s="12" t="inlineStr">
+      <c r="D116" s="13" t="inlineStr">
         <is>
           <t>Feld fehlt im Modell</t>
         </is>
@@ -10939,7 +10939,7 @@
           <t>read</t>
         </is>
       </c>
-      <c r="D146" s="12" t="inlineStr">
+      <c r="D146" s="13" t="inlineStr">
         <is>
           <t>Feld fehlt im Modell</t>
         </is>

--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Messlauf: 2026-08-16T10:49:50+00:00</t>
+          <t>Messlauf: 2026-08-16T11:21:51+00:00</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>49 von 80 geforderten Fähigkeiten sind live bewiesen. „nur erreichbar“ heißt: die Route existiert und hat unsere Probe abgelehnt — das ist kein Nachweis.</t>
+          <t>51 von 80 geforderten Fähigkeiten sind live bewiesen. „nur erreichbar“ heißt: die Route existiert und hat unsere Probe abgelehnt — das ist kein Nachweis.</t>
         </is>
       </c>
     </row>
@@ -721,10 +721,10 @@
         <v>8</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>4</v>
@@ -3101,9 +3101,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>ausgeführt, nicht nachgelesen</t>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr"/>
@@ -3221,9 +3221,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E64" s="11" t="inlineStr">
-        <is>
-          <t>nur erreichbar — kein Nachweis</t>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr"/>

--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Messlauf: 2026-08-16T11:21:51+00:00</t>
+          <t>Messlauf: 2026-08-16T17:00:33+00:00</t>
         </is>
       </c>
     </row>
@@ -3841,9 +3841,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E85" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>nur erreichbar — kein Nachweis</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr"/>
@@ -4613,9 +4613,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E111" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>nur erreichbar — kein Nachweis</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr"/>

--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Messlauf: 2026-08-16T17:00:33+00:00</t>
+          <t>Messlauf: 2026-08-16T17:09:40+00:00</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>51 von 80 geforderten Fähigkeiten sind live bewiesen. „nur erreichbar“ heißt: die Route existiert und hat unsere Probe abgelehnt — das ist kein Nachweis.</t>
+          <t>53 von 80 geforderten Fähigkeiten sind live bewiesen. „nur erreichbar“ heißt: die Route existiert und hat unsere Probe abgelehnt — das ist kein Nachweis.</t>
         </is>
       </c>
     </row>
@@ -777,10 +777,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
@@ -861,10 +861,10 @@
         <v>10</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>4</v>
@@ -3841,9 +3841,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E85" s="11" t="inlineStr">
-        <is>
-          <t>nur erreichbar — kein Nachweis</t>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr"/>
@@ -4613,9 +4613,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E111" s="11" t="inlineStr">
-        <is>
-          <t>nur erreichbar — kein Nachweis</t>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr"/>

--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Messlauf: 2026-08-16T11:21:51+00:00</t>
+          <t>Messlauf: 2026-08-16T17:09:40+00:00</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>51 von 80 geforderten Fähigkeiten sind live bewiesen. „nur erreichbar“ heißt: die Route existiert und hat unsere Probe abgelehnt — das ist kein Nachweis.</t>
+          <t>53 von 80 geforderten Fähigkeiten sind live bewiesen. „nur erreichbar“ heißt: die Route existiert und hat unsere Probe abgelehnt — das ist kein Nachweis.</t>
         </is>
       </c>
     </row>
@@ -777,10 +777,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
@@ -861,10 +861,10 @@
         <v>10</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>4</v>
@@ -3841,9 +3841,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E85" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr"/>
@@ -4613,9 +4613,9 @@
           <t>gebaut</t>
         </is>
       </c>
-      <c r="E111" s="12" t="inlineStr">
-        <is>
-          <t>ungetestet</t>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>bewiesen</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr"/>

--- a/cores/agentos_neo_xentral/review.xlsx
+++ b/cores/agentos_neo_xentral/review.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Messlauf: 2026-08-16T17:09:40+00:00</t>
+          <t>Messlauf: 2026-08-16T17:31:02+00:00</t>
         </is>
       </c>
     </row>
